--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6914BA7-DAC9-46C5-94B5-90C10012C56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93B0383-A5AB-450C-B909-495EAB739141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -23384,6 +23384,9 @@
         <f t="shared" si="18"/>
         <v>UTC-4</v>
       </c>
+      <c r="E900" s="20">
+        <v>525474</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93B0383-A5AB-450C-B909-495EAB739141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF90051-BB08-42DD-8B09-EAD512D1C642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -86,10 +86,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -132,23 +132,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1A1A1A"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -192,7 +189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -209,61 +206,61 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6833,14 +6830,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E900"/>
+  <dimension ref="A1:E901"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.77734375" style="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.109375" style="6"/>
   </cols>
   <sheetData>
@@ -23386,6 +23383,36 @@
       </c>
       <c r="E900" s="20">
         <v>525474</v>
+      </c>
+    </row>
+    <row r="901" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A901" s="8">
+        <v>46207</v>
+      </c>
+      <c r="B901" s="8">
+        <v>46211</v>
+      </c>
+      <c r="C901" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="D901" s="7" t="str">
+        <f t="shared" ref="D901" si="19">IF(
+ AND(
+  A901 &gt;= IF(
+         YEAR(A901)&gt;=2007,
+         DATE(YEAR(A901),3,14)-WEEKDAY(DATE(YEAR(A901),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A901),4,7)-WEEKDAY(DATE(YEAR(A901),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A901 &lt;  IF(
+         YEAR(A901)&gt;=2007,
+         DATE(YEAR(A901),11,7)-WEEKDAY(DATE(YEAR(A901),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A901),10,31)-WEEKDAY(DATE(YEAR(A901),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF90051-BB08-42DD-8B09-EAD512D1C642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006AFFB7-61DB-476F-B75C-155A42C8C272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -23393,7 +23393,7 @@
         <v>46211</v>
       </c>
       <c r="C901" s="21">
-        <v>0.5</v>
+        <v>0.50138888888888888</v>
       </c>
       <c r="D901" s="7" t="str">
         <f t="shared" ref="D901" si="19">IF(
@@ -23413,6 +23413,9 @@
  "UTC-5"
 )</f>
         <v>UTC-4</v>
+      </c>
+      <c r="E901" s="20">
+        <v>482121</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006AFFB7-61DB-476F-B75C-155A42C8C272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7724D715-6013-4504-B7F3-62A78DD5C3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -86,12 +86,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -189,7 +189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -206,68 +206,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -285,7 +285,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6534,9 +6534,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6574,7 +6574,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6680,7 +6680,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6822,7 +6822,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6830,18 +6830,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E901"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E902"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="6"/>
+    <col min="1" max="1" width="12.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.08984375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -7122,7 +7122,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -7644,7 +7644,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -7860,7 +7860,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -7896,7 +7896,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -8040,7 +8040,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -8127,7 +8127,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -8181,7 +8181,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -8271,7 +8271,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -8397,7 +8397,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -8541,7 +8541,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -8559,7 +8559,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" ht="15" thickBot="1">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" ht="15" thickBot="1">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" ht="15" thickBot="1">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" ht="15" thickBot="1">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" ht="15" thickBot="1">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" ht="15" thickBot="1">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" ht="15" thickBot="1">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" ht="15" thickBot="1">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -8829,7 +8829,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" ht="15" thickBot="1">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" ht="15" thickBot="1">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" ht="15" thickBot="1">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" ht="15" thickBot="1">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:5" ht="15" thickBot="1">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -8919,7 +8919,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:5" ht="15" thickBot="1">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -8937,7 +8937,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:5" ht="15" thickBot="1">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:5" ht="15" thickBot="1">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:5" ht="15" thickBot="1">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:5" ht="15" thickBot="1">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:5" ht="15" thickBot="1">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:5" ht="15" thickBot="1">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:5" ht="15" thickBot="1">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:5" ht="15" thickBot="1">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:5" ht="15" thickBot="1">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:5" ht="15" thickBot="1">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -9117,7 +9117,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:5" ht="15" thickBot="1">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:5" ht="15" thickBot="1">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:5" ht="15" thickBot="1">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:5" ht="15" thickBot="1">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -9189,7 +9189,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:5" ht="15" thickBot="1">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -9207,7 +9207,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:5" ht="15" thickBot="1">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:5" ht="15" thickBot="1">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:5" ht="15" thickBot="1">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:5" ht="15" thickBot="1">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:5" ht="15" thickBot="1">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:5" ht="15" thickBot="1">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:5" ht="15" thickBot="1">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:5" ht="15" thickBot="1">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:5" ht="15" thickBot="1">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:5" ht="15" thickBot="1">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:5" ht="15" thickBot="1">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:5" ht="15" thickBot="1">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:5" ht="15" thickBot="1">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -9456,7 +9456,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:5" ht="15" thickBot="1">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:5" ht="15" thickBot="1">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:5" ht="15" thickBot="1">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:5" ht="15" thickBot="1">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:5" ht="15" thickBot="1">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:5" ht="15" thickBot="1">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:5" ht="15" thickBot="1">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -9582,7 +9582,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:5" ht="15" thickBot="1">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:5" ht="15" thickBot="1">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:5" ht="15" thickBot="1">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:5" ht="15" thickBot="1">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:5" ht="15" thickBot="1">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:5" ht="15" thickBot="1">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:5" ht="15" thickBot="1">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -9708,7 +9708,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:5" ht="15" thickBot="1">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -9726,7 +9726,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:5" ht="15" thickBot="1">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:5" ht="15" thickBot="1">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -9762,7 +9762,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:5" ht="15" thickBot="1">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:5" ht="15" thickBot="1">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:5" ht="15" thickBot="1">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:5" ht="15" thickBot="1">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:5" ht="15" thickBot="1">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:5" ht="15" thickBot="1">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:5" ht="15" thickBot="1">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:5" ht="15" thickBot="1">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:5" ht="15" thickBot="1">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:5" ht="15" thickBot="1">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:5" ht="15" thickBot="1">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -9960,7 +9960,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:5" ht="15" thickBot="1">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -9978,7 +9978,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:5" ht="15" thickBot="1">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -9996,7 +9996,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:5" ht="15" thickBot="1">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:5" ht="15" thickBot="1">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -10032,7 +10032,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:5" ht="15" thickBot="1">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:5" ht="15" thickBot="1">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:5" ht="15" thickBot="1">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:5" ht="15" thickBot="1">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:5" ht="15" thickBot="1">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:5" ht="15" thickBot="1">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -10140,7 +10140,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:5" ht="15" thickBot="1">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:5" ht="15" thickBot="1">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -10176,7 +10176,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:5" ht="15" thickBot="1">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:5" ht="15" thickBot="1">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -10212,7 +10212,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:5" ht="15" thickBot="1">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:5" ht="15" thickBot="1">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -10248,7 +10248,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:5" ht="15" thickBot="1">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:5" ht="15" thickBot="1">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:5" ht="15" thickBot="1">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:5" ht="15" thickBot="1">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -10320,7 +10320,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:5" ht="15" thickBot="1">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -10338,7 +10338,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:5" ht="15" thickBot="1">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -10356,7 +10356,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:5" ht="15" thickBot="1">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:5" ht="15" thickBot="1">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:5" ht="15" thickBot="1">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:5" ht="15" thickBot="1">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -10443,7 +10443,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:5" ht="15" thickBot="1">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -10461,7 +10461,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:5" ht="15" thickBot="1">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:5" ht="15" thickBot="1">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -10497,7 +10497,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:5" ht="15" thickBot="1">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -10515,7 +10515,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:5" ht="15" thickBot="1">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:5" ht="15" thickBot="1">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:5" ht="15" thickBot="1">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -10569,7 +10569,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:5" ht="15" thickBot="1">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -10587,7 +10587,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:5" ht="15" thickBot="1">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:5" ht="15" thickBot="1">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:5" ht="15" thickBot="1">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -10641,7 +10641,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:5" ht="15" thickBot="1">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -10659,7 +10659,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:5" ht="15" thickBot="1">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -10677,7 +10677,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:5" ht="15" thickBot="1">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:5" ht="15" thickBot="1">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:5" ht="15" thickBot="1">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -10731,7 +10731,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:5" ht="15" thickBot="1">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:5" ht="15" thickBot="1">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -10767,7 +10767,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:5" ht="15" thickBot="1">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:5" ht="15" thickBot="1">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:5" ht="15" thickBot="1">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:5" ht="15" thickBot="1">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -10839,7 +10839,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:5" ht="15" thickBot="1">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:5" ht="15" thickBot="1">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:5" ht="15" thickBot="1">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:5" ht="15" thickBot="1">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:5" ht="15" thickBot="1">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -10929,7 +10929,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:5" ht="15" thickBot="1">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:5" ht="15" thickBot="1">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:5" ht="15" thickBot="1">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -10983,7 +10983,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:5" ht="15" thickBot="1">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -11001,7 +11001,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:5" ht="15" thickBot="1">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:5" ht="15" thickBot="1">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:5" ht="15" thickBot="1">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -11055,7 +11055,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:5" ht="15" thickBot="1">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:5" ht="15" thickBot="1">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -11091,7 +11091,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:5" ht="15" thickBot="1">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -11109,7 +11109,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:5" ht="15" thickBot="1">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:5" ht="15" thickBot="1">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:5" ht="15" thickBot="1">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -11163,7 +11163,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:5" ht="15" thickBot="1">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -11181,7 +11181,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:5" ht="15" thickBot="1">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -11199,7 +11199,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:5" ht="15" thickBot="1">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:5" ht="15" thickBot="1">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -11235,7 +11235,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:5" ht="15" thickBot="1">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:5" ht="15" thickBot="1">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -11271,7 +11271,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:5" ht="15" thickBot="1">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:5" ht="15" thickBot="1">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -11307,7 +11307,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:5" ht="15" thickBot="1">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:5" ht="15" thickBot="1">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -11343,7 +11343,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:5" ht="15" thickBot="1">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -11361,7 +11361,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:5" ht="15" thickBot="1">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -11379,7 +11379,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:5" ht="15" thickBot="1">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -11397,7 +11397,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:5" ht="15" thickBot="1">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -11415,7 +11415,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:5" ht="15" thickBot="1">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:5" ht="15" thickBot="1">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -11451,7 +11451,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:5" ht="15" thickBot="1">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -11469,7 +11469,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:5" ht="15" thickBot="1">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:5" ht="15" thickBot="1">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -11505,7 +11505,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:5" ht="15" thickBot="1">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -11523,7 +11523,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:5" ht="15" thickBot="1">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:5" ht="15" thickBot="1">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -11574,7 +11574,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:5" ht="15" thickBot="1">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:5" ht="15" thickBot="1">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -11610,7 +11610,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:5" ht="15" thickBot="1">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:5" ht="15" thickBot="1">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -11646,7 +11646,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:5" ht="15" thickBot="1">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:5" ht="15" thickBot="1">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:5" ht="15" thickBot="1">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -11700,7 +11700,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:5" ht="15" thickBot="1">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:5" ht="15" thickBot="1">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -11736,7 +11736,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:5" ht="15" thickBot="1">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:5" ht="15" thickBot="1">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -11772,7 +11772,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:5" ht="15" thickBot="1">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -11790,7 +11790,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:5" ht="15" thickBot="1">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -11808,7 +11808,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:5" ht="15" thickBot="1">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -11826,7 +11826,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:5" ht="15" thickBot="1">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -11844,7 +11844,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:5" ht="15" thickBot="1">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:5" ht="15" thickBot="1">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:5" ht="15" thickBot="1">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:5" ht="15" thickBot="1">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:5" ht="15" thickBot="1">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -11934,7 +11934,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:5" ht="15" thickBot="1">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:5" ht="15" thickBot="1">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -11970,7 +11970,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:5" ht="15" thickBot="1">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:5" ht="15" thickBot="1">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:5" ht="15" thickBot="1">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:5" ht="15" thickBot="1">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:5" ht="15" thickBot="1">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -12060,7 +12060,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:5" ht="15" thickBot="1">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -12078,7 +12078,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:5" ht="15" thickBot="1">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:5" ht="15" thickBot="1">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -12114,7 +12114,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:5" ht="15" thickBot="1">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:5" ht="15" thickBot="1">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -12150,7 +12150,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:5" ht="15" thickBot="1">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:5" ht="15" thickBot="1">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -12186,7 +12186,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:5" ht="15" thickBot="1">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:5" ht="15" thickBot="1">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:5" ht="15" thickBot="1">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -12240,7 +12240,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:5" ht="15" thickBot="1">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:5" ht="15" thickBot="1">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -12276,7 +12276,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:5" ht="15" thickBot="1">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:5" ht="15" thickBot="1">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:5" ht="15" thickBot="1">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -12330,7 +12330,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:5" ht="15" thickBot="1">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -12348,7 +12348,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:5" ht="15" thickBot="1">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:5" ht="15" thickBot="1">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -12384,7 +12384,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:5" ht="15" thickBot="1">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:5" ht="15" thickBot="1">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -12420,7 +12420,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:5" ht="15" thickBot="1">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:5" ht="15" thickBot="1">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:5" ht="15" thickBot="1">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -12474,7 +12474,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:5" ht="15" thickBot="1">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:5" ht="15" thickBot="1">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:5" ht="15" thickBot="1">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -12528,7 +12528,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:5" ht="15" thickBot="1">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -12546,7 +12546,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:5" ht="15" thickBot="1">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:5" ht="15" thickBot="1">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -12582,7 +12582,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:5" ht="15" thickBot="1">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -12600,7 +12600,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:5" ht="15" thickBot="1">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -12618,7 +12618,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:5" ht="15" thickBot="1">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:5" ht="15" thickBot="1">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:5" ht="15" thickBot="1">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -12672,7 +12672,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:5" ht="15" thickBot="1">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -12690,7 +12690,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:5" ht="15" thickBot="1">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:5" ht="15" thickBot="1">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:5" ht="15" thickBot="1">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -12759,7 +12759,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:5" ht="15" thickBot="1">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -12777,7 +12777,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:5" ht="15" thickBot="1">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:5" ht="15" thickBot="1">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:5" ht="15" thickBot="1">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:5" ht="15" thickBot="1">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -12849,7 +12849,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:5" ht="15" thickBot="1">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -12867,7 +12867,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:5" ht="15" thickBot="1">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:5" ht="15" thickBot="1">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -12903,7 +12903,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:5" ht="15" thickBot="1">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -12921,7 +12921,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:5" ht="15" thickBot="1">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:5" ht="15" thickBot="1">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -12957,7 +12957,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:5" ht="15" thickBot="1">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -12975,7 +12975,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:5" ht="15" thickBot="1">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -12993,7 +12993,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:5" ht="15" thickBot="1">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -13011,7 +13011,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:5" ht="15" thickBot="1">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -13029,7 +13029,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:5" ht="15" thickBot="1">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -13047,7 +13047,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:5" ht="15" thickBot="1">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -13065,7 +13065,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:5" ht="15" thickBot="1">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -13083,7 +13083,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:5" ht="15" thickBot="1">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -13101,7 +13101,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:5" ht="15" thickBot="1">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:5" ht="15" thickBot="1">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -13137,7 +13137,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:5" ht="15" thickBot="1">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:5" ht="15" thickBot="1">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:5" ht="15" thickBot="1">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -13191,7 +13191,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:5" ht="15" thickBot="1">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:5" ht="15" thickBot="1">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -13227,7 +13227,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:5" ht="15" thickBot="1">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:5" ht="15" thickBot="1">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -13263,7 +13263,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:5" ht="15" thickBot="1">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -13281,7 +13281,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:5" ht="15" thickBot="1">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:5" ht="15" thickBot="1">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -13317,7 +13317,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:5" ht="15" thickBot="1">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:5" ht="15" thickBot="1">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -13353,7 +13353,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:5" ht="15" thickBot="1">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -13371,7 +13371,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:5" ht="15" thickBot="1">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -13389,7 +13389,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:5" ht="15" thickBot="1">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -13407,7 +13407,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:5" ht="15" thickBot="1">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -13425,7 +13425,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:5" ht="15" thickBot="1">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -13443,7 +13443,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:5" ht="15" thickBot="1">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -13461,7 +13461,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:5" ht="15" thickBot="1">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -13479,7 +13479,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:5" ht="15" thickBot="1">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -13497,7 +13497,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:5" ht="15" thickBot="1">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -13515,7 +13515,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:5" ht="15" thickBot="1">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:5" ht="15" thickBot="1">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -13551,7 +13551,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:5" ht="15" thickBot="1">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -13569,7 +13569,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:5" ht="15" thickBot="1">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -13587,7 +13587,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:5" ht="15" thickBot="1">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -13605,7 +13605,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:5" ht="15" thickBot="1">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -13623,7 +13623,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:5" ht="15" thickBot="1">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -13641,7 +13641,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:5" ht="15" thickBot="1">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -13659,7 +13659,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:5" ht="15" thickBot="1">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -13677,7 +13677,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:5" ht="15" thickBot="1">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:5" ht="15" thickBot="1">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -13713,7 +13713,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:5" ht="15" thickBot="1">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -13731,7 +13731,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:5" ht="15" thickBot="1">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -13749,7 +13749,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:5" ht="15" thickBot="1">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -13767,7 +13767,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:5" ht="15" thickBot="1">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -13785,7 +13785,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:5" ht="15" thickBot="1">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -13803,7 +13803,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:5" ht="15" thickBot="1">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -13821,7 +13821,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:5" ht="15" thickBot="1">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -13839,7 +13839,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:5" ht="15" thickBot="1">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -13857,7 +13857,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:5" ht="15" thickBot="1">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -13875,7 +13875,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:5" ht="15" thickBot="1">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:5" ht="15" thickBot="1">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -13926,7 +13926,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:5" ht="15" thickBot="1">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -13944,7 +13944,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:5" ht="15" thickBot="1">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:5" ht="15" thickBot="1">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -13980,7 +13980,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:5" ht="15" thickBot="1">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -13998,7 +13998,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:5" ht="15" thickBot="1">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:5" ht="15" thickBot="1">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -14034,7 +14034,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:5" ht="15" thickBot="1">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -14052,7 +14052,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:5" ht="15" thickBot="1">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -14070,7 +14070,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:5" ht="15" thickBot="1">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -14088,7 +14088,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:5" ht="15" thickBot="1">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -14106,7 +14106,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:5" ht="15" thickBot="1">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -14124,7 +14124,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:5" ht="15" thickBot="1">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:5" ht="15" thickBot="1">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -14160,7 +14160,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:5" ht="15" thickBot="1">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -14178,7 +14178,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:5" ht="15" thickBot="1">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -14196,7 +14196,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:5" ht="15" thickBot="1">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -14214,7 +14214,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:5" ht="15" thickBot="1">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -14232,7 +14232,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:5" ht="15" thickBot="1">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -14250,7 +14250,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:5" ht="15" thickBot="1">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -14268,7 +14268,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:5" ht="15" thickBot="1">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -14286,7 +14286,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:5" ht="15" thickBot="1">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -14304,7 +14304,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:5" ht="15" thickBot="1">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:5" ht="15" thickBot="1">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:5" ht="15" thickBot="1">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -14358,7 +14358,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:5" ht="15" thickBot="1">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -14376,7 +14376,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:5" ht="15" thickBot="1">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -14394,7 +14394,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:5" ht="15" thickBot="1">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -14412,7 +14412,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:5" ht="15" thickBot="1">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -14430,7 +14430,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:5" ht="15" thickBot="1">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -14448,7 +14448,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:5" ht="15" thickBot="1">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:5" ht="15" thickBot="1">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:5" ht="15" thickBot="1">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -14502,7 +14502,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:5" ht="15" thickBot="1">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -14520,7 +14520,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:5" ht="15" thickBot="1">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:5" ht="15" thickBot="1">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -14556,7 +14556,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:5" ht="15" thickBot="1">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -14574,7 +14574,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:5" ht="15" thickBot="1">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:5" ht="15" thickBot="1">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -14610,7 +14610,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:5" ht="15" thickBot="1">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -14628,7 +14628,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:5" ht="15" thickBot="1">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -14646,7 +14646,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:5" ht="15" thickBot="1">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:5" ht="15" thickBot="1">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:5" ht="15" thickBot="1">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -14700,7 +14700,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:5" ht="15" thickBot="1">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:5" ht="15" thickBot="1">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -14736,7 +14736,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:5" ht="15" thickBot="1">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -14754,7 +14754,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:5" ht="15" thickBot="1">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -14772,7 +14772,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:5" ht="15" thickBot="1">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -14790,7 +14790,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:5" ht="15" thickBot="1">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -14808,7 +14808,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:5" ht="15" thickBot="1">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -14826,7 +14826,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:5" ht="15" thickBot="1">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -14844,7 +14844,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:5" ht="15" thickBot="1">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -14862,7 +14862,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:5" ht="15" thickBot="1">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -14880,7 +14880,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:5" ht="15" thickBot="1">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:5" ht="15" thickBot="1">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -14916,7 +14916,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:5" ht="15" thickBot="1">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -14934,7 +14934,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:5" ht="15" thickBot="1">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -14952,7 +14952,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:5" ht="15" thickBot="1">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -14970,7 +14970,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:5" ht="15" thickBot="1">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -14988,7 +14988,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:5" ht="15" thickBot="1">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -15006,7 +15006,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:5" ht="15" thickBot="1">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -15024,7 +15024,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:5" ht="15" thickBot="1">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -15042,7 +15042,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:5" ht="15" thickBot="1">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -15075,7 +15075,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:5" ht="15" thickBot="1">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -15093,7 +15093,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:5" ht="15" thickBot="1">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -15111,7 +15111,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:5" ht="15" thickBot="1">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -15129,7 +15129,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:5" ht="15" thickBot="1">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -15147,7 +15147,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:5" ht="15" thickBot="1">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -15165,7 +15165,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:5" ht="15" thickBot="1">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -15183,7 +15183,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:5" ht="15" thickBot="1">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -15201,7 +15201,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:5" ht="15" thickBot="1">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -15219,7 +15219,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:5" ht="15" thickBot="1">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -15237,7 +15237,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:5" ht="15" thickBot="1">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -15255,7 +15255,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:5" ht="15" thickBot="1">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -15273,7 +15273,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:5" ht="15" thickBot="1">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -15291,7 +15291,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:5" ht="15" thickBot="1">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -15309,7 +15309,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:5" ht="15" thickBot="1">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:5" ht="15" thickBot="1">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -15345,7 +15345,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:5" ht="15" thickBot="1">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -15363,7 +15363,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:5" ht="15" thickBot="1">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -15381,7 +15381,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:5" ht="15" thickBot="1">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -15399,7 +15399,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:5" ht="15" thickBot="1">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -15417,7 +15417,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:5" ht="15" thickBot="1">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -15435,7 +15435,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:5" ht="15" thickBot="1">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -15453,7 +15453,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:5" ht="15" thickBot="1">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -15471,7 +15471,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:5" ht="15" thickBot="1">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -15489,7 +15489,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:5" ht="15" thickBot="1">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -15507,7 +15507,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:5" ht="15" thickBot="1">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -15525,7 +15525,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:5" ht="15" thickBot="1">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -15543,7 +15543,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:5" ht="15" thickBot="1">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -15561,7 +15561,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:5" ht="15" thickBot="1">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -15579,7 +15579,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:5" ht="15" thickBot="1">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -15597,7 +15597,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:5" ht="15" thickBot="1">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -15615,7 +15615,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:5" ht="15" thickBot="1">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -15633,7 +15633,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:5" ht="15" thickBot="1">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -15651,7 +15651,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:5" ht="15" thickBot="1">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -15669,7 +15669,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:5" ht="15" thickBot="1">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -15687,7 +15687,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:5" ht="15" thickBot="1">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -15705,7 +15705,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:5" ht="15" thickBot="1">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -15723,7 +15723,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:5" ht="15" thickBot="1">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -15741,7 +15741,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:5" ht="15" thickBot="1">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -15759,7 +15759,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:5" ht="15" thickBot="1">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -15777,7 +15777,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:5" ht="15" thickBot="1">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -15795,7 +15795,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:5" ht="15" thickBot="1">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:5" ht="15" thickBot="1">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -15831,7 +15831,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:5" ht="15" thickBot="1">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -15849,7 +15849,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:5" ht="15" thickBot="1">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -15867,7 +15867,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:5" ht="15" thickBot="1">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -15885,7 +15885,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:5" ht="15" thickBot="1">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:5" ht="15" thickBot="1">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -15921,7 +15921,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:5" ht="15" thickBot="1">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -15939,7 +15939,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:5" ht="15" thickBot="1">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -15957,7 +15957,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:5" ht="15" thickBot="1">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -15975,7 +15975,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:5" ht="15" thickBot="1">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:5" ht="15" thickBot="1">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -16011,7 +16011,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:5" ht="15" thickBot="1">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -16029,7 +16029,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:5" ht="15" thickBot="1">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -16047,7 +16047,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:5" ht="15" thickBot="1">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -16065,7 +16065,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:5" ht="15" thickBot="1">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -16083,7 +16083,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:5" ht="15" thickBot="1">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -16101,7 +16101,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:5" ht="15" thickBot="1">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -16119,7 +16119,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:5" ht="15" thickBot="1">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -16137,7 +16137,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:5" ht="15" thickBot="1">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -16155,7 +16155,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:5" ht="15" thickBot="1">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -16173,7 +16173,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:5" ht="15" thickBot="1">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:5" ht="15" thickBot="1">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -16209,7 +16209,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:5" ht="15" thickBot="1">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -16242,7 +16242,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:5" ht="15" thickBot="1">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -16260,7 +16260,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:5" ht="15" thickBot="1">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -16278,7 +16278,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:5" ht="15" thickBot="1">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:5" ht="15" thickBot="1">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -16314,7 +16314,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:5" ht="15" thickBot="1">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -16332,7 +16332,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:5" ht="15" thickBot="1">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -16350,7 +16350,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:5" ht="15" thickBot="1">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -16368,7 +16368,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:5" ht="15" thickBot="1">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -16386,7 +16386,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:5" ht="15" thickBot="1">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -16404,7 +16404,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:5" ht="15" thickBot="1">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:5" ht="15" thickBot="1">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -16440,7 +16440,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:5" ht="15" thickBot="1">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:5" ht="15" thickBot="1">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -16476,7 +16476,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:5" ht="15" thickBot="1">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -16494,7 +16494,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:5" ht="15" thickBot="1">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -16512,7 +16512,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:5" ht="15" thickBot="1">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -16530,7 +16530,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:5" ht="15" thickBot="1">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -16548,7 +16548,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:5" ht="15" thickBot="1">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:5" ht="15" thickBot="1">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -16584,7 +16584,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:5" ht="15" thickBot="1">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -16602,7 +16602,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:5" ht="15" thickBot="1">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -16620,7 +16620,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:5" ht="15" thickBot="1">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -16638,7 +16638,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:5" ht="15" thickBot="1">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -16656,7 +16656,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:5" ht="15" thickBot="1">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -16674,7 +16674,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:5" ht="15" thickBot="1">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -16692,7 +16692,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:5" ht="15" thickBot="1">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:5" ht="15" thickBot="1">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -16728,7 +16728,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:5" ht="15" thickBot="1">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -16746,7 +16746,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:5" ht="15" thickBot="1">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -16764,7 +16764,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:5" ht="15" thickBot="1">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -16782,7 +16782,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:5" ht="15" thickBot="1">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -16800,7 +16800,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:5" ht="15" thickBot="1">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -16818,7 +16818,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:5" ht="15" thickBot="1">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -16836,7 +16836,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:5" ht="15" thickBot="1">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -16854,7 +16854,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:5" ht="15" thickBot="1">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -16872,7 +16872,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:5" ht="15" thickBot="1">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -16890,7 +16890,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:5" ht="15" thickBot="1">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -16908,7 +16908,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:5" ht="15" thickBot="1">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -16926,7 +16926,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:5" ht="15" thickBot="1">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -16944,7 +16944,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:5" ht="15" thickBot="1">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -16962,7 +16962,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:5" ht="15" thickBot="1">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -16980,7 +16980,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:5" ht="15" thickBot="1">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -16998,7 +16998,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:5" ht="15" thickBot="1">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -17016,7 +17016,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:5" ht="15" thickBot="1">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -17034,7 +17034,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:5" ht="15" thickBot="1">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -17052,7 +17052,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:5" ht="15" thickBot="1">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -17070,7 +17070,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:5" ht="15" thickBot="1">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -17088,7 +17088,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:5" ht="15" thickBot="1">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -17106,7 +17106,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:5" ht="15" thickBot="1">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -17124,7 +17124,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:5" ht="15" thickBot="1">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -17142,7 +17142,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:5" ht="15" thickBot="1">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -17160,7 +17160,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:5" ht="15" thickBot="1">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -17178,7 +17178,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:5" ht="15" thickBot="1">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -17196,7 +17196,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:5" ht="15" thickBot="1">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -17214,7 +17214,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:5" ht="15" thickBot="1">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -17232,7 +17232,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:5" ht="15" thickBot="1">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -17250,7 +17250,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:5" ht="15" thickBot="1">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -17268,7 +17268,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:5" ht="15" thickBot="1">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -17286,7 +17286,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:5" ht="15" thickBot="1">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -17304,7 +17304,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:5" ht="15" thickBot="1">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -17322,7 +17322,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:5" ht="15" thickBot="1">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -17340,7 +17340,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:5" ht="15" thickBot="1">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -17358,7 +17358,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:5" ht="15" thickBot="1">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -17376,7 +17376,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:5" ht="15" thickBot="1">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -17409,7 +17409,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:5" ht="15" thickBot="1">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -17427,7 +17427,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:5" ht="15" thickBot="1">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -17445,7 +17445,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:5" ht="15" thickBot="1">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -17463,7 +17463,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:5" ht="15" thickBot="1">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -17481,7 +17481,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:5" ht="15" thickBot="1">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -17499,7 +17499,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:5" ht="15" thickBot="1">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -17517,7 +17517,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:5" ht="15" thickBot="1">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -17535,7 +17535,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:5" ht="15" thickBot="1">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -17553,7 +17553,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:5" ht="15" thickBot="1">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -17571,7 +17571,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:5" ht="15" thickBot="1">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -17589,7 +17589,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:5" ht="15" thickBot="1">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -17607,7 +17607,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:5" ht="15" thickBot="1">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -17625,7 +17625,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:5" ht="15" thickBot="1">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:5" ht="15" thickBot="1">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -17661,7 +17661,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:5" ht="15" thickBot="1">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -17679,7 +17679,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:5" ht="15" thickBot="1">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -17697,7 +17697,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:5" ht="15" thickBot="1">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -17715,7 +17715,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:5" ht="15" thickBot="1">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -17733,7 +17733,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:5" ht="15" thickBot="1">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -17751,7 +17751,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:5" ht="15" thickBot="1">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -17769,7 +17769,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:5" ht="15" thickBot="1">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:5" ht="15" thickBot="1">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -17805,7 +17805,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:5" ht="15" thickBot="1">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -17823,7 +17823,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:5" ht="15" thickBot="1">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -17841,7 +17841,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:5" ht="15" thickBot="1">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -17859,7 +17859,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:5" ht="15" thickBot="1">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -17877,7 +17877,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:5" ht="15" thickBot="1">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -17895,7 +17895,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:5" ht="15" thickBot="1">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -17913,7 +17913,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:5" ht="15" thickBot="1">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:5" ht="15" thickBot="1">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -17949,7 +17949,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:5" ht="15" thickBot="1">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -17967,7 +17967,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:5" ht="15" thickBot="1">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -17985,7 +17985,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:5" ht="15" thickBot="1">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -18003,7 +18003,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:5" ht="15" thickBot="1">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -18021,7 +18021,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:5" ht="15" thickBot="1">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -18039,7 +18039,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:5" ht="15" thickBot="1">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -18057,7 +18057,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:5" ht="15" thickBot="1">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -18075,7 +18075,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:5" ht="15" thickBot="1">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -18093,7 +18093,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:5" ht="15" thickBot="1">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -18111,7 +18111,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:5" ht="15" thickBot="1">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -18129,7 +18129,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:5" ht="15" thickBot="1">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -18147,7 +18147,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:5" ht="15" thickBot="1">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -18165,7 +18165,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:5" ht="15" thickBot="1">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:5" ht="15" thickBot="1">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -18201,7 +18201,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:5" ht="15" thickBot="1">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -18219,7 +18219,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:5" ht="15" thickBot="1">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -18237,7 +18237,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:5" ht="15" thickBot="1">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -18255,7 +18255,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:5" ht="15" thickBot="1">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:5" ht="15" thickBot="1">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -18291,7 +18291,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:5" ht="15" thickBot="1">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -18309,7 +18309,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:5" ht="15" thickBot="1">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -18327,7 +18327,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:5" ht="15" thickBot="1">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -18345,7 +18345,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:5" ht="15" thickBot="1">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -18363,7 +18363,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:5" ht="15" thickBot="1">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -18381,7 +18381,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:5" ht="15" thickBot="1">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -18399,7 +18399,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:5" ht="15" thickBot="1">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:5" ht="15" thickBot="1">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -18435,7 +18435,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:5" ht="15" thickBot="1">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -18453,7 +18453,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:5" ht="15" thickBot="1">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -18471,7 +18471,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:5" ht="15" thickBot="1">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -18489,7 +18489,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:5" ht="15" thickBot="1">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -18507,7 +18507,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:5" ht="15" thickBot="1">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:5" ht="15" thickBot="1">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -18543,7 +18543,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:5" ht="15" thickBot="1">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -18576,7 +18576,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:5" ht="15" thickBot="1">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -18594,7 +18594,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:5" ht="15" thickBot="1">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -18612,7 +18612,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:5" ht="15" thickBot="1">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -18630,7 +18630,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:5" ht="15" thickBot="1">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:5" ht="15" thickBot="1">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -18666,7 +18666,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:5" ht="15" thickBot="1">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -18684,7 +18684,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:5" ht="15" thickBot="1">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -18702,7 +18702,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:5" ht="15" thickBot="1">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -18720,7 +18720,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:5" ht="15" thickBot="1">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -18738,7 +18738,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:5" ht="15" thickBot="1">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -18756,7 +18756,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:5" ht="15" thickBot="1">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -18774,7 +18774,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:5" ht="15" thickBot="1">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:5" ht="15" thickBot="1">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -18810,7 +18810,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:5" ht="15" thickBot="1">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -18828,7 +18828,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:5" ht="15" thickBot="1">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -18846,7 +18846,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:5" ht="15" thickBot="1">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -18864,7 +18864,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:5" ht="15" thickBot="1">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -18882,7 +18882,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:5" ht="15" thickBot="1">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -18900,7 +18900,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:5" ht="15" thickBot="1">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -18918,7 +18918,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:5" ht="15" thickBot="1">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -18936,7 +18936,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:5" ht="15" thickBot="1">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -18954,7 +18954,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:5" ht="15" thickBot="1">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -18972,7 +18972,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:5" ht="15" thickBot="1">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -18990,7 +18990,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:5" ht="15" thickBot="1">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -19008,7 +19008,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:5" ht="15" thickBot="1">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -19026,7 +19026,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:5" ht="15" thickBot="1">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -19044,7 +19044,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:5" ht="15" thickBot="1">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -19062,7 +19062,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:5" ht="15" thickBot="1">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -19080,7 +19080,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:5" ht="15" thickBot="1">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -19098,7 +19098,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:5" ht="15" thickBot="1">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -19116,7 +19116,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:5" ht="15" thickBot="1">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -19134,7 +19134,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:5" ht="15" thickBot="1">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -19152,7 +19152,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:5" ht="15" thickBot="1">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -19170,7 +19170,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:5" ht="15" thickBot="1">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -19188,7 +19188,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:5" ht="15" thickBot="1">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -19206,7 +19206,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:5" ht="15" thickBot="1">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -19224,7 +19224,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:5" ht="15" thickBot="1">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -19242,7 +19242,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:5" ht="15" thickBot="1">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -19260,7 +19260,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:5" ht="15" thickBot="1">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -19278,7 +19278,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:5" ht="15" thickBot="1">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -19296,7 +19296,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:5" ht="15" thickBot="1">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -19314,7 +19314,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:5" ht="15" thickBot="1">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -19332,7 +19332,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:5" ht="15" thickBot="1">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:5" ht="15" thickBot="1">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -19368,7 +19368,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:5" ht="15" thickBot="1">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -19386,7 +19386,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:5" ht="15" thickBot="1">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -19404,7 +19404,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:5" ht="15" thickBot="1">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -19422,7 +19422,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:5" ht="15" thickBot="1">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -19440,7 +19440,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:5" ht="15" thickBot="1">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -19458,7 +19458,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:5" ht="15" thickBot="1">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -19476,7 +19476,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:5" ht="15" thickBot="1">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -19494,7 +19494,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:5" ht="15" thickBot="1">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:5" ht="15" thickBot="1">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -19530,7 +19530,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:5" ht="15" thickBot="1">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -19548,7 +19548,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:5" ht="15" thickBot="1">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -19566,7 +19566,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:5" ht="15" thickBot="1">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -19584,7 +19584,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:5" ht="15" thickBot="1">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -19602,7 +19602,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:5" ht="15" thickBot="1">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -19620,7 +19620,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:5" ht="15" thickBot="1">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -19638,7 +19638,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:5" ht="15" thickBot="1">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -19656,7 +19656,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:5" ht="15" thickBot="1">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:5" ht="15" thickBot="1">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:5" ht="15" thickBot="1">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -19710,7 +19710,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:5" ht="15" thickBot="1">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -19743,7 +19743,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:5" ht="15" thickBot="1">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -19761,7 +19761,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:5" ht="15" thickBot="1">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -19779,7 +19779,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:5" ht="15" thickBot="1">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -19797,7 +19797,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:5" ht="15" thickBot="1">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -19815,7 +19815,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:5" ht="15" thickBot="1">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -19833,7 +19833,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:5" ht="15" thickBot="1">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -19851,7 +19851,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:5" ht="15" thickBot="1">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -19869,7 +19869,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:5" ht="15" thickBot="1">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -19887,7 +19887,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:5" ht="15" thickBot="1">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -19905,7 +19905,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:5" ht="15" thickBot="1">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -19923,7 +19923,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:5" ht="15" thickBot="1">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -19941,7 +19941,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:5" ht="15" thickBot="1">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -19959,7 +19959,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:5" ht="15" thickBot="1">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -19977,7 +19977,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:5" ht="15" thickBot="1">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -19995,7 +19995,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:5" ht="15" thickBot="1">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -20013,7 +20013,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:5" ht="15" thickBot="1">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -20031,7 +20031,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:5" ht="15" thickBot="1">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -20049,7 +20049,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:5" ht="15" thickBot="1">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -20067,7 +20067,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:5" ht="15" thickBot="1">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -20085,7 +20085,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:5" ht="15" thickBot="1">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -20103,7 +20103,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:5" ht="15" thickBot="1">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:5" ht="15" thickBot="1">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -20139,7 +20139,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:5" ht="15" thickBot="1">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -20157,7 +20157,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:5" ht="15" thickBot="1">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -20175,7 +20175,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:5" ht="15" thickBot="1">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -20193,7 +20193,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:5" ht="15" thickBot="1">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -20211,7 +20211,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:5" ht="15" thickBot="1">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -20229,7 +20229,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:5" ht="15" thickBot="1">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -20247,7 +20247,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:5" ht="15" thickBot="1">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -20265,7 +20265,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:5" ht="15" thickBot="1">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -20283,7 +20283,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:5" ht="15" thickBot="1">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -20301,7 +20301,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:5" ht="15" thickBot="1">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -20319,7 +20319,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:5" ht="15" thickBot="1">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -20337,7 +20337,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:5" ht="15" thickBot="1">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -20355,7 +20355,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:5" ht="15" thickBot="1">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -20373,7 +20373,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:5" ht="15" thickBot="1">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -20391,7 +20391,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:5" ht="15" thickBot="1">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -20409,7 +20409,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:5" ht="15" thickBot="1">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -20427,7 +20427,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:5" ht="15" thickBot="1">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -20445,7 +20445,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:5" ht="15" thickBot="1">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -20463,7 +20463,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:5" ht="15" thickBot="1">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -20481,7 +20481,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:5" ht="15" thickBot="1">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -20499,7 +20499,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:5" ht="15" thickBot="1">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -20517,7 +20517,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:5" ht="15" thickBot="1">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -20535,7 +20535,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:5" ht="15" thickBot="1">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -20553,7 +20553,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:5" ht="15" thickBot="1">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -20571,7 +20571,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:5" ht="15" thickBot="1">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -20589,7 +20589,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:5" ht="15" thickBot="1">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -20607,7 +20607,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:5" ht="15" thickBot="1">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -20625,7 +20625,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:5" ht="15" thickBot="1">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -20643,7 +20643,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:5" ht="15" thickBot="1">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -20661,7 +20661,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:5" ht="15" thickBot="1">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -20679,7 +20679,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:5" ht="15" thickBot="1">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -20697,7 +20697,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:5" ht="15" thickBot="1">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -20715,7 +20715,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:5" ht="15" thickBot="1">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -20733,7 +20733,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:5" ht="15" thickBot="1">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -20751,7 +20751,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:5" ht="15" thickBot="1">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -20769,7 +20769,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:5" ht="15" thickBot="1">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -20787,7 +20787,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:5" ht="15" thickBot="1">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -20805,7 +20805,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:5" ht="15" thickBot="1">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -20823,7 +20823,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:5" ht="15" thickBot="1">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -20841,7 +20841,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:5" ht="15" thickBot="1">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -20859,7 +20859,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:5" ht="15" thickBot="1">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -20877,7 +20877,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:5" ht="15" thickBot="1">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -20910,7 +20910,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:5" ht="15" thickBot="1">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -20928,7 +20928,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:5" ht="15" thickBot="1">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -20946,7 +20946,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:5" ht="15" thickBot="1">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -20964,7 +20964,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:5" ht="15" thickBot="1">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -20982,7 +20982,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:5" ht="15" thickBot="1">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -21000,7 +21000,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:5" ht="15" thickBot="1">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -21018,7 +21018,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:5" ht="15" thickBot="1">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -21036,7 +21036,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:5" ht="15" thickBot="1">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -21054,7 +21054,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:5" ht="15" thickBot="1">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -21072,7 +21072,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:5" ht="15" thickBot="1">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -21090,7 +21090,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:5" ht="15" thickBot="1">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -21108,7 +21108,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="782" spans="1:5" ht="15" thickBot="1">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -21126,7 +21126,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="783" spans="1:5" ht="15" thickBot="1">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -21144,7 +21144,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="784" spans="1:5" ht="15" thickBot="1">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -21162,7 +21162,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="785" spans="1:5" ht="15" thickBot="1">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -21180,7 +21180,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="786" spans="1:5" ht="15" thickBot="1">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -21198,7 +21198,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="787" spans="1:5" ht="15" thickBot="1">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -21216,7 +21216,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="788" spans="1:5" ht="15" thickBot="1">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -21234,7 +21234,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="789" spans="1:5" ht="15" thickBot="1">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -21252,7 +21252,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="790" spans="1:5" ht="15" thickBot="1">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -21270,7 +21270,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="791" spans="1:5" ht="15" thickBot="1">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -21288,7 +21288,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="792" spans="1:5" ht="15" thickBot="1">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -21306,7 +21306,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="793" spans="1:5" ht="15" thickBot="1">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -21324,7 +21324,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="794" spans="1:5" ht="15" thickBot="1">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -21342,7 +21342,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="795" spans="1:5" ht="15" thickBot="1">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -21360,7 +21360,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="796" spans="1:5" ht="15" thickBot="1">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -21378,7 +21378,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="797" spans="1:5" ht="15" thickBot="1">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -21396,7 +21396,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="798" spans="1:5" ht="15" thickBot="1">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -21414,7 +21414,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="799" spans="1:5" ht="15" thickBot="1">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -21432,7 +21432,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="800" spans="1:5" ht="15" thickBot="1">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -21450,7 +21450,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="801" spans="1:5" ht="15" thickBot="1">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -21468,7 +21468,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="802" spans="1:5" ht="15" thickBot="1">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -21486,7 +21486,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="803" spans="1:5" ht="15" thickBot="1">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -21504,7 +21504,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="804" spans="1:5" ht="15" thickBot="1">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -21522,7 +21522,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="805" spans="1:5" ht="15" thickBot="1">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -21540,7 +21540,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="806" spans="1:5" ht="15" thickBot="1">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -21558,7 +21558,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="807" spans="1:5" ht="15" thickBot="1">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -21576,7 +21576,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="808" spans="1:5" ht="15" thickBot="1">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -21594,7 +21594,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="809" spans="1:5" ht="15" thickBot="1">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -21612,7 +21612,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="810" spans="1:5" ht="15" thickBot="1">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -21630,7 +21630,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="811" spans="1:5" ht="15" thickBot="1">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -21648,7 +21648,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="812" spans="1:5" ht="15" thickBot="1">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -21666,7 +21666,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="813" spans="1:5" ht="15" thickBot="1">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -21684,7 +21684,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="814" spans="1:5" ht="15" thickBot="1">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -21702,7 +21702,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="815" spans="1:5" ht="15" thickBot="1">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -21720,7 +21720,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="816" spans="1:5" ht="15" thickBot="1">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -21738,7 +21738,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="817" spans="1:5" ht="15" thickBot="1">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -21756,7 +21756,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="818" spans="1:5" ht="15" thickBot="1">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -21774,7 +21774,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="819" spans="1:5" ht="15" thickBot="1">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -21792,7 +21792,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="820" spans="1:5" ht="15" thickBot="1">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -21810,7 +21810,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="821" spans="1:5" ht="15" thickBot="1">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -21828,7 +21828,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="822" spans="1:5" ht="15" thickBot="1">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -21846,7 +21846,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="823" spans="1:5" ht="15" thickBot="1">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -21864,7 +21864,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="824" spans="1:5" ht="15" thickBot="1">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -21882,7 +21882,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="825" spans="1:5" ht="15" thickBot="1">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -21900,7 +21900,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="826" spans="1:5" ht="15" thickBot="1">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -21918,7 +21918,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="827" spans="1:5" ht="15" thickBot="1">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -21936,7 +21936,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="828" spans="1:5" ht="15" thickBot="1">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -21954,7 +21954,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="829" spans="1:5" ht="15" thickBot="1">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -21972,7 +21972,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="830" spans="1:5" ht="15" thickBot="1">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -21990,7 +21990,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="831" spans="1:5" ht="15" thickBot="1">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -22008,7 +22008,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="832" spans="1:5" ht="15" thickBot="1">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -22026,7 +22026,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="833" spans="1:5" ht="15" thickBot="1">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -22044,7 +22044,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="834" spans="1:5" ht="15" thickBot="1">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -22077,7 +22077,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="835" spans="1:5" ht="15" thickBot="1">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -22095,7 +22095,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="836" spans="1:5" ht="15" thickBot="1">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -22113,7 +22113,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="837" spans="1:5" ht="15" thickBot="1">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -22131,7 +22131,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="838" spans="1:5" ht="15" thickBot="1">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -22149,7 +22149,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="839" spans="1:5" ht="15" thickBot="1">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -22167,7 +22167,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="840" spans="1:5" ht="15" thickBot="1">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -22185,7 +22185,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="841" spans="1:5" ht="15" thickBot="1">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -22203,7 +22203,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="842" spans="1:5" ht="15" thickBot="1">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -22221,7 +22221,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="843" spans="1:5" ht="15" thickBot="1">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -22239,7 +22239,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="844" spans="1:5" ht="15" thickBot="1">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -22257,7 +22257,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="845" spans="1:5" ht="15" thickBot="1">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -22275,7 +22275,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="846" spans="1:5" ht="15" thickBot="1">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -22293,7 +22293,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="847" spans="1:5" ht="15" thickBot="1">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -22311,7 +22311,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="848" spans="1:5" ht="15" thickBot="1">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -22329,7 +22329,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="849" spans="1:5" ht="15" thickBot="1">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -22347,7 +22347,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="850" spans="1:5" ht="15" thickBot="1">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -22365,7 +22365,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="851" spans="1:5" ht="15" thickBot="1">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -22383,7 +22383,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="852" spans="1:5" ht="15" thickBot="1">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -22401,7 +22401,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="853" spans="1:5" ht="15" thickBot="1">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -22419,7 +22419,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="854" spans="1:5" ht="15" thickBot="1">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -22437,7 +22437,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="855" spans="1:5" ht="15" thickBot="1">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -22455,7 +22455,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="856" spans="1:5" ht="15" thickBot="1">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -22473,7 +22473,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="857" spans="1:5" ht="15" thickBot="1">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -22491,7 +22491,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="858" spans="1:5" ht="15" thickBot="1">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -22509,7 +22509,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="859" spans="1:5" ht="15" thickBot="1">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -22527,7 +22527,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="860" spans="1:5" ht="15" thickBot="1">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -22545,7 +22545,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="861" spans="1:5" ht="15" thickBot="1">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -22563,7 +22563,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="862" spans="1:5" ht="15" thickBot="1">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -22581,7 +22581,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="863" spans="1:5" ht="15" thickBot="1">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -22599,7 +22599,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="864" spans="1:5" ht="15" thickBot="1">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -22617,7 +22617,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="865" spans="1:5" ht="15" thickBot="1">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -22635,7 +22635,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="866" spans="1:5" ht="15" thickBot="1">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -22653,7 +22653,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="867" spans="1:5" ht="15" thickBot="1">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -22671,7 +22671,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="868" spans="1:5" ht="15" thickBot="1">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -22689,7 +22689,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="869" spans="1:5" ht="15" thickBot="1">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -22707,7 +22707,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="870" spans="1:5" ht="15" thickBot="1">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -22725,7 +22725,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="871" spans="1:5" ht="15" thickBot="1">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -22743,7 +22743,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="872" spans="1:5" ht="15" thickBot="1">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -22761,7 +22761,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="873" spans="1:5" ht="15" thickBot="1">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -22779,7 +22779,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="874" spans="1:5" ht="15" thickBot="1">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -22797,7 +22797,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="875" spans="1:5" ht="15" thickBot="1">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -22815,7 +22815,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="876" spans="1:5" ht="15" thickBot="1">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -22833,7 +22833,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="877" spans="1:5" ht="15" thickBot="1">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -22851,7 +22851,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="878" spans="1:5" ht="15" thickBot="1">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -22884,7 +22884,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="879" spans="1:5" ht="15" thickBot="1">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -22917,7 +22917,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="880" spans="1:5" ht="15" thickBot="1">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -22950,7 +22950,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="881" spans="1:5" ht="15" thickBot="1">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -22968,7 +22968,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="882" spans="1:5" ht="15" thickBot="1">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -23001,7 +23001,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="883" spans="1:5" ht="15" thickBot="1">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -23034,7 +23034,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="884" spans="1:5" ht="15" thickBot="1">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
@@ -23052,7 +23052,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="885" spans="1:5" ht="15" thickBot="1">
       <c r="A885" s="15">
         <v>46088</v>
       </c>
@@ -23070,7 +23070,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:5">
       <c r="A886" s="8">
         <v>46102</v>
       </c>
@@ -23088,7 +23088,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:5">
       <c r="A887" s="8">
         <v>46109</v>
       </c>
@@ -23106,7 +23106,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:5">
       <c r="A888" s="8">
         <v>46116</v>
       </c>
@@ -23124,7 +23124,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:5">
       <c r="A889" s="8">
         <v>46123</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>500040</v>
       </c>
     </row>
-    <row r="890" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:5">
       <c r="A890" s="8">
         <v>46130</v>
       </c>
@@ -23160,7 +23160,7 @@
         <v>508303</v>
       </c>
     </row>
-    <row r="891" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:5">
       <c r="A891" s="8">
         <v>46137</v>
       </c>
@@ -23178,7 +23178,7 @@
         <v>511616</v>
       </c>
     </row>
-    <row r="892" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:5">
       <c r="A892" s="8">
         <v>46144</v>
       </c>
@@ -23196,7 +23196,7 @@
         <v>518773</v>
       </c>
     </row>
-    <row r="893" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:5">
       <c r="A893" s="8">
         <v>46151</v>
       </c>
@@ -23229,7 +23229,7 @@
         <v>513755</v>
       </c>
     </row>
-    <row r="894" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:5">
       <c r="A894" s="8">
         <v>46158</v>
       </c>
@@ -23247,7 +23247,7 @@
         <v>511216</v>
       </c>
     </row>
-    <row r="895" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:5">
       <c r="A895" s="8">
         <v>46165</v>
       </c>
@@ -23265,7 +23265,7 @@
         <v>523574</v>
       </c>
     </row>
-    <row r="896" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:5">
       <c r="A896" s="8">
         <v>46172</v>
       </c>
@@ -23298,7 +23298,7 @@
         <v>492795</v>
       </c>
     </row>
-    <row r="897" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:5">
       <c r="A897" s="8">
         <v>46179</v>
       </c>
@@ -23316,7 +23316,7 @@
         <v>521804</v>
       </c>
     </row>
-    <row r="898" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:5">
       <c r="A898" s="8">
         <v>46186</v>
       </c>
@@ -23334,7 +23334,7 @@
         <v>520406</v>
       </c>
     </row>
-    <row r="899" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:5">
       <c r="A899" s="8">
         <v>46193</v>
       </c>
@@ -23367,7 +23367,7 @@
         <v>521998</v>
       </c>
     </row>
-    <row r="900" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:5">
       <c r="A900" s="8">
         <v>46200</v>
       </c>
@@ -23385,7 +23385,7 @@
         <v>525474</v>
       </c>
     </row>
-    <row r="901" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:5">
       <c r="A901" s="8">
         <v>46207</v>
       </c>
@@ -23396,7 +23396,7 @@
         <v>0.50138888888888888</v>
       </c>
       <c r="D901" s="7" t="str">
-        <f t="shared" ref="D901" si="19">IF(
+        <f t="shared" ref="D901:D902" si="19">IF(
  AND(
   A901 &gt;= IF(
          YEAR(A901)&gt;=2007,
@@ -23418,6 +23418,21 @@
         <v>482121</v>
       </c>
     </row>
+    <row r="902" spans="1:5">
+      <c r="A902" s="8">
+        <v>46214</v>
+      </c>
+      <c r="B902" s="8">
+        <v>46218</v>
+      </c>
+      <c r="C902" s="21">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="D902" s="7" t="str">
+        <f t="shared" si="19"/>
+        <v>UTC-4</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">
     <sortCondition ref="B2:B876"/>
@@ -23431,7 +23446,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="16"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23442,12 +23457,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23455,7 +23470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23463,7 +23478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7724D715-6013-4504-B7F3-62A78DD5C3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98CAEB5-3AC0-4422-82BC-43021C4D79E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" activeTab="1" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -23426,11 +23426,14 @@
         <v>46218</v>
       </c>
       <c r="C902" s="21">
-        <v>0.50138888888888888</v>
+        <v>0.50069444444444444</v>
       </c>
       <c r="D902" s="7" t="str">
         <f t="shared" si="19"/>
         <v>UTC-4</v>
+      </c>
+      <c r="E902" s="20">
+        <v>503525</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98CAEB5-3AC0-4422-82BC-43021C4D79E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7676CC-CE1C-3E4C-846C-9AA01D55E504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" activeTab="1" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="11440" yWindow="600" windowWidth="11700" windowHeight="14740" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -6831,14 +6831,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
   <dimension ref="A1:E902"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.453125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.54296875" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.08984375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.08984375" style="6"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6858,7 +6858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="16">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="16">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" ht="16">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="16">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" ht="16">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="16">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="16">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" ht="16">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" ht="16">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" ht="16">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" ht="16">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" ht="16">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" ht="16">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -7122,7 +7122,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" ht="16">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="16">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" ht="16">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" ht="16">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" ht="16">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="16">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" ht="16">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" ht="16">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" ht="16">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="16">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" ht="16">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" ht="16">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" ht="16">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" ht="16">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="16">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" ht="16">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" ht="16">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" ht="16">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" ht="16">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" ht="16">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="16">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" ht="16">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" ht="16">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="16">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" ht="16">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" ht="16">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" ht="16">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" ht="16">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" ht="16">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -7644,7 +7644,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="16">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" ht="16">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" ht="16">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" ht="16">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" ht="16">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" ht="16">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" ht="16">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" ht="16">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="16">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" ht="16">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="16">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="16">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -7860,7 +7860,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" ht="16">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="16">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -7896,7 +7896,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="16">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" ht="16">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" ht="16">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" ht="16">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" ht="16">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="16">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" ht="16">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="16">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -8040,7 +8040,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" ht="16">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="16">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="16">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" ht="16">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -8127,7 +8127,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" ht="16">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" ht="16">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" ht="16">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -8181,7 +8181,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" ht="16">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="16">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" ht="16">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" ht="16">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" ht="16">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -8271,7 +8271,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" ht="16">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" ht="16">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" ht="16">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" ht="16">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" ht="16">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="16">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" ht="16">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -8397,7 +8397,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" ht="16">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" ht="16">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" ht="16">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" ht="16">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" ht="16">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" ht="16">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" ht="16">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" ht="16">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -8541,7 +8541,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" ht="16">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -8559,7 +8559,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="16">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" ht="16">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" ht="16">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" ht="16">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" ht="16">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" ht="16">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="16">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" thickBot="1">
+    <row r="101" spans="1:5" ht="17" thickBot="1">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1">
+    <row r="102" spans="1:5" ht="17" thickBot="1">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1">
+    <row r="103" spans="1:5" ht="17" thickBot="1">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1">
+    <row r="104" spans="1:5" ht="17" thickBot="1">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1">
+    <row r="105" spans="1:5" ht="17" thickBot="1">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15" thickBot="1">
+    <row r="106" spans="1:5" ht="17" thickBot="1">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15" thickBot="1">
+    <row r="107" spans="1:5" ht="17" thickBot="1">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15" thickBot="1">
+    <row r="108" spans="1:5" ht="17" thickBot="1">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -8829,7 +8829,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="15" thickBot="1">
+    <row r="109" spans="1:5" ht="17" thickBot="1">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15" thickBot="1">
+    <row r="110" spans="1:5" ht="17" thickBot="1">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="15" thickBot="1">
+    <row r="111" spans="1:5" ht="17" thickBot="1">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="15" thickBot="1">
+    <row r="112" spans="1:5" ht="17" thickBot="1">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="15" thickBot="1">
+    <row r="113" spans="1:5" ht="17" thickBot="1">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -8919,7 +8919,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="15" thickBot="1">
+    <row r="114" spans="1:5" ht="17" thickBot="1">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -8937,7 +8937,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="15" thickBot="1">
+    <row r="115" spans="1:5" ht="17" thickBot="1">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="15" thickBot="1">
+    <row r="116" spans="1:5" ht="17" thickBot="1">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="15" thickBot="1">
+    <row r="117" spans="1:5" ht="17" thickBot="1">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="15" thickBot="1">
+    <row r="118" spans="1:5" ht="17" thickBot="1">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="15" thickBot="1">
+    <row r="119" spans="1:5" ht="17" thickBot="1">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="15" thickBot="1">
+    <row r="120" spans="1:5" ht="17" thickBot="1">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="15" thickBot="1">
+    <row r="121" spans="1:5" ht="17" thickBot="1">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="15" thickBot="1">
+    <row r="122" spans="1:5" ht="17" thickBot="1">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15" thickBot="1">
+    <row r="123" spans="1:5" ht="17" thickBot="1">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="15" thickBot="1">
+    <row r="124" spans="1:5" ht="17" thickBot="1">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -9117,7 +9117,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="15" thickBot="1">
+    <row r="125" spans="1:5" ht="17" thickBot="1">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="15" thickBot="1">
+    <row r="126" spans="1:5" ht="17" thickBot="1">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="15" thickBot="1">
+    <row r="127" spans="1:5" ht="17" thickBot="1">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15" thickBot="1">
+    <row r="128" spans="1:5" ht="17" thickBot="1">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -9189,7 +9189,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="15" thickBot="1">
+    <row r="129" spans="1:5" ht="17" thickBot="1">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -9207,7 +9207,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="15" thickBot="1">
+    <row r="130" spans="1:5" ht="17" thickBot="1">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="15" thickBot="1">
+    <row r="131" spans="1:5" ht="17" thickBot="1">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="15" thickBot="1">
+    <row r="132" spans="1:5" ht="17" thickBot="1">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="15" thickBot="1">
+    <row r="133" spans="1:5" ht="17" thickBot="1">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="15" thickBot="1">
+    <row r="134" spans="1:5" ht="17" thickBot="1">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="15" thickBot="1">
+    <row r="135" spans="1:5" ht="17" thickBot="1">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="15" thickBot="1">
+    <row r="136" spans="1:5" ht="17" thickBot="1">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="15" thickBot="1">
+    <row r="137" spans="1:5" ht="17" thickBot="1">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="15" thickBot="1">
+    <row r="138" spans="1:5" ht="17" thickBot="1">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="15" thickBot="1">
+    <row r="139" spans="1:5" ht="17" thickBot="1">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="15" thickBot="1">
+    <row r="140" spans="1:5" ht="17" thickBot="1">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15" thickBot="1">
+    <row r="141" spans="1:5" ht="17" thickBot="1">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="15" thickBot="1">
+    <row r="142" spans="1:5" ht="17" thickBot="1">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -9456,7 +9456,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15" thickBot="1">
+    <row r="143" spans="1:5" ht="17" thickBot="1">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="15" thickBot="1">
+    <row r="144" spans="1:5" ht="17" thickBot="1">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="15" thickBot="1">
+    <row r="145" spans="1:5" ht="17" thickBot="1">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="15" thickBot="1">
+    <row r="146" spans="1:5" ht="17" thickBot="1">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="15" thickBot="1">
+    <row r="147" spans="1:5" ht="17" thickBot="1">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="15" thickBot="1">
+    <row r="148" spans="1:5" ht="17" thickBot="1">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="15" thickBot="1">
+    <row r="149" spans="1:5" ht="17" thickBot="1">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -9582,7 +9582,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="15" thickBot="1">
+    <row r="150" spans="1:5" ht="17" thickBot="1">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="15" thickBot="1">
+    <row r="151" spans="1:5" ht="17" thickBot="1">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="15" thickBot="1">
+    <row r="152" spans="1:5" ht="17" thickBot="1">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="15" thickBot="1">
+    <row r="153" spans="1:5" ht="17" thickBot="1">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="15" thickBot="1">
+    <row r="154" spans="1:5" ht="17" thickBot="1">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="15" thickBot="1">
+    <row r="155" spans="1:5" ht="17" thickBot="1">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="15" thickBot="1">
+    <row r="156" spans="1:5" ht="17" thickBot="1">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -9708,7 +9708,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="15" thickBot="1">
+    <row r="157" spans="1:5" ht="17" thickBot="1">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -9726,7 +9726,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="15" thickBot="1">
+    <row r="158" spans="1:5" ht="17" thickBot="1">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="15" thickBot="1">
+    <row r="159" spans="1:5" ht="17" thickBot="1">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -9762,7 +9762,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="15" thickBot="1">
+    <row r="160" spans="1:5" ht="17" thickBot="1">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="15" thickBot="1">
+    <row r="161" spans="1:5" ht="17" thickBot="1">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="15" thickBot="1">
+    <row r="162" spans="1:5" ht="17" thickBot="1">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="15" thickBot="1">
+    <row r="163" spans="1:5" ht="17" thickBot="1">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="15" thickBot="1">
+    <row r="164" spans="1:5" ht="17" thickBot="1">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15" thickBot="1">
+    <row r="165" spans="1:5" ht="17" thickBot="1">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="15" thickBot="1">
+    <row r="166" spans="1:5" ht="17" thickBot="1">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="15" thickBot="1">
+    <row r="167" spans="1:5" ht="17" thickBot="1">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="15" thickBot="1">
+    <row r="168" spans="1:5" ht="17" thickBot="1">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="15" thickBot="1">
+    <row r="169" spans="1:5" ht="17" thickBot="1">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="15" thickBot="1">
+    <row r="170" spans="1:5" ht="17" thickBot="1">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -9960,7 +9960,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="15" thickBot="1">
+    <row r="171" spans="1:5" ht="17" thickBot="1">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -9978,7 +9978,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="15" thickBot="1">
+    <row r="172" spans="1:5" ht="17" thickBot="1">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -9996,7 +9996,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15" thickBot="1">
+    <row r="173" spans="1:5" ht="17" thickBot="1">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="15" thickBot="1">
+    <row r="174" spans="1:5" ht="17" thickBot="1">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -10032,7 +10032,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="15" thickBot="1">
+    <row r="175" spans="1:5" ht="17" thickBot="1">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="15" thickBot="1">
+    <row r="176" spans="1:5" ht="17" thickBot="1">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="15" thickBot="1">
+    <row r="177" spans="1:5" ht="17" thickBot="1">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="15" thickBot="1">
+    <row r="178" spans="1:5" ht="17" thickBot="1">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="15" thickBot="1">
+    <row r="179" spans="1:5" ht="17" thickBot="1">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15" thickBot="1">
+    <row r="180" spans="1:5" ht="17" thickBot="1">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -10140,7 +10140,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="15" thickBot="1">
+    <row r="181" spans="1:5" ht="17" thickBot="1">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15" thickBot="1">
+    <row r="182" spans="1:5" ht="17" thickBot="1">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -10176,7 +10176,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="15" thickBot="1">
+    <row r="183" spans="1:5" ht="17" thickBot="1">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="15" thickBot="1">
+    <row r="184" spans="1:5" ht="17" thickBot="1">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -10212,7 +10212,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="15" thickBot="1">
+    <row r="185" spans="1:5" ht="17" thickBot="1">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="15" thickBot="1">
+    <row r="186" spans="1:5" ht="17" thickBot="1">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -10248,7 +10248,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="15" thickBot="1">
+    <row r="187" spans="1:5" ht="17" thickBot="1">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="15" thickBot="1">
+    <row r="188" spans="1:5" ht="17" thickBot="1">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="15" thickBot="1">
+    <row r="189" spans="1:5" ht="17" thickBot="1">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="15" thickBot="1">
+    <row r="190" spans="1:5" ht="17" thickBot="1">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -10320,7 +10320,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="15" thickBot="1">
+    <row r="191" spans="1:5" ht="17" thickBot="1">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -10338,7 +10338,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="15" thickBot="1">
+    <row r="192" spans="1:5" ht="17" thickBot="1">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -10356,7 +10356,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="15" thickBot="1">
+    <row r="193" spans="1:5" ht="17" thickBot="1">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="15" thickBot="1">
+    <row r="194" spans="1:5" ht="17" thickBot="1">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="15" thickBot="1">
+    <row r="195" spans="1:5" ht="17" thickBot="1">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="15" thickBot="1">
+    <row r="196" spans="1:5" ht="17" thickBot="1">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -10443,7 +10443,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="15" thickBot="1">
+    <row r="197" spans="1:5" ht="17" thickBot="1">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -10461,7 +10461,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="15" thickBot="1">
+    <row r="198" spans="1:5" ht="17" thickBot="1">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="15" thickBot="1">
+    <row r="199" spans="1:5" ht="17" thickBot="1">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -10497,7 +10497,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="15" thickBot="1">
+    <row r="200" spans="1:5" ht="17" thickBot="1">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -10515,7 +10515,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="15" thickBot="1">
+    <row r="201" spans="1:5" ht="17" thickBot="1">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="15" thickBot="1">
+    <row r="202" spans="1:5" ht="17" thickBot="1">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="15" thickBot="1">
+    <row r="203" spans="1:5" ht="17" thickBot="1">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -10569,7 +10569,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="15" thickBot="1">
+    <row r="204" spans="1:5" ht="17" thickBot="1">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -10587,7 +10587,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="15" thickBot="1">
+    <row r="205" spans="1:5" ht="17" thickBot="1">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="15" thickBot="1">
+    <row r="206" spans="1:5" ht="17" thickBot="1">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="15" thickBot="1">
+    <row r="207" spans="1:5" ht="17" thickBot="1">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -10641,7 +10641,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="15" thickBot="1">
+    <row r="208" spans="1:5" ht="17" thickBot="1">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -10659,7 +10659,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="15" thickBot="1">
+    <row r="209" spans="1:5" ht="17" thickBot="1">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -10677,7 +10677,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="15" thickBot="1">
+    <row r="210" spans="1:5" ht="17" thickBot="1">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="15" thickBot="1">
+    <row r="211" spans="1:5" ht="17" thickBot="1">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="15" thickBot="1">
+    <row r="212" spans="1:5" ht="17" thickBot="1">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -10731,7 +10731,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="15" thickBot="1">
+    <row r="213" spans="1:5" ht="17" thickBot="1">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="15" thickBot="1">
+    <row r="214" spans="1:5" ht="17" thickBot="1">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -10767,7 +10767,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="15" thickBot="1">
+    <row r="215" spans="1:5" ht="17" thickBot="1">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="15" thickBot="1">
+    <row r="216" spans="1:5" ht="17" thickBot="1">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="15" thickBot="1">
+    <row r="217" spans="1:5" ht="17" thickBot="1">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="15" thickBot="1">
+    <row r="218" spans="1:5" ht="17" thickBot="1">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -10839,7 +10839,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="15" thickBot="1">
+    <row r="219" spans="1:5" ht="17" thickBot="1">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="15" thickBot="1">
+    <row r="220" spans="1:5" ht="17" thickBot="1">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="15" thickBot="1">
+    <row r="221" spans="1:5" ht="17" thickBot="1">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="15" thickBot="1">
+    <row r="222" spans="1:5" ht="17" thickBot="1">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="15" thickBot="1">
+    <row r="223" spans="1:5" ht="17" thickBot="1">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -10929,7 +10929,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="15" thickBot="1">
+    <row r="224" spans="1:5" ht="17" thickBot="1">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="15" thickBot="1">
+    <row r="225" spans="1:5" ht="17" thickBot="1">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="15" thickBot="1">
+    <row r="226" spans="1:5" ht="17" thickBot="1">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -10983,7 +10983,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="15" thickBot="1">
+    <row r="227" spans="1:5" ht="17" thickBot="1">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -11001,7 +11001,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="15" thickBot="1">
+    <row r="228" spans="1:5" ht="17" thickBot="1">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="15" thickBot="1">
+    <row r="229" spans="1:5" ht="17" thickBot="1">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="15" thickBot="1">
+    <row r="230" spans="1:5" ht="17" thickBot="1">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -11055,7 +11055,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="15" thickBot="1">
+    <row r="231" spans="1:5" ht="17" thickBot="1">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="15" thickBot="1">
+    <row r="232" spans="1:5" ht="17" thickBot="1">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -11091,7 +11091,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="15" thickBot="1">
+    <row r="233" spans="1:5" ht="17" thickBot="1">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -11109,7 +11109,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="15" thickBot="1">
+    <row r="234" spans="1:5" ht="17" thickBot="1">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="15" thickBot="1">
+    <row r="235" spans="1:5" ht="17" thickBot="1">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="15" thickBot="1">
+    <row r="236" spans="1:5" ht="17" thickBot="1">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -11163,7 +11163,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="15" thickBot="1">
+    <row r="237" spans="1:5" ht="17" thickBot="1">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -11181,7 +11181,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="15" thickBot="1">
+    <row r="238" spans="1:5" ht="17" thickBot="1">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -11199,7 +11199,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="15" thickBot="1">
+    <row r="239" spans="1:5" ht="17" thickBot="1">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="15" thickBot="1">
+    <row r="240" spans="1:5" ht="17" thickBot="1">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -11235,7 +11235,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="15" thickBot="1">
+    <row r="241" spans="1:5" ht="17" thickBot="1">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="15" thickBot="1">
+    <row r="242" spans="1:5" ht="17" thickBot="1">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -11271,7 +11271,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="15" thickBot="1">
+    <row r="243" spans="1:5" ht="17" thickBot="1">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="15" thickBot="1">
+    <row r="244" spans="1:5" ht="17" thickBot="1">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -11307,7 +11307,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="15" thickBot="1">
+    <row r="245" spans="1:5" ht="17" thickBot="1">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="15" thickBot="1">
+    <row r="246" spans="1:5" ht="17" thickBot="1">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -11343,7 +11343,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="15" thickBot="1">
+    <row r="247" spans="1:5" ht="17" thickBot="1">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -11361,7 +11361,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="15" thickBot="1">
+    <row r="248" spans="1:5" ht="17" thickBot="1">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -11379,7 +11379,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="15" thickBot="1">
+    <row r="249" spans="1:5" ht="17" thickBot="1">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -11397,7 +11397,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="15" thickBot="1">
+    <row r="250" spans="1:5" ht="17" thickBot="1">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -11415,7 +11415,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="15" thickBot="1">
+    <row r="251" spans="1:5" ht="17" thickBot="1">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="15" thickBot="1">
+    <row r="252" spans="1:5" ht="17" thickBot="1">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -11451,7 +11451,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="15" thickBot="1">
+    <row r="253" spans="1:5" ht="17" thickBot="1">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -11469,7 +11469,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="15" thickBot="1">
+    <row r="254" spans="1:5" ht="17" thickBot="1">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="15" thickBot="1">
+    <row r="255" spans="1:5" ht="17" thickBot="1">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -11505,7 +11505,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="15" thickBot="1">
+    <row r="256" spans="1:5" ht="17" thickBot="1">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -11523,7 +11523,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="15" thickBot="1">
+    <row r="257" spans="1:5" ht="17" thickBot="1">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="15" thickBot="1">
+    <row r="258" spans="1:5" ht="17" thickBot="1">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -11574,7 +11574,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="15" thickBot="1">
+    <row r="259" spans="1:5" ht="17" thickBot="1">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="15" thickBot="1">
+    <row r="260" spans="1:5" ht="17" thickBot="1">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -11610,7 +11610,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="15" thickBot="1">
+    <row r="261" spans="1:5" ht="17" thickBot="1">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="15" thickBot="1">
+    <row r="262" spans="1:5" ht="17" thickBot="1">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -11646,7 +11646,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="15" thickBot="1">
+    <row r="263" spans="1:5" ht="17" thickBot="1">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="15" thickBot="1">
+    <row r="264" spans="1:5" ht="17" thickBot="1">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="15" thickBot="1">
+    <row r="265" spans="1:5" ht="17" thickBot="1">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -11700,7 +11700,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="15" thickBot="1">
+    <row r="266" spans="1:5" ht="17" thickBot="1">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="15" thickBot="1">
+    <row r="267" spans="1:5" ht="17" thickBot="1">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -11736,7 +11736,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="15" thickBot="1">
+    <row r="268" spans="1:5" ht="17" thickBot="1">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="15" thickBot="1">
+    <row r="269" spans="1:5" ht="17" thickBot="1">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -11772,7 +11772,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="15" thickBot="1">
+    <row r="270" spans="1:5" ht="17" thickBot="1">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -11790,7 +11790,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="15" thickBot="1">
+    <row r="271" spans="1:5" ht="17" thickBot="1">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -11808,7 +11808,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="15" thickBot="1">
+    <row r="272" spans="1:5" ht="17" thickBot="1">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -11826,7 +11826,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="15" thickBot="1">
+    <row r="273" spans="1:5" ht="17" thickBot="1">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -11844,7 +11844,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="15" thickBot="1">
+    <row r="274" spans="1:5" ht="17" thickBot="1">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="15" thickBot="1">
+    <row r="275" spans="1:5" ht="17" thickBot="1">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="15" thickBot="1">
+    <row r="276" spans="1:5" ht="17" thickBot="1">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="15" thickBot="1">
+    <row r="277" spans="1:5" ht="17" thickBot="1">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="15" thickBot="1">
+    <row r="278" spans="1:5" ht="17" thickBot="1">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -11934,7 +11934,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="15" thickBot="1">
+    <row r="279" spans="1:5" ht="17" thickBot="1">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="15" thickBot="1">
+    <row r="280" spans="1:5" ht="17" thickBot="1">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -11970,7 +11970,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="15" thickBot="1">
+    <row r="281" spans="1:5" ht="17" thickBot="1">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="15" thickBot="1">
+    <row r="282" spans="1:5" ht="17" thickBot="1">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="15" thickBot="1">
+    <row r="283" spans="1:5" ht="17" thickBot="1">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="15" thickBot="1">
+    <row r="284" spans="1:5" ht="17" thickBot="1">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="15" thickBot="1">
+    <row r="285" spans="1:5" ht="17" thickBot="1">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -12060,7 +12060,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="15" thickBot="1">
+    <row r="286" spans="1:5" ht="17" thickBot="1">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -12078,7 +12078,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="15" thickBot="1">
+    <row r="287" spans="1:5" ht="17" thickBot="1">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="15" thickBot="1">
+    <row r="288" spans="1:5" ht="17" thickBot="1">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -12114,7 +12114,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="15" thickBot="1">
+    <row r="289" spans="1:5" ht="17" thickBot="1">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="15" thickBot="1">
+    <row r="290" spans="1:5" ht="17" thickBot="1">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -12150,7 +12150,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="15" thickBot="1">
+    <row r="291" spans="1:5" ht="17" thickBot="1">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="15" thickBot="1">
+    <row r="292" spans="1:5" ht="17" thickBot="1">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -12186,7 +12186,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="15" thickBot="1">
+    <row r="293" spans="1:5" ht="17" thickBot="1">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="15" thickBot="1">
+    <row r="294" spans="1:5" ht="17" thickBot="1">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="15" thickBot="1">
+    <row r="295" spans="1:5" ht="17" thickBot="1">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -12240,7 +12240,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="15" thickBot="1">
+    <row r="296" spans="1:5" ht="17" thickBot="1">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="15" thickBot="1">
+    <row r="297" spans="1:5" ht="17" thickBot="1">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -12276,7 +12276,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="15" thickBot="1">
+    <row r="298" spans="1:5" ht="17" thickBot="1">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="15" thickBot="1">
+    <row r="299" spans="1:5" ht="17" thickBot="1">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="15" thickBot="1">
+    <row r="300" spans="1:5" ht="17" thickBot="1">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -12330,7 +12330,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="15" thickBot="1">
+    <row r="301" spans="1:5" ht="17" thickBot="1">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -12348,7 +12348,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="15" thickBot="1">
+    <row r="302" spans="1:5" ht="17" thickBot="1">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="15" thickBot="1">
+    <row r="303" spans="1:5" ht="17" thickBot="1">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -12384,7 +12384,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="15" thickBot="1">
+    <row r="304" spans="1:5" ht="17" thickBot="1">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="15" thickBot="1">
+    <row r="305" spans="1:5" ht="17" thickBot="1">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -12420,7 +12420,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="15" thickBot="1">
+    <row r="306" spans="1:5" ht="17" thickBot="1">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="15" thickBot="1">
+    <row r="307" spans="1:5" ht="17" thickBot="1">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="15" thickBot="1">
+    <row r="308" spans="1:5" ht="17" thickBot="1">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -12474,7 +12474,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="15" thickBot="1">
+    <row r="309" spans="1:5" ht="17" thickBot="1">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="15" thickBot="1">
+    <row r="310" spans="1:5" ht="17" thickBot="1">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="15" thickBot="1">
+    <row r="311" spans="1:5" ht="17" thickBot="1">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -12528,7 +12528,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="15" thickBot="1">
+    <row r="312" spans="1:5" ht="17" thickBot="1">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -12546,7 +12546,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="15" thickBot="1">
+    <row r="313" spans="1:5" ht="17" thickBot="1">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="15" thickBot="1">
+    <row r="314" spans="1:5" ht="17" thickBot="1">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -12582,7 +12582,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="15" thickBot="1">
+    <row r="315" spans="1:5" ht="17" thickBot="1">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -12600,7 +12600,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="15" thickBot="1">
+    <row r="316" spans="1:5" ht="17" thickBot="1">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -12618,7 +12618,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="15" thickBot="1">
+    <row r="317" spans="1:5" ht="17" thickBot="1">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="15" thickBot="1">
+    <row r="318" spans="1:5" ht="17" thickBot="1">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="15" thickBot="1">
+    <row r="319" spans="1:5" ht="17" thickBot="1">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -12672,7 +12672,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="15" thickBot="1">
+    <row r="320" spans="1:5" ht="17" thickBot="1">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -12690,7 +12690,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="15" thickBot="1">
+    <row r="321" spans="1:5" ht="17" thickBot="1">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="15" thickBot="1">
+    <row r="322" spans="1:5" ht="17" thickBot="1">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="15" thickBot="1">
+    <row r="323" spans="1:5" ht="17" thickBot="1">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -12759,7 +12759,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="15" thickBot="1">
+    <row r="324" spans="1:5" ht="17" thickBot="1">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -12777,7 +12777,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="15" thickBot="1">
+    <row r="325" spans="1:5" ht="17" thickBot="1">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="15" thickBot="1">
+    <row r="326" spans="1:5" ht="17" thickBot="1">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="15" thickBot="1">
+    <row r="327" spans="1:5" ht="17" thickBot="1">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="15" thickBot="1">
+    <row r="328" spans="1:5" ht="17" thickBot="1">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -12849,7 +12849,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="15" thickBot="1">
+    <row r="329" spans="1:5" ht="17" thickBot="1">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -12867,7 +12867,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="15" thickBot="1">
+    <row r="330" spans="1:5" ht="17" thickBot="1">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="15" thickBot="1">
+    <row r="331" spans="1:5" ht="17" thickBot="1">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -12903,7 +12903,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="15" thickBot="1">
+    <row r="332" spans="1:5" ht="17" thickBot="1">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -12921,7 +12921,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="15" thickBot="1">
+    <row r="333" spans="1:5" ht="17" thickBot="1">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="15" thickBot="1">
+    <row r="334" spans="1:5" ht="17" thickBot="1">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -12957,7 +12957,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="15" thickBot="1">
+    <row r="335" spans="1:5" ht="17" thickBot="1">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -12975,7 +12975,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="15" thickBot="1">
+    <row r="336" spans="1:5" ht="17" thickBot="1">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -12993,7 +12993,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="15" thickBot="1">
+    <row r="337" spans="1:5" ht="17" thickBot="1">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -13011,7 +13011,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="15" thickBot="1">
+    <row r="338" spans="1:5" ht="17" thickBot="1">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -13029,7 +13029,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="15" thickBot="1">
+    <row r="339" spans="1:5" ht="17" thickBot="1">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -13047,7 +13047,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="15" thickBot="1">
+    <row r="340" spans="1:5" ht="17" thickBot="1">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -13065,7 +13065,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="15" thickBot="1">
+    <row r="341" spans="1:5" ht="17" thickBot="1">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -13083,7 +13083,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="15" thickBot="1">
+    <row r="342" spans="1:5" ht="17" thickBot="1">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -13101,7 +13101,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="15" thickBot="1">
+    <row r="343" spans="1:5" ht="17" thickBot="1">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="15" thickBot="1">
+    <row r="344" spans="1:5" ht="17" thickBot="1">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -13137,7 +13137,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="15" thickBot="1">
+    <row r="345" spans="1:5" ht="17" thickBot="1">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="15" thickBot="1">
+    <row r="346" spans="1:5" ht="17" thickBot="1">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="15" thickBot="1">
+    <row r="347" spans="1:5" ht="17" thickBot="1">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -13191,7 +13191,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="15" thickBot="1">
+    <row r="348" spans="1:5" ht="17" thickBot="1">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="15" thickBot="1">
+    <row r="349" spans="1:5" ht="17" thickBot="1">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -13227,7 +13227,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="15" thickBot="1">
+    <row r="350" spans="1:5" ht="17" thickBot="1">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="15" thickBot="1">
+    <row r="351" spans="1:5" ht="17" thickBot="1">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -13263,7 +13263,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="15" thickBot="1">
+    <row r="352" spans="1:5" ht="17" thickBot="1">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -13281,7 +13281,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="15" thickBot="1">
+    <row r="353" spans="1:5" ht="17" thickBot="1">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="15" thickBot="1">
+    <row r="354" spans="1:5" ht="17" thickBot="1">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -13317,7 +13317,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="15" thickBot="1">
+    <row r="355" spans="1:5" ht="17" thickBot="1">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="15" thickBot="1">
+    <row r="356" spans="1:5" ht="17" thickBot="1">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -13353,7 +13353,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="15" thickBot="1">
+    <row r="357" spans="1:5" ht="17" thickBot="1">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -13371,7 +13371,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="15" thickBot="1">
+    <row r="358" spans="1:5" ht="17" thickBot="1">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -13389,7 +13389,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="15" thickBot="1">
+    <row r="359" spans="1:5" ht="17" thickBot="1">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -13407,7 +13407,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="15" thickBot="1">
+    <row r="360" spans="1:5" ht="17" thickBot="1">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -13425,7 +13425,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="15" thickBot="1">
+    <row r="361" spans="1:5" ht="17" thickBot="1">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -13443,7 +13443,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="15" thickBot="1">
+    <row r="362" spans="1:5" ht="17" thickBot="1">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -13461,7 +13461,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="15" thickBot="1">
+    <row r="363" spans="1:5" ht="17" thickBot="1">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -13479,7 +13479,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="15" thickBot="1">
+    <row r="364" spans="1:5" ht="17" thickBot="1">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -13497,7 +13497,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="15" thickBot="1">
+    <row r="365" spans="1:5" ht="17" thickBot="1">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -13515,7 +13515,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="15" thickBot="1">
+    <row r="366" spans="1:5" ht="17" thickBot="1">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="15" thickBot="1">
+    <row r="367" spans="1:5" ht="17" thickBot="1">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -13551,7 +13551,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="15" thickBot="1">
+    <row r="368" spans="1:5" ht="17" thickBot="1">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -13569,7 +13569,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="15" thickBot="1">
+    <row r="369" spans="1:5" ht="17" thickBot="1">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -13587,7 +13587,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="15" thickBot="1">
+    <row r="370" spans="1:5" ht="17" thickBot="1">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -13605,7 +13605,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="15" thickBot="1">
+    <row r="371" spans="1:5" ht="17" thickBot="1">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -13623,7 +13623,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="15" thickBot="1">
+    <row r="372" spans="1:5" ht="17" thickBot="1">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -13641,7 +13641,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="15" thickBot="1">
+    <row r="373" spans="1:5" ht="17" thickBot="1">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -13659,7 +13659,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="15" thickBot="1">
+    <row r="374" spans="1:5" ht="17" thickBot="1">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -13677,7 +13677,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="15" thickBot="1">
+    <row r="375" spans="1:5" ht="17" thickBot="1">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="15" thickBot="1">
+    <row r="376" spans="1:5" ht="17" thickBot="1">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -13713,7 +13713,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="15" thickBot="1">
+    <row r="377" spans="1:5" ht="17" thickBot="1">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -13731,7 +13731,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="15" thickBot="1">
+    <row r="378" spans="1:5" ht="17" thickBot="1">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -13749,7 +13749,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="15" thickBot="1">
+    <row r="379" spans="1:5" ht="17" thickBot="1">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -13767,7 +13767,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="15" thickBot="1">
+    <row r="380" spans="1:5" ht="17" thickBot="1">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -13785,7 +13785,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="15" thickBot="1">
+    <row r="381" spans="1:5" ht="17" thickBot="1">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -13803,7 +13803,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="15" thickBot="1">
+    <row r="382" spans="1:5" ht="17" thickBot="1">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -13821,7 +13821,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="15" thickBot="1">
+    <row r="383" spans="1:5" ht="17" thickBot="1">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -13839,7 +13839,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="15" thickBot="1">
+    <row r="384" spans="1:5" ht="17" thickBot="1">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -13857,7 +13857,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="15" thickBot="1">
+    <row r="385" spans="1:5" ht="17" thickBot="1">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -13875,7 +13875,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="15" thickBot="1">
+    <row r="386" spans="1:5" ht="17" thickBot="1">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="15" thickBot="1">
+    <row r="387" spans="1:5" ht="17" thickBot="1">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -13926,7 +13926,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="15" thickBot="1">
+    <row r="388" spans="1:5" ht="17" thickBot="1">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -13944,7 +13944,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="15" thickBot="1">
+    <row r="389" spans="1:5" ht="17" thickBot="1">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="15" thickBot="1">
+    <row r="390" spans="1:5" ht="17" thickBot="1">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -13980,7 +13980,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="15" thickBot="1">
+    <row r="391" spans="1:5" ht="17" thickBot="1">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -13998,7 +13998,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="15" thickBot="1">
+    <row r="392" spans="1:5" ht="17" thickBot="1">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="15" thickBot="1">
+    <row r="393" spans="1:5" ht="17" thickBot="1">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -14034,7 +14034,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="15" thickBot="1">
+    <row r="394" spans="1:5" ht="17" thickBot="1">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -14052,7 +14052,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="15" thickBot="1">
+    <row r="395" spans="1:5" ht="17" thickBot="1">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -14070,7 +14070,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="15" thickBot="1">
+    <row r="396" spans="1:5" ht="17" thickBot="1">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -14088,7 +14088,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="15" thickBot="1">
+    <row r="397" spans="1:5" ht="17" thickBot="1">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -14106,7 +14106,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="15" thickBot="1">
+    <row r="398" spans="1:5" ht="17" thickBot="1">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -14124,7 +14124,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="15" thickBot="1">
+    <row r="399" spans="1:5" ht="17" thickBot="1">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="15" thickBot="1">
+    <row r="400" spans="1:5" ht="17" thickBot="1">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -14160,7 +14160,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="15" thickBot="1">
+    <row r="401" spans="1:5" ht="17" thickBot="1">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -14178,7 +14178,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="15" thickBot="1">
+    <row r="402" spans="1:5" ht="17" thickBot="1">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -14196,7 +14196,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="15" thickBot="1">
+    <row r="403" spans="1:5" ht="17" thickBot="1">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -14214,7 +14214,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="15" thickBot="1">
+    <row r="404" spans="1:5" ht="17" thickBot="1">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -14232,7 +14232,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="15" thickBot="1">
+    <row r="405" spans="1:5" ht="17" thickBot="1">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -14250,7 +14250,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="15" thickBot="1">
+    <row r="406" spans="1:5" ht="17" thickBot="1">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -14268,7 +14268,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="15" thickBot="1">
+    <row r="407" spans="1:5" ht="17" thickBot="1">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -14286,7 +14286,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="15" thickBot="1">
+    <row r="408" spans="1:5" ht="17" thickBot="1">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -14304,7 +14304,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="15" thickBot="1">
+    <row r="409" spans="1:5" ht="17" thickBot="1">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="15" thickBot="1">
+    <row r="410" spans="1:5" ht="17" thickBot="1">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="15" thickBot="1">
+    <row r="411" spans="1:5" ht="17" thickBot="1">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -14358,7 +14358,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="15" thickBot="1">
+    <row r="412" spans="1:5" ht="17" thickBot="1">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -14376,7 +14376,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="15" thickBot="1">
+    <row r="413" spans="1:5" ht="17" thickBot="1">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -14394,7 +14394,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="15" thickBot="1">
+    <row r="414" spans="1:5" ht="17" thickBot="1">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -14412,7 +14412,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="15" thickBot="1">
+    <row r="415" spans="1:5" ht="17" thickBot="1">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -14430,7 +14430,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="15" thickBot="1">
+    <row r="416" spans="1:5" ht="17" thickBot="1">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -14448,7 +14448,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="15" thickBot="1">
+    <row r="417" spans="1:5" ht="17" thickBot="1">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="15" thickBot="1">
+    <row r="418" spans="1:5" ht="17" thickBot="1">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="15" thickBot="1">
+    <row r="419" spans="1:5" ht="17" thickBot="1">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -14502,7 +14502,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="15" thickBot="1">
+    <row r="420" spans="1:5" ht="17" thickBot="1">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -14520,7 +14520,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="15" thickBot="1">
+    <row r="421" spans="1:5" ht="17" thickBot="1">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="15" thickBot="1">
+    <row r="422" spans="1:5" ht="17" thickBot="1">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -14556,7 +14556,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="15" thickBot="1">
+    <row r="423" spans="1:5" ht="17" thickBot="1">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -14574,7 +14574,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="15" thickBot="1">
+    <row r="424" spans="1:5" ht="17" thickBot="1">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="15" thickBot="1">
+    <row r="425" spans="1:5" ht="17" thickBot="1">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -14610,7 +14610,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="15" thickBot="1">
+    <row r="426" spans="1:5" ht="17" thickBot="1">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -14628,7 +14628,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="15" thickBot="1">
+    <row r="427" spans="1:5" ht="17" thickBot="1">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -14646,7 +14646,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="15" thickBot="1">
+    <row r="428" spans="1:5" ht="17" thickBot="1">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="15" thickBot="1">
+    <row r="429" spans="1:5" ht="17" thickBot="1">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="15" thickBot="1">
+    <row r="430" spans="1:5" ht="17" thickBot="1">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -14700,7 +14700,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="15" thickBot="1">
+    <row r="431" spans="1:5" ht="17" thickBot="1">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="15" thickBot="1">
+    <row r="432" spans="1:5" ht="17" thickBot="1">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -14736,7 +14736,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="15" thickBot="1">
+    <row r="433" spans="1:5" ht="17" thickBot="1">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -14754,7 +14754,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="15" thickBot="1">
+    <row r="434" spans="1:5" ht="17" thickBot="1">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -14772,7 +14772,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="15" thickBot="1">
+    <row r="435" spans="1:5" ht="17" thickBot="1">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -14790,7 +14790,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="15" thickBot="1">
+    <row r="436" spans="1:5" ht="17" thickBot="1">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -14808,7 +14808,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="15" thickBot="1">
+    <row r="437" spans="1:5" ht="17" thickBot="1">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -14826,7 +14826,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="15" thickBot="1">
+    <row r="438" spans="1:5" ht="17" thickBot="1">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -14844,7 +14844,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="15" thickBot="1">
+    <row r="439" spans="1:5" ht="17" thickBot="1">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -14862,7 +14862,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="15" thickBot="1">
+    <row r="440" spans="1:5" ht="17" thickBot="1">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -14880,7 +14880,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="15" thickBot="1">
+    <row r="441" spans="1:5" ht="17" thickBot="1">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="15" thickBot="1">
+    <row r="442" spans="1:5" ht="17" thickBot="1">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -14916,7 +14916,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="15" thickBot="1">
+    <row r="443" spans="1:5" ht="17" thickBot="1">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -14934,7 +14934,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="15" thickBot="1">
+    <row r="444" spans="1:5" ht="17" thickBot="1">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -14952,7 +14952,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="15" thickBot="1">
+    <row r="445" spans="1:5" ht="17" thickBot="1">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -14970,7 +14970,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="15" thickBot="1">
+    <row r="446" spans="1:5" ht="17" thickBot="1">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -14988,7 +14988,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="15" thickBot="1">
+    <row r="447" spans="1:5" ht="17" thickBot="1">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -15006,7 +15006,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="15" thickBot="1">
+    <row r="448" spans="1:5" ht="17" thickBot="1">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -15024,7 +15024,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="15" thickBot="1">
+    <row r="449" spans="1:5" ht="17" thickBot="1">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -15042,7 +15042,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="15" thickBot="1">
+    <row r="450" spans="1:5" ht="17" thickBot="1">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -15075,7 +15075,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="15" thickBot="1">
+    <row r="451" spans="1:5" ht="17" thickBot="1">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -15093,7 +15093,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="15" thickBot="1">
+    <row r="452" spans="1:5" ht="17" thickBot="1">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -15111,7 +15111,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="15" thickBot="1">
+    <row r="453" spans="1:5" ht="17" thickBot="1">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -15129,7 +15129,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="15" thickBot="1">
+    <row r="454" spans="1:5" ht="17" thickBot="1">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -15147,7 +15147,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="15" thickBot="1">
+    <row r="455" spans="1:5" ht="17" thickBot="1">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -15165,7 +15165,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="15" thickBot="1">
+    <row r="456" spans="1:5" ht="17" thickBot="1">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -15183,7 +15183,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="15" thickBot="1">
+    <row r="457" spans="1:5" ht="17" thickBot="1">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -15201,7 +15201,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="15" thickBot="1">
+    <row r="458" spans="1:5" ht="17" thickBot="1">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -15219,7 +15219,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="15" thickBot="1">
+    <row r="459" spans="1:5" ht="17" thickBot="1">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -15237,7 +15237,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="15" thickBot="1">
+    <row r="460" spans="1:5" ht="17" thickBot="1">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -15255,7 +15255,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="15" thickBot="1">
+    <row r="461" spans="1:5" ht="17" thickBot="1">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -15273,7 +15273,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="15" thickBot="1">
+    <row r="462" spans="1:5" ht="17" thickBot="1">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -15291,7 +15291,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="15" thickBot="1">
+    <row r="463" spans="1:5" ht="17" thickBot="1">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -15309,7 +15309,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="15" thickBot="1">
+    <row r="464" spans="1:5" ht="17" thickBot="1">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="15" thickBot="1">
+    <row r="465" spans="1:5" ht="17" thickBot="1">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -15345,7 +15345,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="15" thickBot="1">
+    <row r="466" spans="1:5" ht="17" thickBot="1">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -15363,7 +15363,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="15" thickBot="1">
+    <row r="467" spans="1:5" ht="17" thickBot="1">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -15381,7 +15381,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="15" thickBot="1">
+    <row r="468" spans="1:5" ht="17" thickBot="1">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -15399,7 +15399,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="15" thickBot="1">
+    <row r="469" spans="1:5" ht="17" thickBot="1">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -15417,7 +15417,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="15" thickBot="1">
+    <row r="470" spans="1:5" ht="17" thickBot="1">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -15435,7 +15435,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="15" thickBot="1">
+    <row r="471" spans="1:5" ht="17" thickBot="1">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -15453,7 +15453,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="15" thickBot="1">
+    <row r="472" spans="1:5" ht="17" thickBot="1">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -15471,7 +15471,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="15" thickBot="1">
+    <row r="473" spans="1:5" ht="17" thickBot="1">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -15489,7 +15489,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="15" thickBot="1">
+    <row r="474" spans="1:5" ht="17" thickBot="1">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -15507,7 +15507,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="15" thickBot="1">
+    <row r="475" spans="1:5" ht="17" thickBot="1">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -15525,7 +15525,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="15" thickBot="1">
+    <row r="476" spans="1:5" ht="17" thickBot="1">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -15543,7 +15543,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="15" thickBot="1">
+    <row r="477" spans="1:5" ht="17" thickBot="1">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -15561,7 +15561,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="15" thickBot="1">
+    <row r="478" spans="1:5" ht="17" thickBot="1">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -15579,7 +15579,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="15" thickBot="1">
+    <row r="479" spans="1:5" ht="17" thickBot="1">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -15597,7 +15597,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="15" thickBot="1">
+    <row r="480" spans="1:5" ht="17" thickBot="1">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -15615,7 +15615,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="15" thickBot="1">
+    <row r="481" spans="1:5" ht="17" thickBot="1">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -15633,7 +15633,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="15" thickBot="1">
+    <row r="482" spans="1:5" ht="17" thickBot="1">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -15651,7 +15651,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="15" thickBot="1">
+    <row r="483" spans="1:5" ht="17" thickBot="1">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -15669,7 +15669,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="15" thickBot="1">
+    <row r="484" spans="1:5" ht="17" thickBot="1">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -15687,7 +15687,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="15" thickBot="1">
+    <row r="485" spans="1:5" ht="17" thickBot="1">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -15705,7 +15705,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="15" thickBot="1">
+    <row r="486" spans="1:5" ht="17" thickBot="1">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -15723,7 +15723,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="15" thickBot="1">
+    <row r="487" spans="1:5" ht="17" thickBot="1">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -15741,7 +15741,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="15" thickBot="1">
+    <row r="488" spans="1:5" ht="17" thickBot="1">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -15759,7 +15759,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="15" thickBot="1">
+    <row r="489" spans="1:5" ht="17" thickBot="1">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -15777,7 +15777,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="15" thickBot="1">
+    <row r="490" spans="1:5" ht="17" thickBot="1">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -15795,7 +15795,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="15" thickBot="1">
+    <row r="491" spans="1:5" ht="17" thickBot="1">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="15" thickBot="1">
+    <row r="492" spans="1:5" ht="17" thickBot="1">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -15831,7 +15831,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="15" thickBot="1">
+    <row r="493" spans="1:5" ht="17" thickBot="1">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -15849,7 +15849,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="15" thickBot="1">
+    <row r="494" spans="1:5" ht="17" thickBot="1">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -15867,7 +15867,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="15" thickBot="1">
+    <row r="495" spans="1:5" ht="17" thickBot="1">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -15885,7 +15885,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="15" thickBot="1">
+    <row r="496" spans="1:5" ht="17" thickBot="1">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="15" thickBot="1">
+    <row r="497" spans="1:5" ht="17" thickBot="1">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -15921,7 +15921,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="15" thickBot="1">
+    <row r="498" spans="1:5" ht="17" thickBot="1">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -15939,7 +15939,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="15" thickBot="1">
+    <row r="499" spans="1:5" ht="17" thickBot="1">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -15957,7 +15957,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="15" thickBot="1">
+    <row r="500" spans="1:5" ht="17" thickBot="1">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -15975,7 +15975,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="15" thickBot="1">
+    <row r="501" spans="1:5" ht="17" thickBot="1">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="15" thickBot="1">
+    <row r="502" spans="1:5" ht="17" thickBot="1">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -16011,7 +16011,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="15" thickBot="1">
+    <row r="503" spans="1:5" ht="17" thickBot="1">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -16029,7 +16029,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="15" thickBot="1">
+    <row r="504" spans="1:5" ht="17" thickBot="1">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -16047,7 +16047,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="15" thickBot="1">
+    <row r="505" spans="1:5" ht="17" thickBot="1">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -16065,7 +16065,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="15" thickBot="1">
+    <row r="506" spans="1:5" ht="17" thickBot="1">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -16083,7 +16083,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="15" thickBot="1">
+    <row r="507" spans="1:5" ht="17" thickBot="1">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -16101,7 +16101,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="15" thickBot="1">
+    <row r="508" spans="1:5" ht="17" thickBot="1">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -16119,7 +16119,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="15" thickBot="1">
+    <row r="509" spans="1:5" ht="17" thickBot="1">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -16137,7 +16137,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="15" thickBot="1">
+    <row r="510" spans="1:5" ht="17" thickBot="1">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -16155,7 +16155,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="15" thickBot="1">
+    <row r="511" spans="1:5" ht="17" thickBot="1">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -16173,7 +16173,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="15" thickBot="1">
+    <row r="512" spans="1:5" ht="17" thickBot="1">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="15" thickBot="1">
+    <row r="513" spans="1:5" ht="17" thickBot="1">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -16209,7 +16209,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="15" thickBot="1">
+    <row r="514" spans="1:5" ht="17" thickBot="1">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -16242,7 +16242,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="15" thickBot="1">
+    <row r="515" spans="1:5" ht="17" thickBot="1">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -16260,7 +16260,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="15" thickBot="1">
+    <row r="516" spans="1:5" ht="17" thickBot="1">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -16278,7 +16278,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="15" thickBot="1">
+    <row r="517" spans="1:5" ht="17" thickBot="1">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="15" thickBot="1">
+    <row r="518" spans="1:5" ht="17" thickBot="1">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -16314,7 +16314,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="15" thickBot="1">
+    <row r="519" spans="1:5" ht="17" thickBot="1">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -16332,7 +16332,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="15" thickBot="1">
+    <row r="520" spans="1:5" ht="17" thickBot="1">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -16350,7 +16350,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="15" thickBot="1">
+    <row r="521" spans="1:5" ht="17" thickBot="1">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -16368,7 +16368,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="15" thickBot="1">
+    <row r="522" spans="1:5" ht="17" thickBot="1">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -16386,7 +16386,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="15" thickBot="1">
+    <row r="523" spans="1:5" ht="17" thickBot="1">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -16404,7 +16404,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="15" thickBot="1">
+    <row r="524" spans="1:5" ht="17" thickBot="1">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="15" thickBot="1">
+    <row r="525" spans="1:5" ht="17" thickBot="1">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -16440,7 +16440,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="15" thickBot="1">
+    <row r="526" spans="1:5" ht="17" thickBot="1">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="15" thickBot="1">
+    <row r="527" spans="1:5" ht="17" thickBot="1">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -16476,7 +16476,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="15" thickBot="1">
+    <row r="528" spans="1:5" ht="17" thickBot="1">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -16494,7 +16494,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="15" thickBot="1">
+    <row r="529" spans="1:5" ht="17" thickBot="1">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -16512,7 +16512,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="15" thickBot="1">
+    <row r="530" spans="1:5" ht="17" thickBot="1">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -16530,7 +16530,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="15" thickBot="1">
+    <row r="531" spans="1:5" ht="17" thickBot="1">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -16548,7 +16548,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="15" thickBot="1">
+    <row r="532" spans="1:5" ht="17" thickBot="1">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="15" thickBot="1">
+    <row r="533" spans="1:5" ht="17" thickBot="1">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -16584,7 +16584,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="15" thickBot="1">
+    <row r="534" spans="1:5" ht="17" thickBot="1">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -16602,7 +16602,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="15" thickBot="1">
+    <row r="535" spans="1:5" ht="17" thickBot="1">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -16620,7 +16620,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="15" thickBot="1">
+    <row r="536" spans="1:5" ht="17" thickBot="1">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -16638,7 +16638,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="15" thickBot="1">
+    <row r="537" spans="1:5" ht="17" thickBot="1">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -16656,7 +16656,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="15" thickBot="1">
+    <row r="538" spans="1:5" ht="17" thickBot="1">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -16674,7 +16674,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="15" thickBot="1">
+    <row r="539" spans="1:5" ht="17" thickBot="1">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -16692,7 +16692,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="15" thickBot="1">
+    <row r="540" spans="1:5" ht="17" thickBot="1">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="15" thickBot="1">
+    <row r="541" spans="1:5" ht="17" thickBot="1">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -16728,7 +16728,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="15" thickBot="1">
+    <row r="542" spans="1:5" ht="17" thickBot="1">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -16746,7 +16746,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="15" thickBot="1">
+    <row r="543" spans="1:5" ht="17" thickBot="1">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -16764,7 +16764,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="15" thickBot="1">
+    <row r="544" spans="1:5" ht="17" thickBot="1">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -16782,7 +16782,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="15" thickBot="1">
+    <row r="545" spans="1:5" ht="17" thickBot="1">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -16800,7 +16800,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="15" thickBot="1">
+    <row r="546" spans="1:5" ht="17" thickBot="1">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -16818,7 +16818,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="15" thickBot="1">
+    <row r="547" spans="1:5" ht="17" thickBot="1">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -16836,7 +16836,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="15" thickBot="1">
+    <row r="548" spans="1:5" ht="17" thickBot="1">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -16854,7 +16854,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="15" thickBot="1">
+    <row r="549" spans="1:5" ht="17" thickBot="1">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -16872,7 +16872,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="15" thickBot="1">
+    <row r="550" spans="1:5" ht="17" thickBot="1">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -16890,7 +16890,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="15" thickBot="1">
+    <row r="551" spans="1:5" ht="17" thickBot="1">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -16908,7 +16908,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="15" thickBot="1">
+    <row r="552" spans="1:5" ht="17" thickBot="1">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -16926,7 +16926,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="15" thickBot="1">
+    <row r="553" spans="1:5" ht="17" thickBot="1">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -16944,7 +16944,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="15" thickBot="1">
+    <row r="554" spans="1:5" ht="17" thickBot="1">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -16962,7 +16962,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="15" thickBot="1">
+    <row r="555" spans="1:5" ht="17" thickBot="1">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -16980,7 +16980,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="15" thickBot="1">
+    <row r="556" spans="1:5" ht="17" thickBot="1">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -16998,7 +16998,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="15" thickBot="1">
+    <row r="557" spans="1:5" ht="17" thickBot="1">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -17016,7 +17016,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="15" thickBot="1">
+    <row r="558" spans="1:5" ht="17" thickBot="1">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -17034,7 +17034,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="15" thickBot="1">
+    <row r="559" spans="1:5" ht="17" thickBot="1">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -17052,7 +17052,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="15" thickBot="1">
+    <row r="560" spans="1:5" ht="17" thickBot="1">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -17070,7 +17070,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="15" thickBot="1">
+    <row r="561" spans="1:5" ht="17" thickBot="1">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -17088,7 +17088,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="15" thickBot="1">
+    <row r="562" spans="1:5" ht="17" thickBot="1">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -17106,7 +17106,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="15" thickBot="1">
+    <row r="563" spans="1:5" ht="17" thickBot="1">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -17124,7 +17124,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="15" thickBot="1">
+    <row r="564" spans="1:5" ht="17" thickBot="1">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -17142,7 +17142,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="15" thickBot="1">
+    <row r="565" spans="1:5" ht="17" thickBot="1">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -17160,7 +17160,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="15" thickBot="1">
+    <row r="566" spans="1:5" ht="17" thickBot="1">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -17178,7 +17178,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="15" thickBot="1">
+    <row r="567" spans="1:5" ht="17" thickBot="1">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -17196,7 +17196,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="15" thickBot="1">
+    <row r="568" spans="1:5" ht="17" thickBot="1">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -17214,7 +17214,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="15" thickBot="1">
+    <row r="569" spans="1:5" ht="17" thickBot="1">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -17232,7 +17232,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="15" thickBot="1">
+    <row r="570" spans="1:5" ht="17" thickBot="1">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -17250,7 +17250,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="15" thickBot="1">
+    <row r="571" spans="1:5" ht="17" thickBot="1">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -17268,7 +17268,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="15" thickBot="1">
+    <row r="572" spans="1:5" ht="17" thickBot="1">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -17286,7 +17286,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="15" thickBot="1">
+    <row r="573" spans="1:5" ht="17" thickBot="1">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -17304,7 +17304,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="15" thickBot="1">
+    <row r="574" spans="1:5" ht="17" thickBot="1">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -17322,7 +17322,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="15" thickBot="1">
+    <row r="575" spans="1:5" ht="17" thickBot="1">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -17340,7 +17340,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="15" thickBot="1">
+    <row r="576" spans="1:5" ht="17" thickBot="1">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -17358,7 +17358,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="15" thickBot="1">
+    <row r="577" spans="1:5" ht="17" thickBot="1">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -17376,7 +17376,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="15" thickBot="1">
+    <row r="578" spans="1:5" ht="17" thickBot="1">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -17409,7 +17409,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="15" thickBot="1">
+    <row r="579" spans="1:5" ht="17" thickBot="1">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -17427,7 +17427,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="15" thickBot="1">
+    <row r="580" spans="1:5" ht="17" thickBot="1">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -17445,7 +17445,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="15" thickBot="1">
+    <row r="581" spans="1:5" ht="17" thickBot="1">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -17463,7 +17463,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="15" thickBot="1">
+    <row r="582" spans="1:5" ht="17" thickBot="1">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -17481,7 +17481,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="15" thickBot="1">
+    <row r="583" spans="1:5" ht="17" thickBot="1">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -17499,7 +17499,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="15" thickBot="1">
+    <row r="584" spans="1:5" ht="17" thickBot="1">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -17517,7 +17517,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="15" thickBot="1">
+    <row r="585" spans="1:5" ht="17" thickBot="1">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -17535,7 +17535,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="15" thickBot="1">
+    <row r="586" spans="1:5" ht="17" thickBot="1">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -17553,7 +17553,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="15" thickBot="1">
+    <row r="587" spans="1:5" ht="17" thickBot="1">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -17571,7 +17571,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="15" thickBot="1">
+    <row r="588" spans="1:5" ht="17" thickBot="1">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -17589,7 +17589,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="15" thickBot="1">
+    <row r="589" spans="1:5" ht="17" thickBot="1">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -17607,7 +17607,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="15" thickBot="1">
+    <row r="590" spans="1:5" ht="17" thickBot="1">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -17625,7 +17625,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="15" thickBot="1">
+    <row r="591" spans="1:5" ht="17" thickBot="1">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="15" thickBot="1">
+    <row r="592" spans="1:5" ht="17" thickBot="1">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -17661,7 +17661,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="15" thickBot="1">
+    <row r="593" spans="1:5" ht="17" thickBot="1">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -17679,7 +17679,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="15" thickBot="1">
+    <row r="594" spans="1:5" ht="17" thickBot="1">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -17697,7 +17697,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="15" thickBot="1">
+    <row r="595" spans="1:5" ht="17" thickBot="1">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -17715,7 +17715,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="15" thickBot="1">
+    <row r="596" spans="1:5" ht="17" thickBot="1">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -17733,7 +17733,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="15" thickBot="1">
+    <row r="597" spans="1:5" ht="17" thickBot="1">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -17751,7 +17751,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="15" thickBot="1">
+    <row r="598" spans="1:5" ht="17" thickBot="1">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -17769,7 +17769,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="15" thickBot="1">
+    <row r="599" spans="1:5" ht="17" thickBot="1">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="15" thickBot="1">
+    <row r="600" spans="1:5" ht="17" thickBot="1">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -17805,7 +17805,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="15" thickBot="1">
+    <row r="601" spans="1:5" ht="17" thickBot="1">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -17823,7 +17823,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="15" thickBot="1">
+    <row r="602" spans="1:5" ht="17" thickBot="1">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -17841,7 +17841,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="15" thickBot="1">
+    <row r="603" spans="1:5" ht="17" thickBot="1">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -17859,7 +17859,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="15" thickBot="1">
+    <row r="604" spans="1:5" ht="17" thickBot="1">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -17877,7 +17877,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="15" thickBot="1">
+    <row r="605" spans="1:5" ht="17" thickBot="1">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -17895,7 +17895,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="15" thickBot="1">
+    <row r="606" spans="1:5" ht="17" thickBot="1">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -17913,7 +17913,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="15" thickBot="1">
+    <row r="607" spans="1:5" ht="17" thickBot="1">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="15" thickBot="1">
+    <row r="608" spans="1:5" ht="17" thickBot="1">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -17949,7 +17949,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="15" thickBot="1">
+    <row r="609" spans="1:5" ht="17" thickBot="1">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -17967,7 +17967,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="15" thickBot="1">
+    <row r="610" spans="1:5" ht="17" thickBot="1">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -17985,7 +17985,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="15" thickBot="1">
+    <row r="611" spans="1:5" ht="17" thickBot="1">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -18003,7 +18003,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="15" thickBot="1">
+    <row r="612" spans="1:5" ht="17" thickBot="1">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -18021,7 +18021,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="15" thickBot="1">
+    <row r="613" spans="1:5" ht="17" thickBot="1">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -18039,7 +18039,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="15" thickBot="1">
+    <row r="614" spans="1:5" ht="17" thickBot="1">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -18057,7 +18057,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="15" thickBot="1">
+    <row r="615" spans="1:5" ht="17" thickBot="1">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -18075,7 +18075,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="15" thickBot="1">
+    <row r="616" spans="1:5" ht="17" thickBot="1">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -18093,7 +18093,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="15" thickBot="1">
+    <row r="617" spans="1:5" ht="17" thickBot="1">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -18111,7 +18111,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="15" thickBot="1">
+    <row r="618" spans="1:5" ht="17" thickBot="1">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -18129,7 +18129,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="15" thickBot="1">
+    <row r="619" spans="1:5" ht="17" thickBot="1">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -18147,7 +18147,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="15" thickBot="1">
+    <row r="620" spans="1:5" ht="17" thickBot="1">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -18165,7 +18165,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="15" thickBot="1">
+    <row r="621" spans="1:5" ht="17" thickBot="1">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="15" thickBot="1">
+    <row r="622" spans="1:5" ht="17" thickBot="1">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -18201,7 +18201,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="15" thickBot="1">
+    <row r="623" spans="1:5" ht="17" thickBot="1">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -18219,7 +18219,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="15" thickBot="1">
+    <row r="624" spans="1:5" ht="17" thickBot="1">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -18237,7 +18237,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="15" thickBot="1">
+    <row r="625" spans="1:5" ht="17" thickBot="1">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -18255,7 +18255,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="15" thickBot="1">
+    <row r="626" spans="1:5" ht="17" thickBot="1">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="15" thickBot="1">
+    <row r="627" spans="1:5" ht="17" thickBot="1">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -18291,7 +18291,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="15" thickBot="1">
+    <row r="628" spans="1:5" ht="17" thickBot="1">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -18309,7 +18309,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="15" thickBot="1">
+    <row r="629" spans="1:5" ht="17" thickBot="1">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -18327,7 +18327,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="15" thickBot="1">
+    <row r="630" spans="1:5" ht="17" thickBot="1">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -18345,7 +18345,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="15" thickBot="1">
+    <row r="631" spans="1:5" ht="17" thickBot="1">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -18363,7 +18363,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="15" thickBot="1">
+    <row r="632" spans="1:5" ht="17" thickBot="1">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -18381,7 +18381,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="15" thickBot="1">
+    <row r="633" spans="1:5" ht="17" thickBot="1">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -18399,7 +18399,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="15" thickBot="1">
+    <row r="634" spans="1:5" ht="17" thickBot="1">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="15" thickBot="1">
+    <row r="635" spans="1:5" ht="17" thickBot="1">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -18435,7 +18435,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="15" thickBot="1">
+    <row r="636" spans="1:5" ht="17" thickBot="1">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -18453,7 +18453,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="15" thickBot="1">
+    <row r="637" spans="1:5" ht="17" thickBot="1">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -18471,7 +18471,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="15" thickBot="1">
+    <row r="638" spans="1:5" ht="17" thickBot="1">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -18489,7 +18489,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="15" thickBot="1">
+    <row r="639" spans="1:5" ht="17" thickBot="1">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -18507,7 +18507,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="15" thickBot="1">
+    <row r="640" spans="1:5" ht="17" thickBot="1">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="15" thickBot="1">
+    <row r="641" spans="1:5" ht="17" thickBot="1">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -18543,7 +18543,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="15" thickBot="1">
+    <row r="642" spans="1:5" ht="17" thickBot="1">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -18576,7 +18576,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="15" thickBot="1">
+    <row r="643" spans="1:5" ht="17" thickBot="1">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -18594,7 +18594,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="15" thickBot="1">
+    <row r="644" spans="1:5" ht="17" thickBot="1">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -18612,7 +18612,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="15" thickBot="1">
+    <row r="645" spans="1:5" ht="17" thickBot="1">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -18630,7 +18630,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="15" thickBot="1">
+    <row r="646" spans="1:5" ht="17" thickBot="1">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="15" thickBot="1">
+    <row r="647" spans="1:5" ht="17" thickBot="1">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -18666,7 +18666,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="15" thickBot="1">
+    <row r="648" spans="1:5" ht="17" thickBot="1">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -18684,7 +18684,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="15" thickBot="1">
+    <row r="649" spans="1:5" ht="17" thickBot="1">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -18702,7 +18702,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="15" thickBot="1">
+    <row r="650" spans="1:5" ht="17" thickBot="1">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -18720,7 +18720,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="15" thickBot="1">
+    <row r="651" spans="1:5" ht="17" thickBot="1">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -18738,7 +18738,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="15" thickBot="1">
+    <row r="652" spans="1:5" ht="17" thickBot="1">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -18756,7 +18756,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="15" thickBot="1">
+    <row r="653" spans="1:5" ht="17" thickBot="1">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -18774,7 +18774,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="15" thickBot="1">
+    <row r="654" spans="1:5" ht="17" thickBot="1">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="15" thickBot="1">
+    <row r="655" spans="1:5" ht="17" thickBot="1">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -18810,7 +18810,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="15" thickBot="1">
+    <row r="656" spans="1:5" ht="17" thickBot="1">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -18828,7 +18828,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="15" thickBot="1">
+    <row r="657" spans="1:5" ht="17" thickBot="1">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -18846,7 +18846,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="15" thickBot="1">
+    <row r="658" spans="1:5" ht="17" thickBot="1">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -18864,7 +18864,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="15" thickBot="1">
+    <row r="659" spans="1:5" ht="17" thickBot="1">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -18882,7 +18882,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="15" thickBot="1">
+    <row r="660" spans="1:5" ht="17" thickBot="1">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -18900,7 +18900,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="15" thickBot="1">
+    <row r="661" spans="1:5" ht="17" thickBot="1">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -18918,7 +18918,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="15" thickBot="1">
+    <row r="662" spans="1:5" ht="17" thickBot="1">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -18936,7 +18936,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="15" thickBot="1">
+    <row r="663" spans="1:5" ht="17" thickBot="1">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -18954,7 +18954,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="15" thickBot="1">
+    <row r="664" spans="1:5" ht="17" thickBot="1">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -18972,7 +18972,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="15" thickBot="1">
+    <row r="665" spans="1:5" ht="17" thickBot="1">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -18990,7 +18990,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="15" thickBot="1">
+    <row r="666" spans="1:5" ht="17" thickBot="1">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -19008,7 +19008,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="15" thickBot="1">
+    <row r="667" spans="1:5" ht="17" thickBot="1">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -19026,7 +19026,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="15" thickBot="1">
+    <row r="668" spans="1:5" ht="17" thickBot="1">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -19044,7 +19044,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="15" thickBot="1">
+    <row r="669" spans="1:5" ht="17" thickBot="1">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -19062,7 +19062,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="15" thickBot="1">
+    <row r="670" spans="1:5" ht="17" thickBot="1">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -19080,7 +19080,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="15" thickBot="1">
+    <row r="671" spans="1:5" ht="17" thickBot="1">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -19098,7 +19098,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="15" thickBot="1">
+    <row r="672" spans="1:5" ht="17" thickBot="1">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -19116,7 +19116,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="15" thickBot="1">
+    <row r="673" spans="1:5" ht="17" thickBot="1">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -19134,7 +19134,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="15" thickBot="1">
+    <row r="674" spans="1:5" ht="17" thickBot="1">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -19152,7 +19152,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="15" thickBot="1">
+    <row r="675" spans="1:5" ht="17" thickBot="1">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -19170,7 +19170,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="15" thickBot="1">
+    <row r="676" spans="1:5" ht="17" thickBot="1">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -19188,7 +19188,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="15" thickBot="1">
+    <row r="677" spans="1:5" ht="17" thickBot="1">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -19206,7 +19206,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="15" thickBot="1">
+    <row r="678" spans="1:5" ht="17" thickBot="1">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -19224,7 +19224,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="15" thickBot="1">
+    <row r="679" spans="1:5" ht="17" thickBot="1">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -19242,7 +19242,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="15" thickBot="1">
+    <row r="680" spans="1:5" ht="17" thickBot="1">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -19260,7 +19260,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="15" thickBot="1">
+    <row r="681" spans="1:5" ht="17" thickBot="1">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -19278,7 +19278,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="15" thickBot="1">
+    <row r="682" spans="1:5" ht="17" thickBot="1">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -19296,7 +19296,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="15" thickBot="1">
+    <row r="683" spans="1:5" ht="17" thickBot="1">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -19314,7 +19314,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="15" thickBot="1">
+    <row r="684" spans="1:5" ht="17" thickBot="1">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -19332,7 +19332,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="15" thickBot="1">
+    <row r="685" spans="1:5" ht="17" thickBot="1">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="15" thickBot="1">
+    <row r="686" spans="1:5" ht="17" thickBot="1">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -19368,7 +19368,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="15" thickBot="1">
+    <row r="687" spans="1:5" ht="17" thickBot="1">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -19386,7 +19386,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="15" thickBot="1">
+    <row r="688" spans="1:5" ht="17" thickBot="1">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -19404,7 +19404,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="15" thickBot="1">
+    <row r="689" spans="1:5" ht="17" thickBot="1">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -19422,7 +19422,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="15" thickBot="1">
+    <row r="690" spans="1:5" ht="17" thickBot="1">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -19440,7 +19440,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="15" thickBot="1">
+    <row r="691" spans="1:5" ht="17" thickBot="1">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -19458,7 +19458,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="15" thickBot="1">
+    <row r="692" spans="1:5" ht="17" thickBot="1">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -19476,7 +19476,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="15" thickBot="1">
+    <row r="693" spans="1:5" ht="17" thickBot="1">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -19494,7 +19494,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="15" thickBot="1">
+    <row r="694" spans="1:5" ht="17" thickBot="1">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="15" thickBot="1">
+    <row r="695" spans="1:5" ht="17" thickBot="1">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -19530,7 +19530,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="15" thickBot="1">
+    <row r="696" spans="1:5" ht="17" thickBot="1">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -19548,7 +19548,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="15" thickBot="1">
+    <row r="697" spans="1:5" ht="17" thickBot="1">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -19566,7 +19566,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="15" thickBot="1">
+    <row r="698" spans="1:5" ht="17" thickBot="1">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -19584,7 +19584,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="15" thickBot="1">
+    <row r="699" spans="1:5" ht="17" thickBot="1">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -19602,7 +19602,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="15" thickBot="1">
+    <row r="700" spans="1:5" ht="17" thickBot="1">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -19620,7 +19620,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="15" thickBot="1">
+    <row r="701" spans="1:5" ht="17" thickBot="1">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -19638,7 +19638,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="15" thickBot="1">
+    <row r="702" spans="1:5" ht="17" thickBot="1">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -19656,7 +19656,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="15" thickBot="1">
+    <row r="703" spans="1:5" ht="17" thickBot="1">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="15" thickBot="1">
+    <row r="704" spans="1:5" ht="17" thickBot="1">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="15" thickBot="1">
+    <row r="705" spans="1:5" ht="17" thickBot="1">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -19710,7 +19710,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="15" thickBot="1">
+    <row r="706" spans="1:5" ht="17" thickBot="1">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -19743,7 +19743,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="15" thickBot="1">
+    <row r="707" spans="1:5" ht="17" thickBot="1">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -19761,7 +19761,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="15" thickBot="1">
+    <row r="708" spans="1:5" ht="17" thickBot="1">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -19779,7 +19779,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="15" thickBot="1">
+    <row r="709" spans="1:5" ht="17" thickBot="1">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -19797,7 +19797,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="15" thickBot="1">
+    <row r="710" spans="1:5" ht="17" thickBot="1">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -19815,7 +19815,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="15" thickBot="1">
+    <row r="711" spans="1:5" ht="17" thickBot="1">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -19833,7 +19833,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="15" thickBot="1">
+    <row r="712" spans="1:5" ht="17" thickBot="1">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -19851,7 +19851,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="15" thickBot="1">
+    <row r="713" spans="1:5" ht="17" thickBot="1">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -19869,7 +19869,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="15" thickBot="1">
+    <row r="714" spans="1:5" ht="17" thickBot="1">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -19887,7 +19887,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="15" thickBot="1">
+    <row r="715" spans="1:5" ht="17" thickBot="1">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -19905,7 +19905,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="15" thickBot="1">
+    <row r="716" spans="1:5" ht="17" thickBot="1">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -19923,7 +19923,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="15" thickBot="1">
+    <row r="717" spans="1:5" ht="17" thickBot="1">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -19941,7 +19941,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="15" thickBot="1">
+    <row r="718" spans="1:5" ht="17" thickBot="1">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -19959,7 +19959,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="15" thickBot="1">
+    <row r="719" spans="1:5" ht="17" thickBot="1">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -19977,7 +19977,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="15" thickBot="1">
+    <row r="720" spans="1:5" ht="17" thickBot="1">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -19995,7 +19995,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="15" thickBot="1">
+    <row r="721" spans="1:5" ht="17" thickBot="1">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -20013,7 +20013,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="15" thickBot="1">
+    <row r="722" spans="1:5" ht="17" thickBot="1">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -20031,7 +20031,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="15" thickBot="1">
+    <row r="723" spans="1:5" ht="17" thickBot="1">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -20049,7 +20049,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="15" thickBot="1">
+    <row r="724" spans="1:5" ht="17" thickBot="1">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -20067,7 +20067,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="15" thickBot="1">
+    <row r="725" spans="1:5" ht="17" thickBot="1">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -20085,7 +20085,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="15" thickBot="1">
+    <row r="726" spans="1:5" ht="17" thickBot="1">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -20103,7 +20103,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="15" thickBot="1">
+    <row r="727" spans="1:5" ht="17" thickBot="1">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="15" thickBot="1">
+    <row r="728" spans="1:5" ht="17" thickBot="1">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -20139,7 +20139,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="15" thickBot="1">
+    <row r="729" spans="1:5" ht="17" thickBot="1">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -20157,7 +20157,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="15" thickBot="1">
+    <row r="730" spans="1:5" ht="17" thickBot="1">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -20175,7 +20175,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="15" thickBot="1">
+    <row r="731" spans="1:5" ht="17" thickBot="1">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -20193,7 +20193,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="15" thickBot="1">
+    <row r="732" spans="1:5" ht="17" thickBot="1">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -20211,7 +20211,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="15" thickBot="1">
+    <row r="733" spans="1:5" ht="17" thickBot="1">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -20229,7 +20229,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="15" thickBot="1">
+    <row r="734" spans="1:5" ht="17" thickBot="1">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -20247,7 +20247,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="15" thickBot="1">
+    <row r="735" spans="1:5" ht="17" thickBot="1">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -20265,7 +20265,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="15" thickBot="1">
+    <row r="736" spans="1:5" ht="17" thickBot="1">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -20283,7 +20283,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="15" thickBot="1">
+    <row r="737" spans="1:5" ht="17" thickBot="1">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -20301,7 +20301,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="15" thickBot="1">
+    <row r="738" spans="1:5" ht="17" thickBot="1">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -20319,7 +20319,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="15" thickBot="1">
+    <row r="739" spans="1:5" ht="17" thickBot="1">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -20337,7 +20337,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="15" thickBot="1">
+    <row r="740" spans="1:5" ht="17" thickBot="1">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -20355,7 +20355,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="15" thickBot="1">
+    <row r="741" spans="1:5" ht="17" thickBot="1">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -20373,7 +20373,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="15" thickBot="1">
+    <row r="742" spans="1:5" ht="17" thickBot="1">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -20391,7 +20391,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="15" thickBot="1">
+    <row r="743" spans="1:5" ht="17" thickBot="1">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -20409,7 +20409,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="15" thickBot="1">
+    <row r="744" spans="1:5" ht="17" thickBot="1">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -20427,7 +20427,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="15" thickBot="1">
+    <row r="745" spans="1:5" ht="17" thickBot="1">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -20445,7 +20445,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="15" thickBot="1">
+    <row r="746" spans="1:5" ht="17" thickBot="1">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -20463,7 +20463,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="15" thickBot="1">
+    <row r="747" spans="1:5" ht="17" thickBot="1">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -20481,7 +20481,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="15" thickBot="1">
+    <row r="748" spans="1:5" ht="17" thickBot="1">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -20499,7 +20499,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="15" thickBot="1">
+    <row r="749" spans="1:5" ht="17" thickBot="1">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -20517,7 +20517,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="15" thickBot="1">
+    <row r="750" spans="1:5" ht="17" thickBot="1">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -20535,7 +20535,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="15" thickBot="1">
+    <row r="751" spans="1:5" ht="17" thickBot="1">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -20553,7 +20553,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="15" thickBot="1">
+    <row r="752" spans="1:5" ht="17" thickBot="1">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -20571,7 +20571,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="15" thickBot="1">
+    <row r="753" spans="1:5" ht="17" thickBot="1">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -20589,7 +20589,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="15" thickBot="1">
+    <row r="754" spans="1:5" ht="17" thickBot="1">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -20607,7 +20607,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="15" thickBot="1">
+    <row r="755" spans="1:5" ht="17" thickBot="1">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -20625,7 +20625,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="15" thickBot="1">
+    <row r="756" spans="1:5" ht="17" thickBot="1">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -20643,7 +20643,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="15" thickBot="1">
+    <row r="757" spans="1:5" ht="17" thickBot="1">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -20661,7 +20661,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="15" thickBot="1">
+    <row r="758" spans="1:5" ht="17" thickBot="1">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -20679,7 +20679,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="15" thickBot="1">
+    <row r="759" spans="1:5" ht="17" thickBot="1">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -20697,7 +20697,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="15" thickBot="1">
+    <row r="760" spans="1:5" ht="17" thickBot="1">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -20715,7 +20715,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="15" thickBot="1">
+    <row r="761" spans="1:5" ht="17" thickBot="1">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -20733,7 +20733,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="15" thickBot="1">
+    <row r="762" spans="1:5" ht="17" thickBot="1">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -20751,7 +20751,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="15" thickBot="1">
+    <row r="763" spans="1:5" ht="17" thickBot="1">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -20769,7 +20769,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="15" thickBot="1">
+    <row r="764" spans="1:5" ht="17" thickBot="1">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -20787,7 +20787,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="15" thickBot="1">
+    <row r="765" spans="1:5" ht="17" thickBot="1">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -20805,7 +20805,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="15" thickBot="1">
+    <row r="766" spans="1:5" ht="17" thickBot="1">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -20823,7 +20823,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="15" thickBot="1">
+    <row r="767" spans="1:5" ht="17" thickBot="1">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -20841,7 +20841,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="15" thickBot="1">
+    <row r="768" spans="1:5" ht="17" thickBot="1">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -20859,7 +20859,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="15" thickBot="1">
+    <row r="769" spans="1:5" ht="17" thickBot="1">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -20877,7 +20877,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="15" thickBot="1">
+    <row r="770" spans="1:5" ht="17" thickBot="1">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -20910,7 +20910,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="15" thickBot="1">
+    <row r="771" spans="1:5" ht="17" thickBot="1">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -20928,7 +20928,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="15" thickBot="1">
+    <row r="772" spans="1:5" ht="17" thickBot="1">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -20946,7 +20946,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="15" thickBot="1">
+    <row r="773" spans="1:5" ht="17" thickBot="1">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -20964,7 +20964,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="15" thickBot="1">
+    <row r="774" spans="1:5" ht="17" thickBot="1">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -20982,7 +20982,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="15" thickBot="1">
+    <row r="775" spans="1:5" ht="17" thickBot="1">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -21000,7 +21000,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="15" thickBot="1">
+    <row r="776" spans="1:5" ht="17" thickBot="1">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -21018,7 +21018,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="15" thickBot="1">
+    <row r="777" spans="1:5" ht="17" thickBot="1">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -21036,7 +21036,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="15" thickBot="1">
+    <row r="778" spans="1:5" ht="17" thickBot="1">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -21054,7 +21054,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="15" thickBot="1">
+    <row r="779" spans="1:5" ht="17" thickBot="1">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -21072,7 +21072,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="15" thickBot="1">
+    <row r="780" spans="1:5" ht="17" thickBot="1">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -21090,7 +21090,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="15" thickBot="1">
+    <row r="781" spans="1:5" ht="17" thickBot="1">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -21108,7 +21108,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="15" thickBot="1">
+    <row r="782" spans="1:5" ht="17" thickBot="1">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -21126,7 +21126,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="15" thickBot="1">
+    <row r="783" spans="1:5" ht="17" thickBot="1">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -21144,7 +21144,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="15" thickBot="1">
+    <row r="784" spans="1:5" ht="17" thickBot="1">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -21162,7 +21162,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="15" thickBot="1">
+    <row r="785" spans="1:5" ht="17" thickBot="1">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -21180,7 +21180,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="15" thickBot="1">
+    <row r="786" spans="1:5" ht="17" thickBot="1">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -21198,7 +21198,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="15" thickBot="1">
+    <row r="787" spans="1:5" ht="17" thickBot="1">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -21216,7 +21216,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="15" thickBot="1">
+    <row r="788" spans="1:5" ht="17" thickBot="1">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -21234,7 +21234,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="15" thickBot="1">
+    <row r="789" spans="1:5" ht="17" thickBot="1">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -21252,7 +21252,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="15" thickBot="1">
+    <row r="790" spans="1:5" ht="17" thickBot="1">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -21270,7 +21270,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="15" thickBot="1">
+    <row r="791" spans="1:5" ht="17" thickBot="1">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -21288,7 +21288,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="15" thickBot="1">
+    <row r="792" spans="1:5" ht="17" thickBot="1">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -21306,7 +21306,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="15" thickBot="1">
+    <row r="793" spans="1:5" ht="17" thickBot="1">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -21324,7 +21324,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="15" thickBot="1">
+    <row r="794" spans="1:5" ht="17" thickBot="1">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -21342,7 +21342,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="15" thickBot="1">
+    <row r="795" spans="1:5" ht="17" thickBot="1">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -21360,7 +21360,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="15" thickBot="1">
+    <row r="796" spans="1:5" ht="17" thickBot="1">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -21378,7 +21378,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="15" thickBot="1">
+    <row r="797" spans="1:5" ht="17" thickBot="1">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -21396,7 +21396,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="15" thickBot="1">
+    <row r="798" spans="1:5" ht="17" thickBot="1">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -21414,7 +21414,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="15" thickBot="1">
+    <row r="799" spans="1:5" ht="17" thickBot="1">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -21432,7 +21432,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="15" thickBot="1">
+    <row r="800" spans="1:5" ht="17" thickBot="1">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -21450,7 +21450,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="15" thickBot="1">
+    <row r="801" spans="1:5" ht="17" thickBot="1">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -21468,7 +21468,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="15" thickBot="1">
+    <row r="802" spans="1:5" ht="17" thickBot="1">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -21486,7 +21486,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="15" thickBot="1">
+    <row r="803" spans="1:5" ht="17" thickBot="1">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -21504,7 +21504,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="15" thickBot="1">
+    <row r="804" spans="1:5" ht="17" thickBot="1">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -21522,7 +21522,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="15" thickBot="1">
+    <row r="805" spans="1:5" ht="17" thickBot="1">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -21540,7 +21540,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="15" thickBot="1">
+    <row r="806" spans="1:5" ht="17" thickBot="1">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -21558,7 +21558,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="15" thickBot="1">
+    <row r="807" spans="1:5" ht="17" thickBot="1">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -21576,7 +21576,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="15" thickBot="1">
+    <row r="808" spans="1:5" ht="17" thickBot="1">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -21594,7 +21594,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="15" thickBot="1">
+    <row r="809" spans="1:5" ht="17" thickBot="1">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -21612,7 +21612,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="15" thickBot="1">
+    <row r="810" spans="1:5" ht="17" thickBot="1">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -21630,7 +21630,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="15" thickBot="1">
+    <row r="811" spans="1:5" ht="17" thickBot="1">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -21648,7 +21648,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="15" thickBot="1">
+    <row r="812" spans="1:5" ht="17" thickBot="1">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -21666,7 +21666,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="15" thickBot="1">
+    <row r="813" spans="1:5" ht="17" thickBot="1">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -21684,7 +21684,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="15" thickBot="1">
+    <row r="814" spans="1:5" ht="17" thickBot="1">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -21702,7 +21702,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="15" thickBot="1">
+    <row r="815" spans="1:5" ht="17" thickBot="1">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -21720,7 +21720,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="15" thickBot="1">
+    <row r="816" spans="1:5" ht="17" thickBot="1">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -21738,7 +21738,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="15" thickBot="1">
+    <row r="817" spans="1:5" ht="17" thickBot="1">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -21756,7 +21756,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="15" thickBot="1">
+    <row r="818" spans="1:5" ht="17" thickBot="1">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -21774,7 +21774,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="15" thickBot="1">
+    <row r="819" spans="1:5" ht="17" thickBot="1">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -21792,7 +21792,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="15" thickBot="1">
+    <row r="820" spans="1:5" ht="17" thickBot="1">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -21810,7 +21810,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="15" thickBot="1">
+    <row r="821" spans="1:5" ht="17" thickBot="1">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -21828,7 +21828,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="15" thickBot="1">
+    <row r="822" spans="1:5" ht="17" thickBot="1">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -21846,7 +21846,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="15" thickBot="1">
+    <row r="823" spans="1:5" ht="17" thickBot="1">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -21864,7 +21864,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="15" thickBot="1">
+    <row r="824" spans="1:5" ht="17" thickBot="1">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -21882,7 +21882,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="15" thickBot="1">
+    <row r="825" spans="1:5" ht="17" thickBot="1">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -21900,7 +21900,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="15" thickBot="1">
+    <row r="826" spans="1:5" ht="17" thickBot="1">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -21918,7 +21918,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="15" thickBot="1">
+    <row r="827" spans="1:5" ht="17" thickBot="1">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -21936,7 +21936,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="15" thickBot="1">
+    <row r="828" spans="1:5" ht="17" thickBot="1">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -21954,7 +21954,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="15" thickBot="1">
+    <row r="829" spans="1:5" ht="17" thickBot="1">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -21972,7 +21972,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="15" thickBot="1">
+    <row r="830" spans="1:5" ht="17" thickBot="1">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -21990,7 +21990,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="15" thickBot="1">
+    <row r="831" spans="1:5" ht="17" thickBot="1">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -22008,7 +22008,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="15" thickBot="1">
+    <row r="832" spans="1:5" ht="17" thickBot="1">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -22026,7 +22026,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="15" thickBot="1">
+    <row r="833" spans="1:5" ht="17" thickBot="1">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -22044,7 +22044,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="15" thickBot="1">
+    <row r="834" spans="1:5" ht="17" thickBot="1">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -22077,7 +22077,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="15" thickBot="1">
+    <row r="835" spans="1:5" ht="17" thickBot="1">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -22095,7 +22095,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="15" thickBot="1">
+    <row r="836" spans="1:5" ht="17" thickBot="1">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -22113,7 +22113,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="15" thickBot="1">
+    <row r="837" spans="1:5" ht="17" thickBot="1">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -22131,7 +22131,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="15" thickBot="1">
+    <row r="838" spans="1:5" ht="17" thickBot="1">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -22149,7 +22149,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="15" thickBot="1">
+    <row r="839" spans="1:5" ht="17" thickBot="1">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -22167,7 +22167,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="15" thickBot="1">
+    <row r="840" spans="1:5" ht="17" thickBot="1">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -22185,7 +22185,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="15" thickBot="1">
+    <row r="841" spans="1:5" ht="17" thickBot="1">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -22203,7 +22203,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="15" thickBot="1">
+    <row r="842" spans="1:5" ht="17" thickBot="1">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -22221,7 +22221,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="15" thickBot="1">
+    <row r="843" spans="1:5" ht="17" thickBot="1">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -22239,7 +22239,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="15" thickBot="1">
+    <row r="844" spans="1:5" ht="17" thickBot="1">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -22257,7 +22257,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="15" thickBot="1">
+    <row r="845" spans="1:5" ht="17" thickBot="1">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -22275,7 +22275,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="15" thickBot="1">
+    <row r="846" spans="1:5" ht="17" thickBot="1">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -22293,7 +22293,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="15" thickBot="1">
+    <row r="847" spans="1:5" ht="17" thickBot="1">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -22311,7 +22311,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="15" thickBot="1">
+    <row r="848" spans="1:5" ht="17" thickBot="1">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -22329,7 +22329,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="15" thickBot="1">
+    <row r="849" spans="1:5" ht="17" thickBot="1">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -22347,7 +22347,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="15" thickBot="1">
+    <row r="850" spans="1:5" ht="17" thickBot="1">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -22365,7 +22365,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="15" thickBot="1">
+    <row r="851" spans="1:5" ht="17" thickBot="1">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -22383,7 +22383,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="15" thickBot="1">
+    <row r="852" spans="1:5" ht="17" thickBot="1">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -22401,7 +22401,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="15" thickBot="1">
+    <row r="853" spans="1:5" ht="17" thickBot="1">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -22419,7 +22419,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="15" thickBot="1">
+    <row r="854" spans="1:5" ht="17" thickBot="1">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -22437,7 +22437,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="15" thickBot="1">
+    <row r="855" spans="1:5" ht="17" thickBot="1">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -22455,7 +22455,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="15" thickBot="1">
+    <row r="856" spans="1:5" ht="17" thickBot="1">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -22473,7 +22473,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="15" thickBot="1">
+    <row r="857" spans="1:5" ht="17" thickBot="1">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -22491,7 +22491,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="15" thickBot="1">
+    <row r="858" spans="1:5" ht="17" thickBot="1">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -22509,7 +22509,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="15" thickBot="1">
+    <row r="859" spans="1:5" ht="17" thickBot="1">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -22527,7 +22527,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="15" thickBot="1">
+    <row r="860" spans="1:5" ht="17" thickBot="1">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -22545,7 +22545,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="15" thickBot="1">
+    <row r="861" spans="1:5" ht="17" thickBot="1">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -22563,7 +22563,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="15" thickBot="1">
+    <row r="862" spans="1:5" ht="17" thickBot="1">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -22581,7 +22581,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="15" thickBot="1">
+    <row r="863" spans="1:5" ht="17" thickBot="1">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -22599,7 +22599,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="15" thickBot="1">
+    <row r="864" spans="1:5" ht="17" thickBot="1">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -22617,7 +22617,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="15" thickBot="1">
+    <row r="865" spans="1:5" ht="17" thickBot="1">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -22635,7 +22635,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="15" thickBot="1">
+    <row r="866" spans="1:5" ht="17" thickBot="1">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -22653,7 +22653,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="15" thickBot="1">
+    <row r="867" spans="1:5" ht="17" thickBot="1">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -22671,7 +22671,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="15" thickBot="1">
+    <row r="868" spans="1:5" ht="17" thickBot="1">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -22689,7 +22689,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="15" thickBot="1">
+    <row r="869" spans="1:5" ht="17" thickBot="1">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -22707,7 +22707,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="15" thickBot="1">
+    <row r="870" spans="1:5" ht="17" thickBot="1">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -22725,7 +22725,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="15" thickBot="1">
+    <row r="871" spans="1:5" ht="17" thickBot="1">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -22743,7 +22743,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="15" thickBot="1">
+    <row r="872" spans="1:5" ht="17" thickBot="1">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -22761,7 +22761,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="15" thickBot="1">
+    <row r="873" spans="1:5" ht="17" thickBot="1">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -22779,7 +22779,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="15" thickBot="1">
+    <row r="874" spans="1:5" ht="17" thickBot="1">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -22797,7 +22797,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="15" thickBot="1">
+    <row r="875" spans="1:5" ht="17" thickBot="1">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -22815,7 +22815,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="15" thickBot="1">
+    <row r="876" spans="1:5" ht="17" thickBot="1">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -22833,7 +22833,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="15" thickBot="1">
+    <row r="877" spans="1:5" ht="17" thickBot="1">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -22851,7 +22851,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="15" thickBot="1">
+    <row r="878" spans="1:5" ht="17" thickBot="1">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -22884,7 +22884,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="15" thickBot="1">
+    <row r="879" spans="1:5" ht="17" thickBot="1">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -22917,7 +22917,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="15" thickBot="1">
+    <row r="880" spans="1:5" ht="17" thickBot="1">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -22950,7 +22950,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="15" thickBot="1">
+    <row r="881" spans="1:5" ht="17" thickBot="1">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -22968,7 +22968,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="15" thickBot="1">
+    <row r="882" spans="1:5" ht="17" thickBot="1">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -23001,7 +23001,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="15" thickBot="1">
+    <row r="883" spans="1:5" ht="17" thickBot="1">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -23034,7 +23034,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="15" thickBot="1">
+    <row r="884" spans="1:5" ht="17" thickBot="1">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
@@ -23052,7 +23052,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="15" thickBot="1">
+    <row r="885" spans="1:5" ht="17" thickBot="1">
       <c r="A885" s="15">
         <v>46088</v>
       </c>
@@ -23070,7 +23070,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5">
+    <row r="886" spans="1:5" ht="16">
       <c r="A886" s="8">
         <v>46102</v>
       </c>
@@ -23088,7 +23088,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5">
+    <row r="887" spans="1:5" ht="16">
       <c r="A887" s="8">
         <v>46109</v>
       </c>
@@ -23106,7 +23106,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5">
+    <row r="888" spans="1:5" ht="16">
       <c r="A888" s="8">
         <v>46116</v>
       </c>
@@ -23124,7 +23124,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5">
+    <row r="889" spans="1:5" ht="16">
       <c r="A889" s="8">
         <v>46123</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>500040</v>
       </c>
     </row>
-    <row r="890" spans="1:5">
+    <row r="890" spans="1:5" ht="16">
       <c r="A890" s="8">
         <v>46130</v>
       </c>
@@ -23160,7 +23160,7 @@
         <v>508303</v>
       </c>
     </row>
-    <row r="891" spans="1:5">
+    <row r="891" spans="1:5" ht="16">
       <c r="A891" s="8">
         <v>46137</v>
       </c>
@@ -23178,7 +23178,7 @@
         <v>511616</v>
       </c>
     </row>
-    <row r="892" spans="1:5">
+    <row r="892" spans="1:5" ht="16">
       <c r="A892" s="8">
         <v>46144</v>
       </c>
@@ -23196,7 +23196,7 @@
         <v>518773</v>
       </c>
     </row>
-    <row r="893" spans="1:5">
+    <row r="893" spans="1:5" ht="16">
       <c r="A893" s="8">
         <v>46151</v>
       </c>
@@ -23229,7 +23229,7 @@
         <v>513755</v>
       </c>
     </row>
-    <row r="894" spans="1:5">
+    <row r="894" spans="1:5" ht="16">
       <c r="A894" s="8">
         <v>46158</v>
       </c>
@@ -23247,7 +23247,7 @@
         <v>511216</v>
       </c>
     </row>
-    <row r="895" spans="1:5">
+    <row r="895" spans="1:5" ht="16">
       <c r="A895" s="8">
         <v>46165</v>
       </c>
@@ -23265,7 +23265,7 @@
         <v>523574</v>
       </c>
     </row>
-    <row r="896" spans="1:5">
+    <row r="896" spans="1:5" ht="16">
       <c r="A896" s="8">
         <v>46172</v>
       </c>
@@ -23298,7 +23298,7 @@
         <v>492795</v>
       </c>
     </row>
-    <row r="897" spans="1:5">
+    <row r="897" spans="1:5" ht="16">
       <c r="A897" s="8">
         <v>46179</v>
       </c>
@@ -23316,7 +23316,7 @@
         <v>521804</v>
       </c>
     </row>
-    <row r="898" spans="1:5">
+    <row r="898" spans="1:5" ht="16">
       <c r="A898" s="8">
         <v>46186</v>
       </c>
@@ -23334,7 +23334,7 @@
         <v>520406</v>
       </c>
     </row>
-    <row r="899" spans="1:5">
+    <row r="899" spans="1:5" ht="16">
       <c r="A899" s="8">
         <v>46193</v>
       </c>
@@ -23367,7 +23367,7 @@
         <v>521998</v>
       </c>
     </row>
-    <row r="900" spans="1:5">
+    <row r="900" spans="1:5" ht="16">
       <c r="A900" s="8">
         <v>46200</v>
       </c>
@@ -23385,7 +23385,7 @@
         <v>525474</v>
       </c>
     </row>
-    <row r="901" spans="1:5">
+    <row r="901" spans="1:5" ht="16">
       <c r="A901" s="8">
         <v>46207</v>
       </c>
@@ -23418,7 +23418,7 @@
         <v>482121</v>
       </c>
     </row>
-    <row r="902" spans="1:5">
+    <row r="902" spans="1:5" ht="16">
       <c r="A902" s="8">
         <v>46214</v>
       </c>
@@ -23449,7 +23449,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23460,9 +23460,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7676CC-CE1C-3E4C-846C-9AA01D55E504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494D759C-A3D6-4712-BD67-50720B4439E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11440" yWindow="600" windowWidth="11700" windowHeight="14740" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -86,12 +86,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -189,7 +189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -206,68 +206,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -285,7 +285,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6534,9 +6534,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6574,7 +6574,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6680,7 +6680,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6822,7 +6822,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6830,18 +6830,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E902"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
+  <dimension ref="A1:E903"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.1640625" style="6"/>
+    <col min="3" max="3" width="10.77734375" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="16">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="16">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="16">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="16">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -7122,7 +7122,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="16">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="16">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="16">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="16">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="16">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="16">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="16">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="16">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="16">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="16">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="16">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="16">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="16">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="16">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="16">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="16">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="16">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="16">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="16">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="16">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="16">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="16">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="16">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="16">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="16">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="16">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="16">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="16">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="16">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -7644,7 +7644,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="16">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="16">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="16">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="16">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="16">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="16">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="16">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="16">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="16">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="16">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="16">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="16">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -7860,7 +7860,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="16">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="16">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -7896,7 +7896,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="16">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="16">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="16">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="16">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="16">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="16">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="16">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="16">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -8040,7 +8040,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="16">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="16">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="16">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="16">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -8127,7 +8127,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="16">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="16">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="16">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -8181,7 +8181,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="16">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="16">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="16">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="16">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="16">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -8271,7 +8271,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="16">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="16">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="16">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="16">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="16">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="16">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="16">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -8397,7 +8397,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="16">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="16">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="16">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="16">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="16">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="16">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="16">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="16">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -8541,7 +8541,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="16">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -8559,7 +8559,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="16">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="16">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="16">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="16">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="16">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="16">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="16">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="17" thickBot="1">
+    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="17" thickBot="1">
+    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="17" thickBot="1">
+    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="17" thickBot="1">
+    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="17" thickBot="1">
+    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="17" thickBot="1">
+    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="17" thickBot="1">
+    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="17" thickBot="1">
+    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -8829,7 +8829,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="17" thickBot="1">
+    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="17" thickBot="1">
+    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="17" thickBot="1">
+    <row r="111" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="17" thickBot="1">
+    <row r="112" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="17" thickBot="1">
+    <row r="113" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -8919,7 +8919,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="17" thickBot="1">
+    <row r="114" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -8937,7 +8937,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="17" thickBot="1">
+    <row r="115" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="17" thickBot="1">
+    <row r="116" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="17" thickBot="1">
+    <row r="117" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="17" thickBot="1">
+    <row r="118" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="17" thickBot="1">
+    <row r="119" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="17" thickBot="1">
+    <row r="120" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="17" thickBot="1">
+    <row r="121" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="17" thickBot="1">
+    <row r="122" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="17" thickBot="1">
+    <row r="123" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="17" thickBot="1">
+    <row r="124" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -9117,7 +9117,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="17" thickBot="1">
+    <row r="125" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="17" thickBot="1">
+    <row r="126" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="17" thickBot="1">
+    <row r="127" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="17" thickBot="1">
+    <row r="128" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -9189,7 +9189,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="17" thickBot="1">
+    <row r="129" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -9207,7 +9207,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="17" thickBot="1">
+    <row r="130" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="17" thickBot="1">
+    <row r="131" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="17" thickBot="1">
+    <row r="132" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="17" thickBot="1">
+    <row r="133" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="17" thickBot="1">
+    <row r="134" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="17" thickBot="1">
+    <row r="135" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="17" thickBot="1">
+    <row r="136" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="17" thickBot="1">
+    <row r="137" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="17" thickBot="1">
+    <row r="138" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="17" thickBot="1">
+    <row r="139" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="17" thickBot="1">
+    <row r="140" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="17" thickBot="1">
+    <row r="141" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="17" thickBot="1">
+    <row r="142" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -9456,7 +9456,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="17" thickBot="1">
+    <row r="143" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="17" thickBot="1">
+    <row r="144" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="17" thickBot="1">
+    <row r="145" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="17" thickBot="1">
+    <row r="146" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="17" thickBot="1">
+    <row r="147" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="17" thickBot="1">
+    <row r="148" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="17" thickBot="1">
+    <row r="149" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -9582,7 +9582,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="17" thickBot="1">
+    <row r="150" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="17" thickBot="1">
+    <row r="151" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="17" thickBot="1">
+    <row r="152" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="17" thickBot="1">
+    <row r="153" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="17" thickBot="1">
+    <row r="154" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="17" thickBot="1">
+    <row r="155" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="17" thickBot="1">
+    <row r="156" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -9708,7 +9708,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="17" thickBot="1">
+    <row r="157" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -9726,7 +9726,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="17" thickBot="1">
+    <row r="158" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="17" thickBot="1">
+    <row r="159" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -9762,7 +9762,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="17" thickBot="1">
+    <row r="160" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="17" thickBot="1">
+    <row r="161" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="17" thickBot="1">
+    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="17" thickBot="1">
+    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="17" thickBot="1">
+    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="17" thickBot="1">
+    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="17" thickBot="1">
+    <row r="166" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="17" thickBot="1">
+    <row r="167" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="17" thickBot="1">
+    <row r="168" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="17" thickBot="1">
+    <row r="169" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="17" thickBot="1">
+    <row r="170" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -9960,7 +9960,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="17" thickBot="1">
+    <row r="171" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -9978,7 +9978,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="17" thickBot="1">
+    <row r="172" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -9996,7 +9996,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="17" thickBot="1">
+    <row r="173" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="17" thickBot="1">
+    <row r="174" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -10032,7 +10032,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="17" thickBot="1">
+    <row r="175" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="17" thickBot="1">
+    <row r="176" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="17" thickBot="1">
+    <row r="177" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="17" thickBot="1">
+    <row r="178" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="17" thickBot="1">
+    <row r="179" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="17" thickBot="1">
+    <row r="180" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -10140,7 +10140,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="17" thickBot="1">
+    <row r="181" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="17" thickBot="1">
+    <row r="182" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -10176,7 +10176,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="17" thickBot="1">
+    <row r="183" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="17" thickBot="1">
+    <row r="184" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -10212,7 +10212,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="17" thickBot="1">
+    <row r="185" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="17" thickBot="1">
+    <row r="186" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -10248,7 +10248,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="17" thickBot="1">
+    <row r="187" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="17" thickBot="1">
+    <row r="188" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="17" thickBot="1">
+    <row r="189" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="17" thickBot="1">
+    <row r="190" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -10320,7 +10320,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="17" thickBot="1">
+    <row r="191" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -10338,7 +10338,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="17" thickBot="1">
+    <row r="192" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -10356,7 +10356,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="17" thickBot="1">
+    <row r="193" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="17" thickBot="1">
+    <row r="194" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="17" thickBot="1">
+    <row r="195" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="17" thickBot="1">
+    <row r="196" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -10443,7 +10443,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="17" thickBot="1">
+    <row r="197" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -10461,7 +10461,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="17" thickBot="1">
+    <row r="198" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="17" thickBot="1">
+    <row r="199" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -10497,7 +10497,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="17" thickBot="1">
+    <row r="200" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -10515,7 +10515,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="17" thickBot="1">
+    <row r="201" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="17" thickBot="1">
+    <row r="202" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="17" thickBot="1">
+    <row r="203" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -10569,7 +10569,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="17" thickBot="1">
+    <row r="204" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -10587,7 +10587,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="17" thickBot="1">
+    <row r="205" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="17" thickBot="1">
+    <row r="206" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="17" thickBot="1">
+    <row r="207" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -10641,7 +10641,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="17" thickBot="1">
+    <row r="208" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -10659,7 +10659,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="17" thickBot="1">
+    <row r="209" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -10677,7 +10677,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="17" thickBot="1">
+    <row r="210" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="17" thickBot="1">
+    <row r="211" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="17" thickBot="1">
+    <row r="212" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -10731,7 +10731,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="17" thickBot="1">
+    <row r="213" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="17" thickBot="1">
+    <row r="214" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -10767,7 +10767,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="17" thickBot="1">
+    <row r="215" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="17" thickBot="1">
+    <row r="216" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="17" thickBot="1">
+    <row r="217" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="17" thickBot="1">
+    <row r="218" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -10839,7 +10839,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="17" thickBot="1">
+    <row r="219" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="17" thickBot="1">
+    <row r="220" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="17" thickBot="1">
+    <row r="221" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="17" thickBot="1">
+    <row r="222" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="17" thickBot="1">
+    <row r="223" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -10929,7 +10929,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="17" thickBot="1">
+    <row r="224" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="17" thickBot="1">
+    <row r="225" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="17" thickBot="1">
+    <row r="226" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -10983,7 +10983,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="17" thickBot="1">
+    <row r="227" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -11001,7 +11001,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="17" thickBot="1">
+    <row r="228" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="17" thickBot="1">
+    <row r="229" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="17" thickBot="1">
+    <row r="230" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -11055,7 +11055,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="17" thickBot="1">
+    <row r="231" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="17" thickBot="1">
+    <row r="232" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -11091,7 +11091,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="17" thickBot="1">
+    <row r="233" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -11109,7 +11109,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="17" thickBot="1">
+    <row r="234" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="17" thickBot="1">
+    <row r="235" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="17" thickBot="1">
+    <row r="236" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -11163,7 +11163,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="17" thickBot="1">
+    <row r="237" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -11181,7 +11181,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="17" thickBot="1">
+    <row r="238" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -11199,7 +11199,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="17" thickBot="1">
+    <row r="239" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="17" thickBot="1">
+    <row r="240" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -11235,7 +11235,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="17" thickBot="1">
+    <row r="241" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="17" thickBot="1">
+    <row r="242" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -11271,7 +11271,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="17" thickBot="1">
+    <row r="243" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="17" thickBot="1">
+    <row r="244" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -11307,7 +11307,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="17" thickBot="1">
+    <row r="245" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="17" thickBot="1">
+    <row r="246" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -11343,7 +11343,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="17" thickBot="1">
+    <row r="247" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -11361,7 +11361,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="17" thickBot="1">
+    <row r="248" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -11379,7 +11379,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="17" thickBot="1">
+    <row r="249" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -11397,7 +11397,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="17" thickBot="1">
+    <row r="250" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -11415,7 +11415,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="17" thickBot="1">
+    <row r="251" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="17" thickBot="1">
+    <row r="252" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -11451,7 +11451,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="17" thickBot="1">
+    <row r="253" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -11469,7 +11469,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="17" thickBot="1">
+    <row r="254" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="17" thickBot="1">
+    <row r="255" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -11505,7 +11505,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="17" thickBot="1">
+    <row r="256" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -11523,7 +11523,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="17" thickBot="1">
+    <row r="257" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="17" thickBot="1">
+    <row r="258" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -11574,7 +11574,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="17" thickBot="1">
+    <row r="259" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="17" thickBot="1">
+    <row r="260" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -11610,7 +11610,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="17" thickBot="1">
+    <row r="261" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="17" thickBot="1">
+    <row r="262" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -11646,7 +11646,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="17" thickBot="1">
+    <row r="263" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="17" thickBot="1">
+    <row r="264" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="17" thickBot="1">
+    <row r="265" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -11700,7 +11700,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="17" thickBot="1">
+    <row r="266" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="17" thickBot="1">
+    <row r="267" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -11736,7 +11736,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="17" thickBot="1">
+    <row r="268" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="17" thickBot="1">
+    <row r="269" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -11772,7 +11772,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="17" thickBot="1">
+    <row r="270" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -11790,7 +11790,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="17" thickBot="1">
+    <row r="271" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -11808,7 +11808,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="17" thickBot="1">
+    <row r="272" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -11826,7 +11826,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="17" thickBot="1">
+    <row r="273" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -11844,7 +11844,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="17" thickBot="1">
+    <row r="274" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="17" thickBot="1">
+    <row r="275" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="17" thickBot="1">
+    <row r="276" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="17" thickBot="1">
+    <row r="277" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="17" thickBot="1">
+    <row r="278" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -11934,7 +11934,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="17" thickBot="1">
+    <row r="279" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="17" thickBot="1">
+    <row r="280" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -11970,7 +11970,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="17" thickBot="1">
+    <row r="281" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="17" thickBot="1">
+    <row r="282" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="17" thickBot="1">
+    <row r="283" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="17" thickBot="1">
+    <row r="284" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="17" thickBot="1">
+    <row r="285" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -12060,7 +12060,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="17" thickBot="1">
+    <row r="286" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -12078,7 +12078,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="17" thickBot="1">
+    <row r="287" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="17" thickBot="1">
+    <row r="288" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -12114,7 +12114,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="17" thickBot="1">
+    <row r="289" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="17" thickBot="1">
+    <row r="290" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -12150,7 +12150,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="17" thickBot="1">
+    <row r="291" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="17" thickBot="1">
+    <row r="292" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -12186,7 +12186,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="17" thickBot="1">
+    <row r="293" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="17" thickBot="1">
+    <row r="294" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="17" thickBot="1">
+    <row r="295" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -12240,7 +12240,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="17" thickBot="1">
+    <row r="296" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="17" thickBot="1">
+    <row r="297" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -12276,7 +12276,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="17" thickBot="1">
+    <row r="298" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="17" thickBot="1">
+    <row r="299" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="17" thickBot="1">
+    <row r="300" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -12330,7 +12330,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="17" thickBot="1">
+    <row r="301" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -12348,7 +12348,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="17" thickBot="1">
+    <row r="302" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="17" thickBot="1">
+    <row r="303" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -12384,7 +12384,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="17" thickBot="1">
+    <row r="304" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="17" thickBot="1">
+    <row r="305" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -12420,7 +12420,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="17" thickBot="1">
+    <row r="306" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="17" thickBot="1">
+    <row r="307" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="17" thickBot="1">
+    <row r="308" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -12474,7 +12474,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="17" thickBot="1">
+    <row r="309" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="17" thickBot="1">
+    <row r="310" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="17" thickBot="1">
+    <row r="311" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -12528,7 +12528,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="17" thickBot="1">
+    <row r="312" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -12546,7 +12546,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="17" thickBot="1">
+    <row r="313" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="17" thickBot="1">
+    <row r="314" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -12582,7 +12582,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="17" thickBot="1">
+    <row r="315" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -12600,7 +12600,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="17" thickBot="1">
+    <row r="316" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -12618,7 +12618,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="17" thickBot="1">
+    <row r="317" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="17" thickBot="1">
+    <row r="318" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="17" thickBot="1">
+    <row r="319" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -12672,7 +12672,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="17" thickBot="1">
+    <row r="320" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -12690,7 +12690,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="17" thickBot="1">
+    <row r="321" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="17" thickBot="1">
+    <row r="322" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="17" thickBot="1">
+    <row r="323" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -12759,7 +12759,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="17" thickBot="1">
+    <row r="324" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -12777,7 +12777,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="17" thickBot="1">
+    <row r="325" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="17" thickBot="1">
+    <row r="326" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="17" thickBot="1">
+    <row r="327" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="17" thickBot="1">
+    <row r="328" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -12849,7 +12849,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="17" thickBot="1">
+    <row r="329" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -12867,7 +12867,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="17" thickBot="1">
+    <row r="330" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="17" thickBot="1">
+    <row r="331" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -12903,7 +12903,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="17" thickBot="1">
+    <row r="332" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -12921,7 +12921,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="17" thickBot="1">
+    <row r="333" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="17" thickBot="1">
+    <row r="334" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -12957,7 +12957,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="17" thickBot="1">
+    <row r="335" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -12975,7 +12975,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="17" thickBot="1">
+    <row r="336" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -12993,7 +12993,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="17" thickBot="1">
+    <row r="337" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -13011,7 +13011,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="17" thickBot="1">
+    <row r="338" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -13029,7 +13029,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="17" thickBot="1">
+    <row r="339" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -13047,7 +13047,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="17" thickBot="1">
+    <row r="340" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -13065,7 +13065,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="17" thickBot="1">
+    <row r="341" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -13083,7 +13083,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="17" thickBot="1">
+    <row r="342" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -13101,7 +13101,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="17" thickBot="1">
+    <row r="343" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="17" thickBot="1">
+    <row r="344" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -13137,7 +13137,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="17" thickBot="1">
+    <row r="345" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="17" thickBot="1">
+    <row r="346" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="17" thickBot="1">
+    <row r="347" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -13191,7 +13191,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="17" thickBot="1">
+    <row r="348" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="17" thickBot="1">
+    <row r="349" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -13227,7 +13227,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="17" thickBot="1">
+    <row r="350" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="17" thickBot="1">
+    <row r="351" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -13263,7 +13263,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="17" thickBot="1">
+    <row r="352" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -13281,7 +13281,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="17" thickBot="1">
+    <row r="353" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="17" thickBot="1">
+    <row r="354" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -13317,7 +13317,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="17" thickBot="1">
+    <row r="355" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="17" thickBot="1">
+    <row r="356" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -13353,7 +13353,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="17" thickBot="1">
+    <row r="357" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -13371,7 +13371,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="17" thickBot="1">
+    <row r="358" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -13389,7 +13389,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="17" thickBot="1">
+    <row r="359" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -13407,7 +13407,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="17" thickBot="1">
+    <row r="360" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -13425,7 +13425,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="17" thickBot="1">
+    <row r="361" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -13443,7 +13443,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="17" thickBot="1">
+    <row r="362" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -13461,7 +13461,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="17" thickBot="1">
+    <row r="363" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -13479,7 +13479,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="17" thickBot="1">
+    <row r="364" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -13497,7 +13497,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="17" thickBot="1">
+    <row r="365" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -13515,7 +13515,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="17" thickBot="1">
+    <row r="366" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="17" thickBot="1">
+    <row r="367" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -13551,7 +13551,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="17" thickBot="1">
+    <row r="368" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -13569,7 +13569,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="17" thickBot="1">
+    <row r="369" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -13587,7 +13587,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="17" thickBot="1">
+    <row r="370" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -13605,7 +13605,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="17" thickBot="1">
+    <row r="371" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -13623,7 +13623,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="17" thickBot="1">
+    <row r="372" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -13641,7 +13641,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="17" thickBot="1">
+    <row r="373" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -13659,7 +13659,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="17" thickBot="1">
+    <row r="374" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -13677,7 +13677,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="17" thickBot="1">
+    <row r="375" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="17" thickBot="1">
+    <row r="376" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -13713,7 +13713,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="17" thickBot="1">
+    <row r="377" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -13731,7 +13731,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="17" thickBot="1">
+    <row r="378" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -13749,7 +13749,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="17" thickBot="1">
+    <row r="379" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -13767,7 +13767,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="17" thickBot="1">
+    <row r="380" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -13785,7 +13785,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="17" thickBot="1">
+    <row r="381" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -13803,7 +13803,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="17" thickBot="1">
+    <row r="382" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -13821,7 +13821,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="17" thickBot="1">
+    <row r="383" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -13839,7 +13839,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="17" thickBot="1">
+    <row r="384" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -13857,7 +13857,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="17" thickBot="1">
+    <row r="385" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -13875,7 +13875,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="17" thickBot="1">
+    <row r="386" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="17" thickBot="1">
+    <row r="387" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -13926,7 +13926,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="17" thickBot="1">
+    <row r="388" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -13944,7 +13944,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="17" thickBot="1">
+    <row r="389" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="17" thickBot="1">
+    <row r="390" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -13980,7 +13980,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="17" thickBot="1">
+    <row r="391" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -13998,7 +13998,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="17" thickBot="1">
+    <row r="392" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="17" thickBot="1">
+    <row r="393" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -14034,7 +14034,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="17" thickBot="1">
+    <row r="394" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -14052,7 +14052,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="17" thickBot="1">
+    <row r="395" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -14070,7 +14070,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="17" thickBot="1">
+    <row r="396" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -14088,7 +14088,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="17" thickBot="1">
+    <row r="397" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -14106,7 +14106,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="17" thickBot="1">
+    <row r="398" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -14124,7 +14124,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="17" thickBot="1">
+    <row r="399" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="17" thickBot="1">
+    <row r="400" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -14160,7 +14160,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="17" thickBot="1">
+    <row r="401" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -14178,7 +14178,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="17" thickBot="1">
+    <row r="402" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -14196,7 +14196,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="17" thickBot="1">
+    <row r="403" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -14214,7 +14214,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="17" thickBot="1">
+    <row r="404" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -14232,7 +14232,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="17" thickBot="1">
+    <row r="405" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -14250,7 +14250,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="17" thickBot="1">
+    <row r="406" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -14268,7 +14268,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="17" thickBot="1">
+    <row r="407" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -14286,7 +14286,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="17" thickBot="1">
+    <row r="408" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -14304,7 +14304,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="17" thickBot="1">
+    <row r="409" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="17" thickBot="1">
+    <row r="410" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="17" thickBot="1">
+    <row r="411" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -14358,7 +14358,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="17" thickBot="1">
+    <row r="412" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -14376,7 +14376,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="17" thickBot="1">
+    <row r="413" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -14394,7 +14394,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="17" thickBot="1">
+    <row r="414" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -14412,7 +14412,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="17" thickBot="1">
+    <row r="415" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -14430,7 +14430,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="17" thickBot="1">
+    <row r="416" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -14448,7 +14448,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="17" thickBot="1">
+    <row r="417" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="17" thickBot="1">
+    <row r="418" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="17" thickBot="1">
+    <row r="419" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -14502,7 +14502,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="17" thickBot="1">
+    <row r="420" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -14520,7 +14520,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="17" thickBot="1">
+    <row r="421" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="17" thickBot="1">
+    <row r="422" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -14556,7 +14556,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="17" thickBot="1">
+    <row r="423" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -14574,7 +14574,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="17" thickBot="1">
+    <row r="424" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="17" thickBot="1">
+    <row r="425" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -14610,7 +14610,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="17" thickBot="1">
+    <row r="426" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -14628,7 +14628,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="17" thickBot="1">
+    <row r="427" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -14646,7 +14646,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="17" thickBot="1">
+    <row r="428" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="17" thickBot="1">
+    <row r="429" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="17" thickBot="1">
+    <row r="430" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -14700,7 +14700,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="17" thickBot="1">
+    <row r="431" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="17" thickBot="1">
+    <row r="432" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -14736,7 +14736,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="17" thickBot="1">
+    <row r="433" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -14754,7 +14754,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="17" thickBot="1">
+    <row r="434" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -14772,7 +14772,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="17" thickBot="1">
+    <row r="435" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -14790,7 +14790,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="17" thickBot="1">
+    <row r="436" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -14808,7 +14808,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="17" thickBot="1">
+    <row r="437" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -14826,7 +14826,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="17" thickBot="1">
+    <row r="438" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -14844,7 +14844,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="17" thickBot="1">
+    <row r="439" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -14862,7 +14862,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="17" thickBot="1">
+    <row r="440" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -14880,7 +14880,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="17" thickBot="1">
+    <row r="441" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="17" thickBot="1">
+    <row r="442" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -14916,7 +14916,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="17" thickBot="1">
+    <row r="443" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -14934,7 +14934,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="17" thickBot="1">
+    <row r="444" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -14952,7 +14952,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="17" thickBot="1">
+    <row r="445" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -14970,7 +14970,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="17" thickBot="1">
+    <row r="446" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -14988,7 +14988,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="17" thickBot="1">
+    <row r="447" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -15006,7 +15006,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="17" thickBot="1">
+    <row r="448" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -15024,7 +15024,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="17" thickBot="1">
+    <row r="449" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -15042,7 +15042,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="17" thickBot="1">
+    <row r="450" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -15075,7 +15075,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="17" thickBot="1">
+    <row r="451" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -15093,7 +15093,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="17" thickBot="1">
+    <row r="452" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -15111,7 +15111,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="17" thickBot="1">
+    <row r="453" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -15129,7 +15129,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="17" thickBot="1">
+    <row r="454" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -15147,7 +15147,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="17" thickBot="1">
+    <row r="455" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -15165,7 +15165,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="17" thickBot="1">
+    <row r="456" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -15183,7 +15183,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="17" thickBot="1">
+    <row r="457" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -15201,7 +15201,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="17" thickBot="1">
+    <row r="458" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -15219,7 +15219,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="17" thickBot="1">
+    <row r="459" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -15237,7 +15237,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="17" thickBot="1">
+    <row r="460" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -15255,7 +15255,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="17" thickBot="1">
+    <row r="461" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -15273,7 +15273,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="17" thickBot="1">
+    <row r="462" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -15291,7 +15291,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="17" thickBot="1">
+    <row r="463" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -15309,7 +15309,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="17" thickBot="1">
+    <row r="464" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="17" thickBot="1">
+    <row r="465" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -15345,7 +15345,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="17" thickBot="1">
+    <row r="466" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -15363,7 +15363,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="17" thickBot="1">
+    <row r="467" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -15381,7 +15381,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="17" thickBot="1">
+    <row r="468" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -15399,7 +15399,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="17" thickBot="1">
+    <row r="469" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -15417,7 +15417,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="17" thickBot="1">
+    <row r="470" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -15435,7 +15435,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="17" thickBot="1">
+    <row r="471" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -15453,7 +15453,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="17" thickBot="1">
+    <row r="472" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -15471,7 +15471,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="17" thickBot="1">
+    <row r="473" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -15489,7 +15489,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="17" thickBot="1">
+    <row r="474" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -15507,7 +15507,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="17" thickBot="1">
+    <row r="475" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -15525,7 +15525,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="17" thickBot="1">
+    <row r="476" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -15543,7 +15543,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="17" thickBot="1">
+    <row r="477" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -15561,7 +15561,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="17" thickBot="1">
+    <row r="478" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -15579,7 +15579,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="17" thickBot="1">
+    <row r="479" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -15597,7 +15597,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="17" thickBot="1">
+    <row r="480" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -15615,7 +15615,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="17" thickBot="1">
+    <row r="481" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -15633,7 +15633,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="17" thickBot="1">
+    <row r="482" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -15651,7 +15651,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="17" thickBot="1">
+    <row r="483" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -15669,7 +15669,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="17" thickBot="1">
+    <row r="484" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -15687,7 +15687,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="17" thickBot="1">
+    <row r="485" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -15705,7 +15705,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="17" thickBot="1">
+    <row r="486" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -15723,7 +15723,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="17" thickBot="1">
+    <row r="487" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -15741,7 +15741,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="17" thickBot="1">
+    <row r="488" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -15759,7 +15759,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="17" thickBot="1">
+    <row r="489" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -15777,7 +15777,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="17" thickBot="1">
+    <row r="490" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -15795,7 +15795,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="17" thickBot="1">
+    <row r="491" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="17" thickBot="1">
+    <row r="492" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -15831,7 +15831,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="17" thickBot="1">
+    <row r="493" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -15849,7 +15849,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="17" thickBot="1">
+    <row r="494" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -15867,7 +15867,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="17" thickBot="1">
+    <row r="495" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -15885,7 +15885,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="17" thickBot="1">
+    <row r="496" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="17" thickBot="1">
+    <row r="497" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -15921,7 +15921,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="17" thickBot="1">
+    <row r="498" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -15939,7 +15939,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="17" thickBot="1">
+    <row r="499" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -15957,7 +15957,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="17" thickBot="1">
+    <row r="500" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -15975,7 +15975,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="17" thickBot="1">
+    <row r="501" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="17" thickBot="1">
+    <row r="502" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -16011,7 +16011,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="17" thickBot="1">
+    <row r="503" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -16029,7 +16029,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="17" thickBot="1">
+    <row r="504" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -16047,7 +16047,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="17" thickBot="1">
+    <row r="505" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -16065,7 +16065,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="17" thickBot="1">
+    <row r="506" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -16083,7 +16083,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="17" thickBot="1">
+    <row r="507" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -16101,7 +16101,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="17" thickBot="1">
+    <row r="508" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -16119,7 +16119,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="17" thickBot="1">
+    <row r="509" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -16137,7 +16137,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="17" thickBot="1">
+    <row r="510" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -16155,7 +16155,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="17" thickBot="1">
+    <row r="511" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -16173,7 +16173,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="17" thickBot="1">
+    <row r="512" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="17" thickBot="1">
+    <row r="513" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -16209,7 +16209,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="17" thickBot="1">
+    <row r="514" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -16242,7 +16242,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="17" thickBot="1">
+    <row r="515" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -16260,7 +16260,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="17" thickBot="1">
+    <row r="516" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -16278,7 +16278,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="17" thickBot="1">
+    <row r="517" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="17" thickBot="1">
+    <row r="518" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -16314,7 +16314,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="17" thickBot="1">
+    <row r="519" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -16332,7 +16332,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="17" thickBot="1">
+    <row r="520" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -16350,7 +16350,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="17" thickBot="1">
+    <row r="521" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -16368,7 +16368,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="17" thickBot="1">
+    <row r="522" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -16386,7 +16386,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="17" thickBot="1">
+    <row r="523" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -16404,7 +16404,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="17" thickBot="1">
+    <row r="524" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="17" thickBot="1">
+    <row r="525" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -16440,7 +16440,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="17" thickBot="1">
+    <row r="526" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="17" thickBot="1">
+    <row r="527" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -16476,7 +16476,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="17" thickBot="1">
+    <row r="528" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -16494,7 +16494,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="17" thickBot="1">
+    <row r="529" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -16512,7 +16512,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="17" thickBot="1">
+    <row r="530" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -16530,7 +16530,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="17" thickBot="1">
+    <row r="531" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -16548,7 +16548,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="17" thickBot="1">
+    <row r="532" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="17" thickBot="1">
+    <row r="533" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -16584,7 +16584,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="17" thickBot="1">
+    <row r="534" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -16602,7 +16602,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="17" thickBot="1">
+    <row r="535" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -16620,7 +16620,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="17" thickBot="1">
+    <row r="536" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -16638,7 +16638,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="17" thickBot="1">
+    <row r="537" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -16656,7 +16656,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="17" thickBot="1">
+    <row r="538" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -16674,7 +16674,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="17" thickBot="1">
+    <row r="539" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -16692,7 +16692,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="17" thickBot="1">
+    <row r="540" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="17" thickBot="1">
+    <row r="541" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -16728,7 +16728,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="17" thickBot="1">
+    <row r="542" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -16746,7 +16746,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="17" thickBot="1">
+    <row r="543" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -16764,7 +16764,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="17" thickBot="1">
+    <row r="544" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -16782,7 +16782,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="17" thickBot="1">
+    <row r="545" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -16800,7 +16800,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="17" thickBot="1">
+    <row r="546" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -16818,7 +16818,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="17" thickBot="1">
+    <row r="547" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -16836,7 +16836,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="17" thickBot="1">
+    <row r="548" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -16854,7 +16854,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="17" thickBot="1">
+    <row r="549" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -16872,7 +16872,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="17" thickBot="1">
+    <row r="550" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -16890,7 +16890,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="17" thickBot="1">
+    <row r="551" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -16908,7 +16908,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="17" thickBot="1">
+    <row r="552" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -16926,7 +16926,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="17" thickBot="1">
+    <row r="553" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -16944,7 +16944,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="17" thickBot="1">
+    <row r="554" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -16962,7 +16962,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="17" thickBot="1">
+    <row r="555" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -16980,7 +16980,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="17" thickBot="1">
+    <row r="556" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -16998,7 +16998,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="17" thickBot="1">
+    <row r="557" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -17016,7 +17016,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="17" thickBot="1">
+    <row r="558" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -17034,7 +17034,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="17" thickBot="1">
+    <row r="559" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -17052,7 +17052,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="17" thickBot="1">
+    <row r="560" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -17070,7 +17070,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="17" thickBot="1">
+    <row r="561" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -17088,7 +17088,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="17" thickBot="1">
+    <row r="562" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -17106,7 +17106,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="17" thickBot="1">
+    <row r="563" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -17124,7 +17124,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="17" thickBot="1">
+    <row r="564" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -17142,7 +17142,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="17" thickBot="1">
+    <row r="565" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -17160,7 +17160,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="17" thickBot="1">
+    <row r="566" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -17178,7 +17178,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="17" thickBot="1">
+    <row r="567" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -17196,7 +17196,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="17" thickBot="1">
+    <row r="568" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -17214,7 +17214,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="17" thickBot="1">
+    <row r="569" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -17232,7 +17232,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="17" thickBot="1">
+    <row r="570" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -17250,7 +17250,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="17" thickBot="1">
+    <row r="571" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -17268,7 +17268,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="17" thickBot="1">
+    <row r="572" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -17286,7 +17286,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="17" thickBot="1">
+    <row r="573" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -17304,7 +17304,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="17" thickBot="1">
+    <row r="574" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -17322,7 +17322,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="17" thickBot="1">
+    <row r="575" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -17340,7 +17340,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="17" thickBot="1">
+    <row r="576" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -17358,7 +17358,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="17" thickBot="1">
+    <row r="577" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -17376,7 +17376,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="17" thickBot="1">
+    <row r="578" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -17409,7 +17409,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="17" thickBot="1">
+    <row r="579" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -17427,7 +17427,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="17" thickBot="1">
+    <row r="580" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -17445,7 +17445,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="17" thickBot="1">
+    <row r="581" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -17463,7 +17463,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="17" thickBot="1">
+    <row r="582" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -17481,7 +17481,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="17" thickBot="1">
+    <row r="583" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -17499,7 +17499,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="17" thickBot="1">
+    <row r="584" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -17517,7 +17517,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="17" thickBot="1">
+    <row r="585" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -17535,7 +17535,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="17" thickBot="1">
+    <row r="586" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -17553,7 +17553,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="17" thickBot="1">
+    <row r="587" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -17571,7 +17571,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="17" thickBot="1">
+    <row r="588" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -17589,7 +17589,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="17" thickBot="1">
+    <row r="589" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -17607,7 +17607,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="17" thickBot="1">
+    <row r="590" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -17625,7 +17625,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="17" thickBot="1">
+    <row r="591" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="17" thickBot="1">
+    <row r="592" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -17661,7 +17661,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="17" thickBot="1">
+    <row r="593" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -17679,7 +17679,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="17" thickBot="1">
+    <row r="594" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -17697,7 +17697,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="17" thickBot="1">
+    <row r="595" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -17715,7 +17715,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="17" thickBot="1">
+    <row r="596" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -17733,7 +17733,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="17" thickBot="1">
+    <row r="597" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -17751,7 +17751,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="17" thickBot="1">
+    <row r="598" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -17769,7 +17769,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="17" thickBot="1">
+    <row r="599" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="17" thickBot="1">
+    <row r="600" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -17805,7 +17805,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="17" thickBot="1">
+    <row r="601" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -17823,7 +17823,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="17" thickBot="1">
+    <row r="602" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -17841,7 +17841,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="17" thickBot="1">
+    <row r="603" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -17859,7 +17859,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="17" thickBot="1">
+    <row r="604" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -17877,7 +17877,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="17" thickBot="1">
+    <row r="605" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -17895,7 +17895,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="17" thickBot="1">
+    <row r="606" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -17913,7 +17913,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="17" thickBot="1">
+    <row r="607" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="17" thickBot="1">
+    <row r="608" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -17949,7 +17949,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="17" thickBot="1">
+    <row r="609" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -17967,7 +17967,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="17" thickBot="1">
+    <row r="610" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -17985,7 +17985,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="17" thickBot="1">
+    <row r="611" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -18003,7 +18003,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="17" thickBot="1">
+    <row r="612" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -18021,7 +18021,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="17" thickBot="1">
+    <row r="613" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -18039,7 +18039,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="17" thickBot="1">
+    <row r="614" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -18057,7 +18057,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="17" thickBot="1">
+    <row r="615" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -18075,7 +18075,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="17" thickBot="1">
+    <row r="616" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -18093,7 +18093,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="17" thickBot="1">
+    <row r="617" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -18111,7 +18111,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="17" thickBot="1">
+    <row r="618" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -18129,7 +18129,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="17" thickBot="1">
+    <row r="619" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -18147,7 +18147,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="17" thickBot="1">
+    <row r="620" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -18165,7 +18165,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="17" thickBot="1">
+    <row r="621" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="17" thickBot="1">
+    <row r="622" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -18201,7 +18201,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="17" thickBot="1">
+    <row r="623" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -18219,7 +18219,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="17" thickBot="1">
+    <row r="624" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -18237,7 +18237,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="17" thickBot="1">
+    <row r="625" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -18255,7 +18255,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="17" thickBot="1">
+    <row r="626" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="17" thickBot="1">
+    <row r="627" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -18291,7 +18291,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="17" thickBot="1">
+    <row r="628" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -18309,7 +18309,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="17" thickBot="1">
+    <row r="629" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -18327,7 +18327,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="17" thickBot="1">
+    <row r="630" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -18345,7 +18345,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="17" thickBot="1">
+    <row r="631" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -18363,7 +18363,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="17" thickBot="1">
+    <row r="632" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -18381,7 +18381,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="17" thickBot="1">
+    <row r="633" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -18399,7 +18399,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="17" thickBot="1">
+    <row r="634" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="17" thickBot="1">
+    <row r="635" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -18435,7 +18435,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="17" thickBot="1">
+    <row r="636" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -18453,7 +18453,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="17" thickBot="1">
+    <row r="637" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -18471,7 +18471,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="17" thickBot="1">
+    <row r="638" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -18489,7 +18489,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="17" thickBot="1">
+    <row r="639" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -18507,7 +18507,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="17" thickBot="1">
+    <row r="640" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="17" thickBot="1">
+    <row r="641" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -18543,7 +18543,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="17" thickBot="1">
+    <row r="642" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -18576,7 +18576,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="17" thickBot="1">
+    <row r="643" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -18594,7 +18594,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="17" thickBot="1">
+    <row r="644" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -18612,7 +18612,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="17" thickBot="1">
+    <row r="645" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -18630,7 +18630,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="17" thickBot="1">
+    <row r="646" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="17" thickBot="1">
+    <row r="647" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -18666,7 +18666,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="17" thickBot="1">
+    <row r="648" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -18684,7 +18684,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="17" thickBot="1">
+    <row r="649" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -18702,7 +18702,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="17" thickBot="1">
+    <row r="650" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -18720,7 +18720,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="17" thickBot="1">
+    <row r="651" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -18738,7 +18738,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="17" thickBot="1">
+    <row r="652" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -18756,7 +18756,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="17" thickBot="1">
+    <row r="653" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -18774,7 +18774,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="17" thickBot="1">
+    <row r="654" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="17" thickBot="1">
+    <row r="655" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -18810,7 +18810,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="17" thickBot="1">
+    <row r="656" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -18828,7 +18828,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="17" thickBot="1">
+    <row r="657" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -18846,7 +18846,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="17" thickBot="1">
+    <row r="658" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -18864,7 +18864,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="17" thickBot="1">
+    <row r="659" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -18882,7 +18882,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="17" thickBot="1">
+    <row r="660" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -18900,7 +18900,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="17" thickBot="1">
+    <row r="661" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -18918,7 +18918,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="17" thickBot="1">
+    <row r="662" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -18936,7 +18936,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="17" thickBot="1">
+    <row r="663" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -18954,7 +18954,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="17" thickBot="1">
+    <row r="664" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -18972,7 +18972,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="17" thickBot="1">
+    <row r="665" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -18990,7 +18990,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="17" thickBot="1">
+    <row r="666" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -19008,7 +19008,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="17" thickBot="1">
+    <row r="667" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -19026,7 +19026,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="17" thickBot="1">
+    <row r="668" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -19044,7 +19044,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="17" thickBot="1">
+    <row r="669" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -19062,7 +19062,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="17" thickBot="1">
+    <row r="670" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -19080,7 +19080,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="17" thickBot="1">
+    <row r="671" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -19098,7 +19098,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="17" thickBot="1">
+    <row r="672" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -19116,7 +19116,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="17" thickBot="1">
+    <row r="673" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -19134,7 +19134,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="17" thickBot="1">
+    <row r="674" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -19152,7 +19152,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="17" thickBot="1">
+    <row r="675" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -19170,7 +19170,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="17" thickBot="1">
+    <row r="676" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -19188,7 +19188,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="17" thickBot="1">
+    <row r="677" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -19206,7 +19206,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="17" thickBot="1">
+    <row r="678" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -19224,7 +19224,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="17" thickBot="1">
+    <row r="679" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -19242,7 +19242,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="17" thickBot="1">
+    <row r="680" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -19260,7 +19260,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="17" thickBot="1">
+    <row r="681" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -19278,7 +19278,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="17" thickBot="1">
+    <row r="682" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -19296,7 +19296,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="17" thickBot="1">
+    <row r="683" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -19314,7 +19314,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="17" thickBot="1">
+    <row r="684" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -19332,7 +19332,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="17" thickBot="1">
+    <row r="685" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="17" thickBot="1">
+    <row r="686" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -19368,7 +19368,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="17" thickBot="1">
+    <row r="687" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -19386,7 +19386,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="17" thickBot="1">
+    <row r="688" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -19404,7 +19404,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="17" thickBot="1">
+    <row r="689" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -19422,7 +19422,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="17" thickBot="1">
+    <row r="690" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -19440,7 +19440,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="17" thickBot="1">
+    <row r="691" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -19458,7 +19458,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="17" thickBot="1">
+    <row r="692" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -19476,7 +19476,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="17" thickBot="1">
+    <row r="693" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -19494,7 +19494,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="17" thickBot="1">
+    <row r="694" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="17" thickBot="1">
+    <row r="695" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -19530,7 +19530,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="17" thickBot="1">
+    <row r="696" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -19548,7 +19548,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="17" thickBot="1">
+    <row r="697" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -19566,7 +19566,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="17" thickBot="1">
+    <row r="698" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -19584,7 +19584,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="17" thickBot="1">
+    <row r="699" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -19602,7 +19602,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="17" thickBot="1">
+    <row r="700" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -19620,7 +19620,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="17" thickBot="1">
+    <row r="701" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -19638,7 +19638,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="17" thickBot="1">
+    <row r="702" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -19656,7 +19656,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="17" thickBot="1">
+    <row r="703" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="17" thickBot="1">
+    <row r="704" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="17" thickBot="1">
+    <row r="705" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -19710,7 +19710,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="17" thickBot="1">
+    <row r="706" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -19743,7 +19743,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="17" thickBot="1">
+    <row r="707" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -19761,7 +19761,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="17" thickBot="1">
+    <row r="708" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -19779,7 +19779,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="17" thickBot="1">
+    <row r="709" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -19797,7 +19797,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="17" thickBot="1">
+    <row r="710" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -19815,7 +19815,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="17" thickBot="1">
+    <row r="711" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -19833,7 +19833,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="17" thickBot="1">
+    <row r="712" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -19851,7 +19851,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="17" thickBot="1">
+    <row r="713" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -19869,7 +19869,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="17" thickBot="1">
+    <row r="714" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -19887,7 +19887,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="17" thickBot="1">
+    <row r="715" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -19905,7 +19905,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="17" thickBot="1">
+    <row r="716" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -19923,7 +19923,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="17" thickBot="1">
+    <row r="717" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -19941,7 +19941,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="17" thickBot="1">
+    <row r="718" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -19959,7 +19959,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="17" thickBot="1">
+    <row r="719" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -19977,7 +19977,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="17" thickBot="1">
+    <row r="720" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -19995,7 +19995,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="17" thickBot="1">
+    <row r="721" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -20013,7 +20013,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="17" thickBot="1">
+    <row r="722" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -20031,7 +20031,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="17" thickBot="1">
+    <row r="723" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -20049,7 +20049,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="17" thickBot="1">
+    <row r="724" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -20067,7 +20067,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="17" thickBot="1">
+    <row r="725" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -20085,7 +20085,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="17" thickBot="1">
+    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -20103,7 +20103,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="17" thickBot="1">
+    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="17" thickBot="1">
+    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -20139,7 +20139,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="17" thickBot="1">
+    <row r="729" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -20157,7 +20157,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="17" thickBot="1">
+    <row r="730" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -20175,7 +20175,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="17" thickBot="1">
+    <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -20193,7 +20193,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="17" thickBot="1">
+    <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -20211,7 +20211,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="17" thickBot="1">
+    <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -20229,7 +20229,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="17" thickBot="1">
+    <row r="734" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -20247,7 +20247,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="17" thickBot="1">
+    <row r="735" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -20265,7 +20265,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="17" thickBot="1">
+    <row r="736" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -20283,7 +20283,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="17" thickBot="1">
+    <row r="737" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -20301,7 +20301,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="17" thickBot="1">
+    <row r="738" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -20319,7 +20319,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="17" thickBot="1">
+    <row r="739" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -20337,7 +20337,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="17" thickBot="1">
+    <row r="740" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -20355,7 +20355,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="17" thickBot="1">
+    <row r="741" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -20373,7 +20373,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="17" thickBot="1">
+    <row r="742" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -20391,7 +20391,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="17" thickBot="1">
+    <row r="743" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -20409,7 +20409,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="17" thickBot="1">
+    <row r="744" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -20427,7 +20427,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="17" thickBot="1">
+    <row r="745" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -20445,7 +20445,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="17" thickBot="1">
+    <row r="746" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -20463,7 +20463,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="17" thickBot="1">
+    <row r="747" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -20481,7 +20481,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="17" thickBot="1">
+    <row r="748" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -20499,7 +20499,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="17" thickBot="1">
+    <row r="749" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -20517,7 +20517,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="17" thickBot="1">
+    <row r="750" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -20535,7 +20535,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="17" thickBot="1">
+    <row r="751" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -20553,7 +20553,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="17" thickBot="1">
+    <row r="752" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -20571,7 +20571,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="17" thickBot="1">
+    <row r="753" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -20589,7 +20589,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="17" thickBot="1">
+    <row r="754" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -20607,7 +20607,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="17" thickBot="1">
+    <row r="755" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -20625,7 +20625,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="17" thickBot="1">
+    <row r="756" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -20643,7 +20643,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="17" thickBot="1">
+    <row r="757" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -20661,7 +20661,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="17" thickBot="1">
+    <row r="758" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -20679,7 +20679,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="17" thickBot="1">
+    <row r="759" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -20697,7 +20697,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="17" thickBot="1">
+    <row r="760" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -20715,7 +20715,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="17" thickBot="1">
+    <row r="761" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -20733,7 +20733,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="17" thickBot="1">
+    <row r="762" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -20751,7 +20751,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="17" thickBot="1">
+    <row r="763" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -20769,7 +20769,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="17" thickBot="1">
+    <row r="764" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -20787,7 +20787,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="17" thickBot="1">
+    <row r="765" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -20805,7 +20805,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="17" thickBot="1">
+    <row r="766" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -20823,7 +20823,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="17" thickBot="1">
+    <row r="767" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -20841,7 +20841,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="17" thickBot="1">
+    <row r="768" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -20859,7 +20859,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="17" thickBot="1">
+    <row r="769" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -20877,7 +20877,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="17" thickBot="1">
+    <row r="770" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -20910,7 +20910,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="17" thickBot="1">
+    <row r="771" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -20928,7 +20928,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="17" thickBot="1">
+    <row r="772" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -20946,7 +20946,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="17" thickBot="1">
+    <row r="773" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -20964,7 +20964,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="17" thickBot="1">
+    <row r="774" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -20982,7 +20982,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="17" thickBot="1">
+    <row r="775" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -21000,7 +21000,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="17" thickBot="1">
+    <row r="776" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -21018,7 +21018,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="17" thickBot="1">
+    <row r="777" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -21036,7 +21036,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="17" thickBot="1">
+    <row r="778" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -21054,7 +21054,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="17" thickBot="1">
+    <row r="779" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -21072,7 +21072,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="17" thickBot="1">
+    <row r="780" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -21090,7 +21090,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="17" thickBot="1">
+    <row r="781" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -21108,7 +21108,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="17" thickBot="1">
+    <row r="782" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -21126,7 +21126,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="17" thickBot="1">
+    <row r="783" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -21144,7 +21144,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="17" thickBot="1">
+    <row r="784" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -21162,7 +21162,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="17" thickBot="1">
+    <row r="785" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -21180,7 +21180,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="17" thickBot="1">
+    <row r="786" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -21198,7 +21198,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="17" thickBot="1">
+    <row r="787" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -21216,7 +21216,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="17" thickBot="1">
+    <row r="788" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -21234,7 +21234,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="17" thickBot="1">
+    <row r="789" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -21252,7 +21252,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="17" thickBot="1">
+    <row r="790" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -21270,7 +21270,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="17" thickBot="1">
+    <row r="791" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -21288,7 +21288,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="17" thickBot="1">
+    <row r="792" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -21306,7 +21306,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="17" thickBot="1">
+    <row r="793" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -21324,7 +21324,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="17" thickBot="1">
+    <row r="794" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -21342,7 +21342,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="17" thickBot="1">
+    <row r="795" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -21360,7 +21360,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="17" thickBot="1">
+    <row r="796" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -21378,7 +21378,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="17" thickBot="1">
+    <row r="797" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -21396,7 +21396,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="17" thickBot="1">
+    <row r="798" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -21414,7 +21414,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="17" thickBot="1">
+    <row r="799" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -21432,7 +21432,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="17" thickBot="1">
+    <row r="800" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -21450,7 +21450,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="17" thickBot="1">
+    <row r="801" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -21468,7 +21468,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="17" thickBot="1">
+    <row r="802" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -21486,7 +21486,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="17" thickBot="1">
+    <row r="803" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -21504,7 +21504,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="17" thickBot="1">
+    <row r="804" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -21522,7 +21522,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="17" thickBot="1">
+    <row r="805" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -21540,7 +21540,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="17" thickBot="1">
+    <row r="806" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -21558,7 +21558,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="17" thickBot="1">
+    <row r="807" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -21576,7 +21576,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="17" thickBot="1">
+    <row r="808" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -21594,7 +21594,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="17" thickBot="1">
+    <row r="809" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -21612,7 +21612,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="17" thickBot="1">
+    <row r="810" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -21630,7 +21630,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="17" thickBot="1">
+    <row r="811" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -21648,7 +21648,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="17" thickBot="1">
+    <row r="812" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -21666,7 +21666,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="17" thickBot="1">
+    <row r="813" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -21684,7 +21684,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="17" thickBot="1">
+    <row r="814" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -21702,7 +21702,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="17" thickBot="1">
+    <row r="815" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -21720,7 +21720,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="17" thickBot="1">
+    <row r="816" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -21738,7 +21738,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="17" thickBot="1">
+    <row r="817" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -21756,7 +21756,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="17" thickBot="1">
+    <row r="818" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -21774,7 +21774,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="17" thickBot="1">
+    <row r="819" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -21792,7 +21792,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="17" thickBot="1">
+    <row r="820" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -21810,7 +21810,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="17" thickBot="1">
+    <row r="821" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -21828,7 +21828,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="17" thickBot="1">
+    <row r="822" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -21846,7 +21846,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="17" thickBot="1">
+    <row r="823" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -21864,7 +21864,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="17" thickBot="1">
+    <row r="824" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -21882,7 +21882,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="17" thickBot="1">
+    <row r="825" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -21900,7 +21900,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="17" thickBot="1">
+    <row r="826" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -21918,7 +21918,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="17" thickBot="1">
+    <row r="827" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -21936,7 +21936,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="17" thickBot="1">
+    <row r="828" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -21954,7 +21954,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="17" thickBot="1">
+    <row r="829" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -21972,7 +21972,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="17" thickBot="1">
+    <row r="830" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -21990,7 +21990,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="17" thickBot="1">
+    <row r="831" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -22008,7 +22008,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="17" thickBot="1">
+    <row r="832" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -22026,7 +22026,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="17" thickBot="1">
+    <row r="833" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -22044,7 +22044,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="17" thickBot="1">
+    <row r="834" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -22077,7 +22077,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="17" thickBot="1">
+    <row r="835" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -22095,7 +22095,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="17" thickBot="1">
+    <row r="836" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -22113,7 +22113,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="17" thickBot="1">
+    <row r="837" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -22131,7 +22131,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="17" thickBot="1">
+    <row r="838" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -22149,7 +22149,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="17" thickBot="1">
+    <row r="839" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -22167,7 +22167,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="17" thickBot="1">
+    <row r="840" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -22185,7 +22185,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="17" thickBot="1">
+    <row r="841" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -22203,7 +22203,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="17" thickBot="1">
+    <row r="842" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -22221,7 +22221,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="17" thickBot="1">
+    <row r="843" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -22239,7 +22239,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="17" thickBot="1">
+    <row r="844" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -22257,7 +22257,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="17" thickBot="1">
+    <row r="845" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -22275,7 +22275,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="17" thickBot="1">
+    <row r="846" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -22293,7 +22293,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="17" thickBot="1">
+    <row r="847" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -22311,7 +22311,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="17" thickBot="1">
+    <row r="848" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -22329,7 +22329,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="17" thickBot="1">
+    <row r="849" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -22347,7 +22347,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="17" thickBot="1">
+    <row r="850" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -22365,7 +22365,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="17" thickBot="1">
+    <row r="851" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -22383,7 +22383,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="17" thickBot="1">
+    <row r="852" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -22401,7 +22401,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="17" thickBot="1">
+    <row r="853" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -22419,7 +22419,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="17" thickBot="1">
+    <row r="854" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -22437,7 +22437,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="17" thickBot="1">
+    <row r="855" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -22455,7 +22455,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="17" thickBot="1">
+    <row r="856" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -22473,7 +22473,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="17" thickBot="1">
+    <row r="857" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -22491,7 +22491,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="17" thickBot="1">
+    <row r="858" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -22509,7 +22509,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="17" thickBot="1">
+    <row r="859" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -22527,7 +22527,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="17" thickBot="1">
+    <row r="860" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -22545,7 +22545,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="17" thickBot="1">
+    <row r="861" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -22563,7 +22563,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="17" thickBot="1">
+    <row r="862" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -22581,7 +22581,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="17" thickBot="1">
+    <row r="863" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -22599,7 +22599,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="17" thickBot="1">
+    <row r="864" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -22617,7 +22617,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="17" thickBot="1">
+    <row r="865" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -22635,7 +22635,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="17" thickBot="1">
+    <row r="866" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -22653,7 +22653,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="17" thickBot="1">
+    <row r="867" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -22671,7 +22671,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="17" thickBot="1">
+    <row r="868" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -22689,7 +22689,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="17" thickBot="1">
+    <row r="869" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -22707,7 +22707,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="17" thickBot="1">
+    <row r="870" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -22725,7 +22725,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="17" thickBot="1">
+    <row r="871" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -22743,7 +22743,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="17" thickBot="1">
+    <row r="872" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -22761,7 +22761,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="17" thickBot="1">
+    <row r="873" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -22779,7 +22779,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="17" thickBot="1">
+    <row r="874" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -22797,7 +22797,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="17" thickBot="1">
+    <row r="875" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -22815,7 +22815,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="17" thickBot="1">
+    <row r="876" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -22833,7 +22833,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="17" thickBot="1">
+    <row r="877" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -22851,7 +22851,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="17" thickBot="1">
+    <row r="878" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -22884,7 +22884,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="17" thickBot="1">
+    <row r="879" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -22917,7 +22917,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="17" thickBot="1">
+    <row r="880" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -22950,7 +22950,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="17" thickBot="1">
+    <row r="881" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -22968,7 +22968,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="17" thickBot="1">
+    <row r="882" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -23001,7 +23001,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="17" thickBot="1">
+    <row r="883" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -23034,7 +23034,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="17" thickBot="1">
+    <row r="884" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
@@ -23052,7 +23052,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="17" thickBot="1">
+    <row r="885" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A885" s="15">
         <v>46088</v>
       </c>
@@ -23070,7 +23070,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" ht="16">
+    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A886" s="8">
         <v>46102</v>
       </c>
@@ -23088,7 +23088,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5" ht="16">
+    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A887" s="8">
         <v>46109</v>
       </c>
@@ -23106,7 +23106,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5" ht="16">
+    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A888" s="8">
         <v>46116</v>
       </c>
@@ -23124,7 +23124,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5" ht="16">
+    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A889" s="8">
         <v>46123</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>500040</v>
       </c>
     </row>
-    <row r="890" spans="1:5" ht="16">
+    <row r="890" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A890" s="8">
         <v>46130</v>
       </c>
@@ -23160,7 +23160,7 @@
         <v>508303</v>
       </c>
     </row>
-    <row r="891" spans="1:5" ht="16">
+    <row r="891" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A891" s="8">
         <v>46137</v>
       </c>
@@ -23178,7 +23178,7 @@
         <v>511616</v>
       </c>
     </row>
-    <row r="892" spans="1:5" ht="16">
+    <row r="892" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A892" s="8">
         <v>46144</v>
       </c>
@@ -23196,7 +23196,7 @@
         <v>518773</v>
       </c>
     </row>
-    <row r="893" spans="1:5" ht="16">
+    <row r="893" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A893" s="8">
         <v>46151</v>
       </c>
@@ -23229,7 +23229,7 @@
         <v>513755</v>
       </c>
     </row>
-    <row r="894" spans="1:5" ht="16">
+    <row r="894" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A894" s="8">
         <v>46158</v>
       </c>
@@ -23247,7 +23247,7 @@
         <v>511216</v>
       </c>
     </row>
-    <row r="895" spans="1:5" ht="16">
+    <row r="895" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A895" s="8">
         <v>46165</v>
       </c>
@@ -23265,7 +23265,7 @@
         <v>523574</v>
       </c>
     </row>
-    <row r="896" spans="1:5" ht="16">
+    <row r="896" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A896" s="8">
         <v>46172</v>
       </c>
@@ -23298,7 +23298,7 @@
         <v>492795</v>
       </c>
     </row>
-    <row r="897" spans="1:5" ht="16">
+    <row r="897" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A897" s="8">
         <v>46179</v>
       </c>
@@ -23316,7 +23316,7 @@
         <v>521804</v>
       </c>
     </row>
-    <row r="898" spans="1:5" ht="16">
+    <row r="898" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A898" s="8">
         <v>46186</v>
       </c>
@@ -23334,7 +23334,7 @@
         <v>520406</v>
       </c>
     </row>
-    <row r="899" spans="1:5" ht="16">
+    <row r="899" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A899" s="8">
         <v>46193</v>
       </c>
@@ -23367,7 +23367,7 @@
         <v>521998</v>
       </c>
     </row>
-    <row r="900" spans="1:5" ht="16">
+    <row r="900" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A900" s="8">
         <v>46200</v>
       </c>
@@ -23385,7 +23385,7 @@
         <v>525474</v>
       </c>
     </row>
-    <row r="901" spans="1:5" ht="16">
+    <row r="901" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A901" s="8">
         <v>46207</v>
       </c>
@@ -23396,7 +23396,7 @@
         <v>0.50138888888888888</v>
       </c>
       <c r="D901" s="7" t="str">
-        <f t="shared" ref="D901:D902" si="19">IF(
+        <f t="shared" ref="D901:D903" si="19">IF(
  AND(
   A901 &gt;= IF(
          YEAR(A901)&gt;=2007,
@@ -23418,7 +23418,7 @@
         <v>482121</v>
       </c>
     </row>
-    <row r="902" spans="1:5" ht="16">
+    <row r="902" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A902" s="8">
         <v>46214</v>
       </c>
@@ -23434,6 +23434,21 @@
       </c>
       <c r="E902" s="20">
         <v>503525</v>
+      </c>
+    </row>
+    <row r="903" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A903" s="8">
+        <v>46221</v>
+      </c>
+      <c r="B903" s="8">
+        <v>46225</v>
+      </c>
+      <c r="C903" s="21">
+        <v>0.50069444444444444</v>
+      </c>
+      <c r="D903" s="7" t="str">
+        <f t="shared" si="19"/>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>
@@ -23449,7 +23464,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23460,12 +23475,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23473,7 +23488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23481,7 +23496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494D759C-A3D6-4712-BD67-50720B4439E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF21228A-D10E-4F29-9B32-14BF0986E9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -6835,7 +6835,7 @@
   <cols>
     <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.109375" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.109375" style="6"/>
@@ -23444,11 +23444,14 @@
         <v>46225</v>
       </c>
       <c r="C903" s="21">
-        <v>0.50069444444444444</v>
+        <v>0.50347222222222221</v>
       </c>
       <c r="D903" s="7" t="str">
         <f t="shared" si="19"/>
         <v>UTC-4</v>
+      </c>
+      <c r="E903" s="20">
+        <v>523900</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF21228A-D10E-4F29-9B32-14BF0986E9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4322CC3E-EA3B-4431-9457-74F7BC602B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -6836,7 +6836,7 @@
     <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.109375" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.109375" style="6"/>
   </cols>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4322CC3E-EA3B-4431-9457-74F7BC602B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F7AA59-0A09-4D2F-9E8E-49878CB87DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -6830,7 +6830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E903"/>
+  <dimension ref="A1:E904"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
@@ -23452,6 +23452,36 @@
       </c>
       <c r="E903" s="20">
         <v>523900</v>
+      </c>
+    </row>
+    <row r="904" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A904" s="8">
+        <v>46228</v>
+      </c>
+      <c r="B904" s="8">
+        <v>46232</v>
+      </c>
+      <c r="C904" s="21">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="D904" s="7" t="str">
+        <f t="shared" ref="D904" si="20">IF(
+ AND(
+  A904 &gt;= IF(
+         YEAR(A904)&gt;=2007,
+         DATE(YEAR(A904),3,14)-WEEKDAY(DATE(YEAR(A904),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A904),4,7)-WEEKDAY(DATE(YEAR(A904),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A904 &lt;  IF(
+         YEAR(A904)&gt;=2007,
+         DATE(YEAR(A904),11,7)-WEEKDAY(DATE(YEAR(A904),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A904),10,31)-WEEKDAY(DATE(YEAR(A904),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F7AA59-0A09-4D2F-9E8E-49878CB87DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1492ECC-0738-4BC5-BFE5-EEA186B30F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -23462,7 +23462,7 @@
         <v>46232</v>
       </c>
       <c r="C904" s="21">
-        <v>0.50138888888888888</v>
+        <v>0.52013888888888893</v>
       </c>
       <c r="D904" s="7" t="str">
         <f t="shared" ref="D904" si="20">IF(
@@ -23482,6 +23482,9 @@
  "UTC-5"
 )</f>
         <v>UTC-4</v>
+      </c>
+      <c r="E904" s="20">
+        <v>527162</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1492ECC-0738-4BC5-BFE5-EEA186B30F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBB0126-D230-45F2-8B30-66C57BCC8548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -23465,7 +23465,7 @@
         <v>0.52013888888888893</v>
       </c>
       <c r="D904" s="7" t="str">
-        <f t="shared" ref="D904" si="20">IF(
+        <f t="shared" ref="D904:D905" si="20">IF(
  AND(
   A904 &gt;= IF(
          YEAR(A904)&gt;=2007,

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBB0126-D230-45F2-8B30-66C57BCC8548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D4BD3E-43FB-4949-9204-E8899AC7DD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -6830,7 +6830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E904"/>
+  <dimension ref="A1:E905"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
@@ -23485,6 +23485,24 @@
       </c>
       <c r="E904" s="20">
         <v>527162</v>
+      </c>
+    </row>
+    <row r="905" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A905" s="8">
+        <v>46235</v>
+      </c>
+      <c r="B905" s="8">
+        <v>46239</v>
+      </c>
+      <c r="C905" s="21">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="D905" s="7" t="str">
+        <f t="shared" si="20"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E905" s="20">
+        <v>526410</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D4BD3E-43FB-4949-9204-E8899AC7DD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A504099-85D3-42FE-96EC-A0B0CE5200DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -6830,7 +6830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E905"/>
+  <dimension ref="A1:E906"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
@@ -23503,6 +23503,36 @@
       </c>
       <c r="E905" s="20">
         <v>526410</v>
+      </c>
+    </row>
+    <row r="906" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A906" s="8">
+        <v>46242</v>
+      </c>
+      <c r="B906" s="8">
+        <v>46246</v>
+      </c>
+      <c r="C906" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="D906" s="7" t="str">
+        <f t="shared" ref="D906" si="21">IF(
+ AND(
+  A906 &gt;= IF(
+         YEAR(A906)&gt;=2007,
+         DATE(YEAR(A906),3,14)-WEEKDAY(DATE(YEAR(A906),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A906),4,7)-WEEKDAY(DATE(YEAR(A906),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A906 &lt;  IF(
+         YEAR(A906)&gt;=2007,
+         DATE(YEAR(A906),11,7)-WEEKDAY(DATE(YEAR(A906),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A906),10,31)-WEEKDAY(DATE(YEAR(A906),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A504099-85D3-42FE-96EC-A0B0CE5200DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03223FB-EA7D-C24B-AF44-EE24A99BE524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -86,12 +86,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -189,7 +189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -206,68 +206,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -285,7 +285,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6534,9 +6534,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6574,7 +6574,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6680,7 +6680,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6822,7 +6822,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6831,17 +6831,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
   <dimension ref="A1:E906"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="6"/>
+    <col min="3" max="3" width="11.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="16">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="16">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="16">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="16">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="16">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="16">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="16">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="16">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="16">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="16">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="16">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="16">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -7122,7 +7122,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="16">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="16">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="16">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="16">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="16">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="16">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="16">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="16">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="16">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="16">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="16">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="16">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="16">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="16">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="16">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="16">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="16">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="16">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="16">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="16">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="16">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="16">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="16">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="16">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="16">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="16">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="16">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="16">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="16">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -7644,7 +7644,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="16">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="16">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="16">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" ht="16">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" ht="16">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" ht="16">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" ht="16">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" ht="16">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" ht="16">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" ht="16">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" ht="16">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" ht="16">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -7860,7 +7860,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" ht="16">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" ht="16">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -7896,7 +7896,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" ht="16">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" ht="16">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" ht="16">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" ht="16">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" ht="16">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" ht="16">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" ht="16">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" ht="16">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -8040,7 +8040,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" ht="16">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" ht="16">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" ht="16">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" ht="16">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -8127,7 +8127,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" ht="16">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" ht="16">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" ht="16">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -8181,7 +8181,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" ht="16">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" ht="16">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" ht="16">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" ht="16">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" ht="16">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -8271,7 +8271,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" ht="16">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" ht="16">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" ht="16">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" ht="16">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" ht="16">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" ht="16">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" ht="16">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -8397,7 +8397,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" ht="16">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" ht="16">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" ht="16">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" ht="16">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" ht="16">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" ht="16">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" ht="16">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" ht="16">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -8541,7 +8541,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" ht="16">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -8559,7 +8559,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" ht="16">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" ht="16">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" ht="16">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" ht="16">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" ht="16">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" ht="16">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" ht="16">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" ht="17" thickBot="1">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" ht="17" thickBot="1">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" ht="17" thickBot="1">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" ht="17" thickBot="1">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" ht="17" thickBot="1">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" ht="17" thickBot="1">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" ht="17" thickBot="1">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" ht="17" thickBot="1">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -8829,7 +8829,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" ht="17" thickBot="1">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" ht="17" thickBot="1">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" ht="17" thickBot="1">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" ht="17" thickBot="1">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:5" ht="17" thickBot="1">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -8919,7 +8919,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:5" ht="17" thickBot="1">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -8937,7 +8937,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:5" ht="17" thickBot="1">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:5" ht="17" thickBot="1">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:5" ht="17" thickBot="1">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:5" ht="17" thickBot="1">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:5" ht="17" thickBot="1">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:5" ht="17" thickBot="1">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:5" ht="17" thickBot="1">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:5" ht="17" thickBot="1">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:5" ht="17" thickBot="1">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:5" ht="17" thickBot="1">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -9117,7 +9117,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:5" ht="17" thickBot="1">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:5" ht="17" thickBot="1">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:5" ht="17" thickBot="1">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:5" ht="17" thickBot="1">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -9189,7 +9189,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:5" ht="17" thickBot="1">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -9207,7 +9207,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:5" ht="17" thickBot="1">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:5" ht="17" thickBot="1">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:5" ht="17" thickBot="1">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:5" ht="17" thickBot="1">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:5" ht="17" thickBot="1">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:5" ht="17" thickBot="1">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:5" ht="17" thickBot="1">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:5" ht="17" thickBot="1">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:5" ht="17" thickBot="1">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:5" ht="17" thickBot="1">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:5" ht="17" thickBot="1">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:5" ht="17" thickBot="1">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:5" ht="17" thickBot="1">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -9456,7 +9456,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:5" ht="17" thickBot="1">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:5" ht="17" thickBot="1">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:5" ht="17" thickBot="1">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:5" ht="17" thickBot="1">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:5" ht="17" thickBot="1">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:5" ht="17" thickBot="1">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:5" ht="17" thickBot="1">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -9582,7 +9582,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:5" ht="17" thickBot="1">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:5" ht="17" thickBot="1">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:5" ht="17" thickBot="1">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:5" ht="17" thickBot="1">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:5" ht="17" thickBot="1">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:5" ht="17" thickBot="1">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:5" ht="17" thickBot="1">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -9708,7 +9708,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:5" ht="17" thickBot="1">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -9726,7 +9726,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:5" ht="17" thickBot="1">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:5" ht="17" thickBot="1">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -9762,7 +9762,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:5" ht="17" thickBot="1">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:5" ht="17" thickBot="1">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:5" ht="17" thickBot="1">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:5" ht="17" thickBot="1">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:5" ht="17" thickBot="1">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:5" ht="17" thickBot="1">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:5" ht="17" thickBot="1">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:5" ht="17" thickBot="1">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:5" ht="17" thickBot="1">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:5" ht="17" thickBot="1">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:5" ht="17" thickBot="1">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -9960,7 +9960,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:5" ht="17" thickBot="1">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -9978,7 +9978,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:5" ht="17" thickBot="1">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -9996,7 +9996,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:5" ht="17" thickBot="1">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:5" ht="17" thickBot="1">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -10032,7 +10032,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:5" ht="17" thickBot="1">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:5" ht="17" thickBot="1">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:5" ht="17" thickBot="1">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:5" ht="17" thickBot="1">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:5" ht="17" thickBot="1">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:5" ht="17" thickBot="1">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -10140,7 +10140,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:5" ht="17" thickBot="1">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:5" ht="17" thickBot="1">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -10176,7 +10176,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:5" ht="17" thickBot="1">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:5" ht="17" thickBot="1">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -10212,7 +10212,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:5" ht="17" thickBot="1">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:5" ht="17" thickBot="1">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -10248,7 +10248,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:5" ht="17" thickBot="1">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:5" ht="17" thickBot="1">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:5" ht="17" thickBot="1">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:5" ht="17" thickBot="1">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -10320,7 +10320,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:5" ht="17" thickBot="1">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -10338,7 +10338,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:5" ht="17" thickBot="1">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -10356,7 +10356,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:5" ht="17" thickBot="1">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:5" ht="17" thickBot="1">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:5" ht="17" thickBot="1">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:5" ht="17" thickBot="1">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -10443,7 +10443,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:5" ht="17" thickBot="1">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -10461,7 +10461,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:5" ht="17" thickBot="1">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:5" ht="17" thickBot="1">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -10497,7 +10497,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:5" ht="17" thickBot="1">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -10515,7 +10515,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:5" ht="17" thickBot="1">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:5" ht="17" thickBot="1">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:5" ht="17" thickBot="1">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -10569,7 +10569,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:5" ht="17" thickBot="1">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -10587,7 +10587,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:5" ht="17" thickBot="1">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:5" ht="17" thickBot="1">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:5" ht="17" thickBot="1">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -10641,7 +10641,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:5" ht="17" thickBot="1">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -10659,7 +10659,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:5" ht="17" thickBot="1">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -10677,7 +10677,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:5" ht="17" thickBot="1">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:5" ht="17" thickBot="1">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:5" ht="17" thickBot="1">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -10731,7 +10731,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:5" ht="17" thickBot="1">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:5" ht="17" thickBot="1">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -10767,7 +10767,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:5" ht="17" thickBot="1">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:5" ht="17" thickBot="1">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:5" ht="17" thickBot="1">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:5" ht="17" thickBot="1">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -10839,7 +10839,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:5" ht="17" thickBot="1">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:5" ht="17" thickBot="1">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:5" ht="17" thickBot="1">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:5" ht="17" thickBot="1">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:5" ht="17" thickBot="1">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -10929,7 +10929,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:5" ht="17" thickBot="1">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:5" ht="17" thickBot="1">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:5" ht="17" thickBot="1">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -10983,7 +10983,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:5" ht="17" thickBot="1">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -11001,7 +11001,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:5" ht="17" thickBot="1">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:5" ht="17" thickBot="1">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:5" ht="17" thickBot="1">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -11055,7 +11055,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:5" ht="17" thickBot="1">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:5" ht="17" thickBot="1">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -11091,7 +11091,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:5" ht="17" thickBot="1">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -11109,7 +11109,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:5" ht="17" thickBot="1">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:5" ht="17" thickBot="1">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:5" ht="17" thickBot="1">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -11163,7 +11163,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:5" ht="17" thickBot="1">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -11181,7 +11181,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:5" ht="17" thickBot="1">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -11199,7 +11199,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:5" ht="17" thickBot="1">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:5" ht="17" thickBot="1">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -11235,7 +11235,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:5" ht="17" thickBot="1">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:5" ht="17" thickBot="1">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -11271,7 +11271,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:5" ht="17" thickBot="1">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:5" ht="17" thickBot="1">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -11307,7 +11307,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:5" ht="17" thickBot="1">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:5" ht="17" thickBot="1">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -11343,7 +11343,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:5" ht="17" thickBot="1">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -11361,7 +11361,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:5" ht="17" thickBot="1">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -11379,7 +11379,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:5" ht="17" thickBot="1">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -11397,7 +11397,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:5" ht="17" thickBot="1">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -11415,7 +11415,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:5" ht="17" thickBot="1">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:5" ht="17" thickBot="1">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -11451,7 +11451,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:5" ht="17" thickBot="1">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -11469,7 +11469,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:5" ht="17" thickBot="1">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:5" ht="17" thickBot="1">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -11505,7 +11505,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:5" ht="17" thickBot="1">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -11523,7 +11523,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:5" ht="17" thickBot="1">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:5" ht="17" thickBot="1">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -11574,7 +11574,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:5" ht="17" thickBot="1">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:5" ht="17" thickBot="1">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -11610,7 +11610,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:5" ht="17" thickBot="1">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:5" ht="17" thickBot="1">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -11646,7 +11646,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:5" ht="17" thickBot="1">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:5" ht="17" thickBot="1">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:5" ht="17" thickBot="1">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -11700,7 +11700,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:5" ht="17" thickBot="1">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:5" ht="17" thickBot="1">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -11736,7 +11736,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:5" ht="17" thickBot="1">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:5" ht="17" thickBot="1">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -11772,7 +11772,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:5" ht="17" thickBot="1">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -11790,7 +11790,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:5" ht="17" thickBot="1">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -11808,7 +11808,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:5" ht="17" thickBot="1">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -11826,7 +11826,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:5" ht="17" thickBot="1">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -11844,7 +11844,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:5" ht="17" thickBot="1">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:5" ht="17" thickBot="1">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:5" ht="17" thickBot="1">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:5" ht="17" thickBot="1">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:5" ht="17" thickBot="1">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -11934,7 +11934,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:5" ht="17" thickBot="1">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:5" ht="17" thickBot="1">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -11970,7 +11970,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:5" ht="17" thickBot="1">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:5" ht="17" thickBot="1">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:5" ht="17" thickBot="1">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:5" ht="17" thickBot="1">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:5" ht="17" thickBot="1">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -12060,7 +12060,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:5" ht="17" thickBot="1">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -12078,7 +12078,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:5" ht="17" thickBot="1">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:5" ht="17" thickBot="1">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -12114,7 +12114,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:5" ht="17" thickBot="1">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:5" ht="17" thickBot="1">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -12150,7 +12150,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:5" ht="17" thickBot="1">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:5" ht="17" thickBot="1">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -12186,7 +12186,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:5" ht="17" thickBot="1">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:5" ht="17" thickBot="1">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:5" ht="17" thickBot="1">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -12240,7 +12240,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:5" ht="17" thickBot="1">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:5" ht="17" thickBot="1">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -12276,7 +12276,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:5" ht="17" thickBot="1">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:5" ht="17" thickBot="1">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:5" ht="17" thickBot="1">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -12330,7 +12330,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:5" ht="17" thickBot="1">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -12348,7 +12348,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:5" ht="17" thickBot="1">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:5" ht="17" thickBot="1">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -12384,7 +12384,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:5" ht="17" thickBot="1">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:5" ht="17" thickBot="1">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -12420,7 +12420,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:5" ht="17" thickBot="1">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:5" ht="17" thickBot="1">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:5" ht="17" thickBot="1">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -12474,7 +12474,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:5" ht="17" thickBot="1">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:5" ht="17" thickBot="1">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:5" ht="17" thickBot="1">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -12528,7 +12528,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:5" ht="17" thickBot="1">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -12546,7 +12546,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:5" ht="17" thickBot="1">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:5" ht="17" thickBot="1">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -12582,7 +12582,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:5" ht="17" thickBot="1">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -12600,7 +12600,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:5" ht="17" thickBot="1">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -12618,7 +12618,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:5" ht="17" thickBot="1">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:5" ht="17" thickBot="1">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:5" ht="17" thickBot="1">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -12672,7 +12672,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:5" ht="17" thickBot="1">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -12690,7 +12690,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:5" ht="17" thickBot="1">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:5" ht="17" thickBot="1">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:5" ht="17" thickBot="1">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -12759,7 +12759,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:5" ht="17" thickBot="1">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -12777,7 +12777,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:5" ht="17" thickBot="1">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:5" ht="17" thickBot="1">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:5" ht="17" thickBot="1">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:5" ht="17" thickBot="1">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -12849,7 +12849,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:5" ht="17" thickBot="1">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -12867,7 +12867,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:5" ht="17" thickBot="1">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:5" ht="17" thickBot="1">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -12903,7 +12903,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:5" ht="17" thickBot="1">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -12921,7 +12921,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:5" ht="17" thickBot="1">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:5" ht="17" thickBot="1">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -12957,7 +12957,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:5" ht="17" thickBot="1">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -12975,7 +12975,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:5" ht="17" thickBot="1">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -12993,7 +12993,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:5" ht="17" thickBot="1">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -13011,7 +13011,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:5" ht="17" thickBot="1">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -13029,7 +13029,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:5" ht="17" thickBot="1">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -13047,7 +13047,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:5" ht="17" thickBot="1">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -13065,7 +13065,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:5" ht="17" thickBot="1">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -13083,7 +13083,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:5" ht="17" thickBot="1">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -13101,7 +13101,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:5" ht="17" thickBot="1">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:5" ht="17" thickBot="1">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -13137,7 +13137,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:5" ht="17" thickBot="1">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:5" ht="17" thickBot="1">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:5" ht="17" thickBot="1">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -13191,7 +13191,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:5" ht="17" thickBot="1">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:5" ht="17" thickBot="1">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -13227,7 +13227,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:5" ht="17" thickBot="1">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:5" ht="17" thickBot="1">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -13263,7 +13263,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:5" ht="17" thickBot="1">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -13281,7 +13281,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:5" ht="17" thickBot="1">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:5" ht="17" thickBot="1">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -13317,7 +13317,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:5" ht="17" thickBot="1">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:5" ht="17" thickBot="1">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -13353,7 +13353,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:5" ht="17" thickBot="1">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -13371,7 +13371,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:5" ht="17" thickBot="1">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -13389,7 +13389,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:5" ht="17" thickBot="1">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -13407,7 +13407,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:5" ht="17" thickBot="1">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -13425,7 +13425,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:5" ht="17" thickBot="1">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -13443,7 +13443,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:5" ht="17" thickBot="1">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -13461,7 +13461,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:5" ht="17" thickBot="1">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -13479,7 +13479,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:5" ht="17" thickBot="1">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -13497,7 +13497,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:5" ht="17" thickBot="1">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -13515,7 +13515,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:5" ht="17" thickBot="1">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:5" ht="17" thickBot="1">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -13551,7 +13551,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:5" ht="17" thickBot="1">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -13569,7 +13569,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:5" ht="17" thickBot="1">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -13587,7 +13587,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:5" ht="17" thickBot="1">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -13605,7 +13605,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:5" ht="17" thickBot="1">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -13623,7 +13623,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:5" ht="17" thickBot="1">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -13641,7 +13641,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:5" ht="17" thickBot="1">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -13659,7 +13659,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:5" ht="17" thickBot="1">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -13677,7 +13677,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:5" ht="17" thickBot="1">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:5" ht="17" thickBot="1">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -13713,7 +13713,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:5" ht="17" thickBot="1">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -13731,7 +13731,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:5" ht="17" thickBot="1">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -13749,7 +13749,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:5" ht="17" thickBot="1">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -13767,7 +13767,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:5" ht="17" thickBot="1">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -13785,7 +13785,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:5" ht="17" thickBot="1">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -13803,7 +13803,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:5" ht="17" thickBot="1">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -13821,7 +13821,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:5" ht="17" thickBot="1">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -13839,7 +13839,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:5" ht="17" thickBot="1">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -13857,7 +13857,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:5" ht="17" thickBot="1">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -13875,7 +13875,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:5" ht="17" thickBot="1">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:5" ht="17" thickBot="1">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -13926,7 +13926,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:5" ht="17" thickBot="1">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -13944,7 +13944,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:5" ht="17" thickBot="1">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:5" ht="17" thickBot="1">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -13980,7 +13980,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:5" ht="17" thickBot="1">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -13998,7 +13998,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:5" ht="17" thickBot="1">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:5" ht="17" thickBot="1">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -14034,7 +14034,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:5" ht="17" thickBot="1">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -14052,7 +14052,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:5" ht="17" thickBot="1">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -14070,7 +14070,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:5" ht="17" thickBot="1">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -14088,7 +14088,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:5" ht="17" thickBot="1">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -14106,7 +14106,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:5" ht="17" thickBot="1">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -14124,7 +14124,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:5" ht="17" thickBot="1">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:5" ht="17" thickBot="1">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -14160,7 +14160,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:5" ht="17" thickBot="1">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -14178,7 +14178,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:5" ht="17" thickBot="1">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -14196,7 +14196,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:5" ht="17" thickBot="1">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -14214,7 +14214,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:5" ht="17" thickBot="1">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -14232,7 +14232,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:5" ht="17" thickBot="1">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -14250,7 +14250,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:5" ht="17" thickBot="1">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -14268,7 +14268,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:5" ht="17" thickBot="1">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -14286,7 +14286,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:5" ht="17" thickBot="1">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -14304,7 +14304,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:5" ht="17" thickBot="1">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:5" ht="17" thickBot="1">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:5" ht="17" thickBot="1">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -14358,7 +14358,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:5" ht="17" thickBot="1">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -14376,7 +14376,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:5" ht="17" thickBot="1">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -14394,7 +14394,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:5" ht="17" thickBot="1">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -14412,7 +14412,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:5" ht="17" thickBot="1">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -14430,7 +14430,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:5" ht="17" thickBot="1">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -14448,7 +14448,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:5" ht="17" thickBot="1">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:5" ht="17" thickBot="1">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:5" ht="17" thickBot="1">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -14502,7 +14502,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:5" ht="17" thickBot="1">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -14520,7 +14520,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:5" ht="17" thickBot="1">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:5" ht="17" thickBot="1">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -14556,7 +14556,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:5" ht="17" thickBot="1">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -14574,7 +14574,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:5" ht="17" thickBot="1">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:5" ht="17" thickBot="1">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -14610,7 +14610,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:5" ht="17" thickBot="1">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -14628,7 +14628,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:5" ht="17" thickBot="1">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -14646,7 +14646,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:5" ht="17" thickBot="1">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:5" ht="17" thickBot="1">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:5" ht="17" thickBot="1">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -14700,7 +14700,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:5" ht="17" thickBot="1">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:5" ht="17" thickBot="1">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -14736,7 +14736,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:5" ht="17" thickBot="1">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -14754,7 +14754,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:5" ht="17" thickBot="1">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -14772,7 +14772,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:5" ht="17" thickBot="1">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -14790,7 +14790,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:5" ht="17" thickBot="1">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -14808,7 +14808,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:5" ht="17" thickBot="1">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -14826,7 +14826,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:5" ht="17" thickBot="1">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -14844,7 +14844,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:5" ht="17" thickBot="1">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -14862,7 +14862,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:5" ht="17" thickBot="1">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -14880,7 +14880,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:5" ht="17" thickBot="1">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:5" ht="17" thickBot="1">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -14916,7 +14916,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:5" ht="17" thickBot="1">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -14934,7 +14934,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:5" ht="17" thickBot="1">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -14952,7 +14952,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:5" ht="17" thickBot="1">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -14970,7 +14970,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:5" ht="17" thickBot="1">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -14988,7 +14988,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:5" ht="17" thickBot="1">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -15006,7 +15006,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:5" ht="17" thickBot="1">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -15024,7 +15024,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:5" ht="17" thickBot="1">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -15042,7 +15042,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:5" ht="17" thickBot="1">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -15075,7 +15075,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:5" ht="17" thickBot="1">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -15093,7 +15093,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:5" ht="17" thickBot="1">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -15111,7 +15111,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:5" ht="17" thickBot="1">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -15129,7 +15129,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:5" ht="17" thickBot="1">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -15147,7 +15147,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:5" ht="17" thickBot="1">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -15165,7 +15165,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:5" ht="17" thickBot="1">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -15183,7 +15183,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:5" ht="17" thickBot="1">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -15201,7 +15201,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:5" ht="17" thickBot="1">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -15219,7 +15219,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:5" ht="17" thickBot="1">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -15237,7 +15237,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:5" ht="17" thickBot="1">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -15255,7 +15255,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:5" ht="17" thickBot="1">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -15273,7 +15273,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:5" ht="17" thickBot="1">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -15291,7 +15291,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:5" ht="17" thickBot="1">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -15309,7 +15309,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:5" ht="17" thickBot="1">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:5" ht="17" thickBot="1">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -15345,7 +15345,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:5" ht="17" thickBot="1">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -15363,7 +15363,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:5" ht="17" thickBot="1">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -15381,7 +15381,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:5" ht="17" thickBot="1">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -15399,7 +15399,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:5" ht="17" thickBot="1">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -15417,7 +15417,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:5" ht="17" thickBot="1">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -15435,7 +15435,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:5" ht="17" thickBot="1">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -15453,7 +15453,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:5" ht="17" thickBot="1">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -15471,7 +15471,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:5" ht="17" thickBot="1">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -15489,7 +15489,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:5" ht="17" thickBot="1">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -15507,7 +15507,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:5" ht="17" thickBot="1">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -15525,7 +15525,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:5" ht="17" thickBot="1">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -15543,7 +15543,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:5" ht="17" thickBot="1">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -15561,7 +15561,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:5" ht="17" thickBot="1">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -15579,7 +15579,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:5" ht="17" thickBot="1">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -15597,7 +15597,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:5" ht="17" thickBot="1">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -15615,7 +15615,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:5" ht="17" thickBot="1">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -15633,7 +15633,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:5" ht="17" thickBot="1">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -15651,7 +15651,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:5" ht="17" thickBot="1">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -15669,7 +15669,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:5" ht="17" thickBot="1">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -15687,7 +15687,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:5" ht="17" thickBot="1">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -15705,7 +15705,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:5" ht="17" thickBot="1">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -15723,7 +15723,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:5" ht="17" thickBot="1">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -15741,7 +15741,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:5" ht="17" thickBot="1">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -15759,7 +15759,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:5" ht="17" thickBot="1">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -15777,7 +15777,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:5" ht="17" thickBot="1">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -15795,7 +15795,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:5" ht="17" thickBot="1">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:5" ht="17" thickBot="1">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -15831,7 +15831,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:5" ht="17" thickBot="1">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -15849,7 +15849,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:5" ht="17" thickBot="1">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -15867,7 +15867,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:5" ht="17" thickBot="1">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -15885,7 +15885,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:5" ht="17" thickBot="1">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:5" ht="17" thickBot="1">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -15921,7 +15921,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:5" ht="17" thickBot="1">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -15939,7 +15939,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:5" ht="17" thickBot="1">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -15957,7 +15957,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:5" ht="17" thickBot="1">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -15975,7 +15975,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:5" ht="17" thickBot="1">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:5" ht="17" thickBot="1">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -16011,7 +16011,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:5" ht="17" thickBot="1">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -16029,7 +16029,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:5" ht="17" thickBot="1">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -16047,7 +16047,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:5" ht="17" thickBot="1">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -16065,7 +16065,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:5" ht="17" thickBot="1">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -16083,7 +16083,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:5" ht="17" thickBot="1">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -16101,7 +16101,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:5" ht="17" thickBot="1">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -16119,7 +16119,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:5" ht="17" thickBot="1">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -16137,7 +16137,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:5" ht="17" thickBot="1">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -16155,7 +16155,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:5" ht="17" thickBot="1">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -16173,7 +16173,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:5" ht="17" thickBot="1">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:5" ht="17" thickBot="1">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -16209,7 +16209,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:5" ht="17" thickBot="1">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -16242,7 +16242,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:5" ht="17" thickBot="1">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -16260,7 +16260,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:5" ht="17" thickBot="1">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -16278,7 +16278,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:5" ht="17" thickBot="1">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:5" ht="17" thickBot="1">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -16314,7 +16314,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:5" ht="17" thickBot="1">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -16332,7 +16332,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:5" ht="17" thickBot="1">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -16350,7 +16350,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:5" ht="17" thickBot="1">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -16368,7 +16368,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:5" ht="17" thickBot="1">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -16386,7 +16386,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:5" ht="17" thickBot="1">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -16404,7 +16404,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:5" ht="17" thickBot="1">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:5" ht="17" thickBot="1">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -16440,7 +16440,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:5" ht="17" thickBot="1">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:5" ht="17" thickBot="1">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -16476,7 +16476,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:5" ht="17" thickBot="1">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -16494,7 +16494,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:5" ht="17" thickBot="1">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -16512,7 +16512,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:5" ht="17" thickBot="1">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -16530,7 +16530,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:5" ht="17" thickBot="1">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -16548,7 +16548,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:5" ht="17" thickBot="1">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:5" ht="17" thickBot="1">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -16584,7 +16584,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:5" ht="17" thickBot="1">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -16602,7 +16602,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:5" ht="17" thickBot="1">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -16620,7 +16620,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:5" ht="17" thickBot="1">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -16638,7 +16638,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:5" ht="17" thickBot="1">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -16656,7 +16656,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:5" ht="17" thickBot="1">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -16674,7 +16674,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:5" ht="17" thickBot="1">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -16692,7 +16692,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:5" ht="17" thickBot="1">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:5" ht="17" thickBot="1">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -16728,7 +16728,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:5" ht="17" thickBot="1">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -16746,7 +16746,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:5" ht="17" thickBot="1">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -16764,7 +16764,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:5" ht="17" thickBot="1">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -16782,7 +16782,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:5" ht="17" thickBot="1">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -16800,7 +16800,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:5" ht="17" thickBot="1">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -16818,7 +16818,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:5" ht="17" thickBot="1">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -16836,7 +16836,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:5" ht="17" thickBot="1">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -16854,7 +16854,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:5" ht="17" thickBot="1">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -16872,7 +16872,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:5" ht="17" thickBot="1">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -16890,7 +16890,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:5" ht="17" thickBot="1">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -16908,7 +16908,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:5" ht="17" thickBot="1">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -16926,7 +16926,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:5" ht="17" thickBot="1">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -16944,7 +16944,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:5" ht="17" thickBot="1">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -16962,7 +16962,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:5" ht="17" thickBot="1">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -16980,7 +16980,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:5" ht="17" thickBot="1">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -16998,7 +16998,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:5" ht="17" thickBot="1">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -17016,7 +17016,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:5" ht="17" thickBot="1">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -17034,7 +17034,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:5" ht="17" thickBot="1">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -17052,7 +17052,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:5" ht="17" thickBot="1">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -17070,7 +17070,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:5" ht="17" thickBot="1">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -17088,7 +17088,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:5" ht="17" thickBot="1">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -17106,7 +17106,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:5" ht="17" thickBot="1">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -17124,7 +17124,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:5" ht="17" thickBot="1">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -17142,7 +17142,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:5" ht="17" thickBot="1">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -17160,7 +17160,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:5" ht="17" thickBot="1">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -17178,7 +17178,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:5" ht="17" thickBot="1">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -17196,7 +17196,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:5" ht="17" thickBot="1">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -17214,7 +17214,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:5" ht="17" thickBot="1">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -17232,7 +17232,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:5" ht="17" thickBot="1">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -17250,7 +17250,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:5" ht="17" thickBot="1">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -17268,7 +17268,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:5" ht="17" thickBot="1">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -17286,7 +17286,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:5" ht="17" thickBot="1">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -17304,7 +17304,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:5" ht="17" thickBot="1">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -17322,7 +17322,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:5" ht="17" thickBot="1">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -17340,7 +17340,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:5" ht="17" thickBot="1">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -17358,7 +17358,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:5" ht="17" thickBot="1">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -17376,7 +17376,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:5" ht="17" thickBot="1">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -17409,7 +17409,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:5" ht="17" thickBot="1">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -17427,7 +17427,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:5" ht="17" thickBot="1">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -17445,7 +17445,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:5" ht="17" thickBot="1">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -17463,7 +17463,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:5" ht="17" thickBot="1">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -17481,7 +17481,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:5" ht="17" thickBot="1">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -17499,7 +17499,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:5" ht="17" thickBot="1">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -17517,7 +17517,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:5" ht="17" thickBot="1">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -17535,7 +17535,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:5" ht="17" thickBot="1">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -17553,7 +17553,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:5" ht="17" thickBot="1">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -17571,7 +17571,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:5" ht="17" thickBot="1">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -17589,7 +17589,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:5" ht="17" thickBot="1">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -17607,7 +17607,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:5" ht="17" thickBot="1">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -17625,7 +17625,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:5" ht="17" thickBot="1">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:5" ht="17" thickBot="1">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -17661,7 +17661,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:5" ht="17" thickBot="1">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -17679,7 +17679,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:5" ht="17" thickBot="1">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -17697,7 +17697,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:5" ht="17" thickBot="1">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -17715,7 +17715,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:5" ht="17" thickBot="1">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -17733,7 +17733,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:5" ht="17" thickBot="1">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -17751,7 +17751,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:5" ht="17" thickBot="1">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -17769,7 +17769,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:5" ht="17" thickBot="1">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:5" ht="17" thickBot="1">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -17805,7 +17805,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:5" ht="17" thickBot="1">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -17823,7 +17823,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:5" ht="17" thickBot="1">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -17841,7 +17841,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:5" ht="17" thickBot="1">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -17859,7 +17859,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:5" ht="17" thickBot="1">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -17877,7 +17877,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:5" ht="17" thickBot="1">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -17895,7 +17895,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:5" ht="17" thickBot="1">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -17913,7 +17913,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:5" ht="17" thickBot="1">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:5" ht="17" thickBot="1">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -17949,7 +17949,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:5" ht="17" thickBot="1">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -17967,7 +17967,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:5" ht="17" thickBot="1">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -17985,7 +17985,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:5" ht="17" thickBot="1">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -18003,7 +18003,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:5" ht="17" thickBot="1">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -18021,7 +18021,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:5" ht="17" thickBot="1">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -18039,7 +18039,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:5" ht="17" thickBot="1">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -18057,7 +18057,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:5" ht="17" thickBot="1">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -18075,7 +18075,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:5" ht="17" thickBot="1">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -18093,7 +18093,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:5" ht="17" thickBot="1">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -18111,7 +18111,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:5" ht="17" thickBot="1">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -18129,7 +18129,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:5" ht="17" thickBot="1">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -18147,7 +18147,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:5" ht="17" thickBot="1">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -18165,7 +18165,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:5" ht="17" thickBot="1">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:5" ht="17" thickBot="1">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -18201,7 +18201,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:5" ht="17" thickBot="1">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -18219,7 +18219,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:5" ht="17" thickBot="1">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -18237,7 +18237,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:5" ht="17" thickBot="1">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -18255,7 +18255,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:5" ht="17" thickBot="1">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:5" ht="17" thickBot="1">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -18291,7 +18291,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:5" ht="17" thickBot="1">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -18309,7 +18309,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:5" ht="17" thickBot="1">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -18327,7 +18327,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:5" ht="17" thickBot="1">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -18345,7 +18345,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:5" ht="17" thickBot="1">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -18363,7 +18363,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:5" ht="17" thickBot="1">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -18381,7 +18381,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:5" ht="17" thickBot="1">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -18399,7 +18399,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:5" ht="17" thickBot="1">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:5" ht="17" thickBot="1">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -18435,7 +18435,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:5" ht="17" thickBot="1">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -18453,7 +18453,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:5" ht="17" thickBot="1">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -18471,7 +18471,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:5" ht="17" thickBot="1">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -18489,7 +18489,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:5" ht="17" thickBot="1">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -18507,7 +18507,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:5" ht="17" thickBot="1">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:5" ht="17" thickBot="1">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -18543,7 +18543,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:5" ht="17" thickBot="1">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -18576,7 +18576,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:5" ht="17" thickBot="1">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -18594,7 +18594,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:5" ht="17" thickBot="1">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -18612,7 +18612,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:5" ht="17" thickBot="1">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -18630,7 +18630,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:5" ht="17" thickBot="1">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:5" ht="17" thickBot="1">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -18666,7 +18666,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:5" ht="17" thickBot="1">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -18684,7 +18684,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:5" ht="17" thickBot="1">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -18702,7 +18702,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:5" ht="17" thickBot="1">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -18720,7 +18720,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:5" ht="17" thickBot="1">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -18738,7 +18738,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:5" ht="17" thickBot="1">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -18756,7 +18756,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:5" ht="17" thickBot="1">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -18774,7 +18774,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:5" ht="17" thickBot="1">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:5" ht="17" thickBot="1">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -18810,7 +18810,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:5" ht="17" thickBot="1">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -18828,7 +18828,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:5" ht="17" thickBot="1">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -18846,7 +18846,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:5" ht="17" thickBot="1">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -18864,7 +18864,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:5" ht="17" thickBot="1">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -18882,7 +18882,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:5" ht="17" thickBot="1">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -18900,7 +18900,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:5" ht="17" thickBot="1">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -18918,7 +18918,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:5" ht="17" thickBot="1">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -18936,7 +18936,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:5" ht="17" thickBot="1">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -18954,7 +18954,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:5" ht="17" thickBot="1">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -18972,7 +18972,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:5" ht="17" thickBot="1">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -18990,7 +18990,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:5" ht="17" thickBot="1">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -19008,7 +19008,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:5" ht="17" thickBot="1">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -19026,7 +19026,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:5" ht="17" thickBot="1">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -19044,7 +19044,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:5" ht="17" thickBot="1">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -19062,7 +19062,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:5" ht="17" thickBot="1">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -19080,7 +19080,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:5" ht="17" thickBot="1">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -19098,7 +19098,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:5" ht="17" thickBot="1">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -19116,7 +19116,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:5" ht="17" thickBot="1">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -19134,7 +19134,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:5" ht="17" thickBot="1">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -19152,7 +19152,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:5" ht="17" thickBot="1">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -19170,7 +19170,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:5" ht="17" thickBot="1">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -19188,7 +19188,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:5" ht="17" thickBot="1">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -19206,7 +19206,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:5" ht="17" thickBot="1">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -19224,7 +19224,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:5" ht="17" thickBot="1">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -19242,7 +19242,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:5" ht="17" thickBot="1">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -19260,7 +19260,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:5" ht="17" thickBot="1">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -19278,7 +19278,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:5" ht="17" thickBot="1">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -19296,7 +19296,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:5" ht="17" thickBot="1">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -19314,7 +19314,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:5" ht="17" thickBot="1">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -19332,7 +19332,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:5" ht="17" thickBot="1">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:5" ht="17" thickBot="1">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -19368,7 +19368,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:5" ht="17" thickBot="1">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -19386,7 +19386,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:5" ht="17" thickBot="1">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -19404,7 +19404,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:5" ht="17" thickBot="1">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -19422,7 +19422,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:5" ht="17" thickBot="1">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -19440,7 +19440,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:5" ht="17" thickBot="1">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -19458,7 +19458,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:5" ht="17" thickBot="1">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -19476,7 +19476,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:5" ht="17" thickBot="1">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -19494,7 +19494,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:5" ht="17" thickBot="1">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:5" ht="17" thickBot="1">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -19530,7 +19530,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:5" ht="17" thickBot="1">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -19548,7 +19548,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:5" ht="17" thickBot="1">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -19566,7 +19566,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:5" ht="17" thickBot="1">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -19584,7 +19584,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:5" ht="17" thickBot="1">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -19602,7 +19602,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:5" ht="17" thickBot="1">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -19620,7 +19620,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:5" ht="17" thickBot="1">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -19638,7 +19638,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:5" ht="17" thickBot="1">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -19656,7 +19656,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:5" ht="17" thickBot="1">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:5" ht="17" thickBot="1">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:5" ht="17" thickBot="1">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -19710,7 +19710,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:5" ht="17" thickBot="1">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -19743,7 +19743,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:5" ht="17" thickBot="1">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -19761,7 +19761,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:5" ht="17" thickBot="1">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -19779,7 +19779,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:5" ht="17" thickBot="1">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -19797,7 +19797,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:5" ht="17" thickBot="1">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -19815,7 +19815,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:5" ht="17" thickBot="1">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -19833,7 +19833,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:5" ht="17" thickBot="1">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -19851,7 +19851,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:5" ht="17" thickBot="1">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -19869,7 +19869,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:5" ht="17" thickBot="1">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -19887,7 +19887,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:5" ht="17" thickBot="1">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -19905,7 +19905,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:5" ht="17" thickBot="1">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -19923,7 +19923,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:5" ht="17" thickBot="1">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -19941,7 +19941,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:5" ht="17" thickBot="1">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -19959,7 +19959,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:5" ht="17" thickBot="1">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -19977,7 +19977,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:5" ht="17" thickBot="1">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -19995,7 +19995,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:5" ht="17" thickBot="1">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -20013,7 +20013,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:5" ht="17" thickBot="1">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -20031,7 +20031,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:5" ht="17" thickBot="1">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -20049,7 +20049,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:5" ht="17" thickBot="1">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -20067,7 +20067,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:5" ht="17" thickBot="1">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -20085,7 +20085,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:5" ht="17" thickBot="1">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -20103,7 +20103,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:5" ht="17" thickBot="1">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:5" ht="17" thickBot="1">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -20139,7 +20139,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:5" ht="17" thickBot="1">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -20157,7 +20157,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:5" ht="17" thickBot="1">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -20175,7 +20175,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:5" ht="17" thickBot="1">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -20193,7 +20193,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:5" ht="17" thickBot="1">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -20211,7 +20211,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:5" ht="17" thickBot="1">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -20229,7 +20229,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:5" ht="17" thickBot="1">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -20247,7 +20247,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:5" ht="17" thickBot="1">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -20265,7 +20265,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:5" ht="17" thickBot="1">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -20283,7 +20283,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:5" ht="17" thickBot="1">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -20301,7 +20301,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:5" ht="17" thickBot="1">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -20319,7 +20319,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:5" ht="17" thickBot="1">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -20337,7 +20337,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:5" ht="17" thickBot="1">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -20355,7 +20355,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:5" ht="17" thickBot="1">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -20373,7 +20373,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:5" ht="17" thickBot="1">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -20391,7 +20391,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:5" ht="17" thickBot="1">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -20409,7 +20409,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:5" ht="17" thickBot="1">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -20427,7 +20427,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:5" ht="17" thickBot="1">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -20445,7 +20445,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:5" ht="17" thickBot="1">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -20463,7 +20463,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:5" ht="17" thickBot="1">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -20481,7 +20481,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:5" ht="17" thickBot="1">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -20499,7 +20499,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:5" ht="17" thickBot="1">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -20517,7 +20517,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:5" ht="17" thickBot="1">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -20535,7 +20535,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:5" ht="17" thickBot="1">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -20553,7 +20553,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:5" ht="17" thickBot="1">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -20571,7 +20571,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:5" ht="17" thickBot="1">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -20589,7 +20589,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:5" ht="17" thickBot="1">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -20607,7 +20607,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:5" ht="17" thickBot="1">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -20625,7 +20625,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:5" ht="17" thickBot="1">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -20643,7 +20643,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:5" ht="17" thickBot="1">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -20661,7 +20661,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:5" ht="17" thickBot="1">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -20679,7 +20679,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:5" ht="17" thickBot="1">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -20697,7 +20697,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:5" ht="17" thickBot="1">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -20715,7 +20715,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:5" ht="17" thickBot="1">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -20733,7 +20733,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:5" ht="17" thickBot="1">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -20751,7 +20751,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:5" ht="17" thickBot="1">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -20769,7 +20769,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:5" ht="17" thickBot="1">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -20787,7 +20787,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:5" ht="17" thickBot="1">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -20805,7 +20805,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:5" ht="17" thickBot="1">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -20823,7 +20823,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:5" ht="17" thickBot="1">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -20841,7 +20841,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:5" ht="17" thickBot="1">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -20859,7 +20859,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:5" ht="17" thickBot="1">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -20877,7 +20877,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:5" ht="17" thickBot="1">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -20910,7 +20910,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:5" ht="17" thickBot="1">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -20928,7 +20928,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:5" ht="17" thickBot="1">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -20946,7 +20946,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:5" ht="17" thickBot="1">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -20964,7 +20964,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:5" ht="17" thickBot="1">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -20982,7 +20982,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:5" ht="17" thickBot="1">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -21000,7 +21000,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:5" ht="17" thickBot="1">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -21018,7 +21018,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:5" ht="17" thickBot="1">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -21036,7 +21036,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:5" ht="17" thickBot="1">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -21054,7 +21054,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:5" ht="17" thickBot="1">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -21072,7 +21072,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:5" ht="17" thickBot="1">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -21090,7 +21090,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:5" ht="17" thickBot="1">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -21108,7 +21108,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="782" spans="1:5" ht="17" thickBot="1">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -21126,7 +21126,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="783" spans="1:5" ht="17" thickBot="1">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -21144,7 +21144,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="784" spans="1:5" ht="17" thickBot="1">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -21162,7 +21162,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="785" spans="1:5" ht="17" thickBot="1">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -21180,7 +21180,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="786" spans="1:5" ht="17" thickBot="1">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -21198,7 +21198,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="787" spans="1:5" ht="17" thickBot="1">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -21216,7 +21216,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="788" spans="1:5" ht="17" thickBot="1">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -21234,7 +21234,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="789" spans="1:5" ht="17" thickBot="1">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -21252,7 +21252,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="790" spans="1:5" ht="17" thickBot="1">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -21270,7 +21270,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="791" spans="1:5" ht="17" thickBot="1">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -21288,7 +21288,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="792" spans="1:5" ht="17" thickBot="1">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -21306,7 +21306,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="793" spans="1:5" ht="17" thickBot="1">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -21324,7 +21324,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="794" spans="1:5" ht="17" thickBot="1">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -21342,7 +21342,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="795" spans="1:5" ht="17" thickBot="1">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -21360,7 +21360,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="796" spans="1:5" ht="17" thickBot="1">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -21378,7 +21378,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="797" spans="1:5" ht="17" thickBot="1">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -21396,7 +21396,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="798" spans="1:5" ht="17" thickBot="1">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -21414,7 +21414,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="799" spans="1:5" ht="17" thickBot="1">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -21432,7 +21432,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="800" spans="1:5" ht="17" thickBot="1">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -21450,7 +21450,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="801" spans="1:5" ht="17" thickBot="1">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -21468,7 +21468,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="802" spans="1:5" ht="17" thickBot="1">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -21486,7 +21486,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="803" spans="1:5" ht="17" thickBot="1">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -21504,7 +21504,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="804" spans="1:5" ht="17" thickBot="1">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -21522,7 +21522,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="805" spans="1:5" ht="17" thickBot="1">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -21540,7 +21540,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="806" spans="1:5" ht="17" thickBot="1">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -21558,7 +21558,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="807" spans="1:5" ht="17" thickBot="1">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -21576,7 +21576,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="808" spans="1:5" ht="17" thickBot="1">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -21594,7 +21594,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="809" spans="1:5" ht="17" thickBot="1">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -21612,7 +21612,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="810" spans="1:5" ht="17" thickBot="1">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -21630,7 +21630,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="811" spans="1:5" ht="17" thickBot="1">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -21648,7 +21648,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="812" spans="1:5" ht="17" thickBot="1">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -21666,7 +21666,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="813" spans="1:5" ht="17" thickBot="1">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -21684,7 +21684,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="814" spans="1:5" ht="17" thickBot="1">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -21702,7 +21702,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="815" spans="1:5" ht="17" thickBot="1">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -21720,7 +21720,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="816" spans="1:5" ht="17" thickBot="1">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -21738,7 +21738,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="817" spans="1:5" ht="17" thickBot="1">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -21756,7 +21756,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="818" spans="1:5" ht="17" thickBot="1">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -21774,7 +21774,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="819" spans="1:5" ht="17" thickBot="1">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -21792,7 +21792,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="820" spans="1:5" ht="17" thickBot="1">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -21810,7 +21810,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="821" spans="1:5" ht="17" thickBot="1">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -21828,7 +21828,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="822" spans="1:5" ht="17" thickBot="1">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -21846,7 +21846,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="823" spans="1:5" ht="17" thickBot="1">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -21864,7 +21864,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="824" spans="1:5" ht="17" thickBot="1">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -21882,7 +21882,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="825" spans="1:5" ht="17" thickBot="1">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -21900,7 +21900,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="826" spans="1:5" ht="17" thickBot="1">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -21918,7 +21918,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="827" spans="1:5" ht="17" thickBot="1">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -21936,7 +21936,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="828" spans="1:5" ht="17" thickBot="1">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -21954,7 +21954,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="829" spans="1:5" ht="17" thickBot="1">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -21972,7 +21972,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="830" spans="1:5" ht="17" thickBot="1">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -21990,7 +21990,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="831" spans="1:5" ht="17" thickBot="1">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -22008,7 +22008,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="832" spans="1:5" ht="17" thickBot="1">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -22026,7 +22026,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="833" spans="1:5" ht="17" thickBot="1">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -22044,7 +22044,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="834" spans="1:5" ht="17" thickBot="1">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -22077,7 +22077,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="835" spans="1:5" ht="17" thickBot="1">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -22095,7 +22095,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="836" spans="1:5" ht="17" thickBot="1">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -22113,7 +22113,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="837" spans="1:5" ht="17" thickBot="1">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -22131,7 +22131,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="838" spans="1:5" ht="17" thickBot="1">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -22149,7 +22149,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="839" spans="1:5" ht="17" thickBot="1">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -22167,7 +22167,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="840" spans="1:5" ht="17" thickBot="1">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -22185,7 +22185,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="841" spans="1:5" ht="17" thickBot="1">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -22203,7 +22203,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="842" spans="1:5" ht="17" thickBot="1">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -22221,7 +22221,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="843" spans="1:5" ht="17" thickBot="1">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -22239,7 +22239,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="844" spans="1:5" ht="17" thickBot="1">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -22257,7 +22257,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="845" spans="1:5" ht="17" thickBot="1">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -22275,7 +22275,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="846" spans="1:5" ht="17" thickBot="1">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -22293,7 +22293,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="847" spans="1:5" ht="17" thickBot="1">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -22311,7 +22311,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="848" spans="1:5" ht="17" thickBot="1">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -22329,7 +22329,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="849" spans="1:5" ht="17" thickBot="1">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -22347,7 +22347,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="850" spans="1:5" ht="17" thickBot="1">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -22365,7 +22365,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="851" spans="1:5" ht="17" thickBot="1">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -22383,7 +22383,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="852" spans="1:5" ht="17" thickBot="1">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -22401,7 +22401,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="853" spans="1:5" ht="17" thickBot="1">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -22419,7 +22419,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="854" spans="1:5" ht="17" thickBot="1">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -22437,7 +22437,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="855" spans="1:5" ht="17" thickBot="1">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -22455,7 +22455,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="856" spans="1:5" ht="17" thickBot="1">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -22473,7 +22473,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="857" spans="1:5" ht="17" thickBot="1">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -22491,7 +22491,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="858" spans="1:5" ht="17" thickBot="1">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -22509,7 +22509,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="859" spans="1:5" ht="17" thickBot="1">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -22527,7 +22527,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="860" spans="1:5" ht="17" thickBot="1">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -22545,7 +22545,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="861" spans="1:5" ht="17" thickBot="1">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -22563,7 +22563,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="862" spans="1:5" ht="17" thickBot="1">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -22581,7 +22581,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="863" spans="1:5" ht="17" thickBot="1">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -22599,7 +22599,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="864" spans="1:5" ht="17" thickBot="1">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -22617,7 +22617,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="865" spans="1:5" ht="17" thickBot="1">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -22635,7 +22635,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="866" spans="1:5" ht="17" thickBot="1">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -22653,7 +22653,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="867" spans="1:5" ht="17" thickBot="1">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -22671,7 +22671,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="868" spans="1:5" ht="17" thickBot="1">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -22689,7 +22689,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="869" spans="1:5" ht="17" thickBot="1">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -22707,7 +22707,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="870" spans="1:5" ht="17" thickBot="1">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -22725,7 +22725,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="871" spans="1:5" ht="17" thickBot="1">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -22743,7 +22743,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="872" spans="1:5" ht="17" thickBot="1">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -22761,7 +22761,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="873" spans="1:5" ht="17" thickBot="1">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -22779,7 +22779,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="874" spans="1:5" ht="17" thickBot="1">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -22797,7 +22797,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="875" spans="1:5" ht="17" thickBot="1">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -22815,7 +22815,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="876" spans="1:5" ht="17" thickBot="1">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -22833,7 +22833,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="877" spans="1:5" ht="17" thickBot="1">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -22851,7 +22851,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="878" spans="1:5" ht="17" thickBot="1">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -22884,7 +22884,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="879" spans="1:5" ht="17" thickBot="1">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -22917,7 +22917,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="880" spans="1:5" ht="17" thickBot="1">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -22950,7 +22950,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="881" spans="1:5" ht="17" thickBot="1">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -22968,7 +22968,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="882" spans="1:5" ht="17" thickBot="1">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -23001,7 +23001,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="883" spans="1:5" ht="17" thickBot="1">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -23034,7 +23034,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="884" spans="1:5" ht="17" thickBot="1">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
@@ -23052,7 +23052,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="885" spans="1:5" ht="17" thickBot="1">
       <c r="A885" s="15">
         <v>46088</v>
       </c>
@@ -23070,7 +23070,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:5" ht="16">
       <c r="A886" s="8">
         <v>46102</v>
       </c>
@@ -23088,7 +23088,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:5" ht="16">
       <c r="A887" s="8">
         <v>46109</v>
       </c>
@@ -23106,7 +23106,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:5" ht="16">
       <c r="A888" s="8">
         <v>46116</v>
       </c>
@@ -23124,7 +23124,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:5" ht="16">
       <c r="A889" s="8">
         <v>46123</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>500040</v>
       </c>
     </row>
-    <row r="890" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:5" ht="16">
       <c r="A890" s="8">
         <v>46130</v>
       </c>
@@ -23160,7 +23160,7 @@
         <v>508303</v>
       </c>
     </row>
-    <row r="891" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:5" ht="16">
       <c r="A891" s="8">
         <v>46137</v>
       </c>
@@ -23178,7 +23178,7 @@
         <v>511616</v>
       </c>
     </row>
-    <row r="892" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:5" ht="16">
       <c r="A892" s="8">
         <v>46144</v>
       </c>
@@ -23196,7 +23196,7 @@
         <v>518773</v>
       </c>
     </row>
-    <row r="893" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:5" ht="16">
       <c r="A893" s="8">
         <v>46151</v>
       </c>
@@ -23229,7 +23229,7 @@
         <v>513755</v>
       </c>
     </row>
-    <row r="894" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:5" ht="16">
       <c r="A894" s="8">
         <v>46158</v>
       </c>
@@ -23247,7 +23247,7 @@
         <v>511216</v>
       </c>
     </row>
-    <row r="895" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:5" ht="16">
       <c r="A895" s="8">
         <v>46165</v>
       </c>
@@ -23265,7 +23265,7 @@
         <v>523574</v>
       </c>
     </row>
-    <row r="896" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:5" ht="16">
       <c r="A896" s="8">
         <v>46172</v>
       </c>
@@ -23298,7 +23298,7 @@
         <v>492795</v>
       </c>
     </row>
-    <row r="897" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:5" ht="16">
       <c r="A897" s="8">
         <v>46179</v>
       </c>
@@ -23316,7 +23316,7 @@
         <v>521804</v>
       </c>
     </row>
-    <row r="898" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:5" ht="16">
       <c r="A898" s="8">
         <v>46186</v>
       </c>
@@ -23334,7 +23334,7 @@
         <v>520406</v>
       </c>
     </row>
-    <row r="899" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:5" ht="16">
       <c r="A899" s="8">
         <v>46193</v>
       </c>
@@ -23367,7 +23367,7 @@
         <v>521998</v>
       </c>
     </row>
-    <row r="900" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:5" ht="16">
       <c r="A900" s="8">
         <v>46200</v>
       </c>
@@ -23385,7 +23385,7 @@
         <v>525474</v>
       </c>
     </row>
-    <row r="901" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:5" ht="16">
       <c r="A901" s="8">
         <v>46207</v>
       </c>
@@ -23418,7 +23418,7 @@
         <v>482121</v>
       </c>
     </row>
-    <row r="902" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:5" ht="16">
       <c r="A902" s="8">
         <v>46214</v>
       </c>
@@ -23436,7 +23436,7 @@
         <v>503525</v>
       </c>
     </row>
-    <row r="903" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:5" ht="16">
       <c r="A903" s="8">
         <v>46221</v>
       </c>
@@ -23454,7 +23454,7 @@
         <v>523900</v>
       </c>
     </row>
-    <row r="904" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:5" ht="16">
       <c r="A904" s="8">
         <v>46228</v>
       </c>
@@ -23487,7 +23487,7 @@
         <v>527162</v>
       </c>
     </row>
-    <row r="905" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:5" ht="16">
       <c r="A905" s="8">
         <v>46235</v>
       </c>
@@ -23505,7 +23505,7 @@
         <v>526410</v>
       </c>
     </row>
-    <row r="906" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:5" ht="16">
       <c r="A906" s="8">
         <v>46242</v>
       </c>
@@ -23513,7 +23513,7 @@
         <v>46246</v>
       </c>
       <c r="C906" s="21">
-        <v>0.5</v>
+        <v>0.50069444444444444</v>
       </c>
       <c r="D906" s="7" t="str">
         <f t="shared" ref="D906" si="21">IF(
@@ -23534,6 +23534,9 @@
 )</f>
         <v>UTC-4</v>
       </c>
+      <c r="E906" s="20">
+        <v>526624</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">
@@ -23548,7 +23551,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23559,12 +23562,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23572,7 +23575,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23580,7 +23583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03223FB-EA7D-C24B-AF44-EE24A99BE524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155FC8E2-A783-4C8A-80CB-4E2470ADE9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -86,12 +86,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -189,7 +189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -206,68 +206,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -285,7 +285,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6534,9 +6534,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6574,7 +6574,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6680,7 +6680,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6822,7 +6822,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6830,18 +6830,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E906"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
+  <dimension ref="A1:E907"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.1640625" style="6"/>
+    <col min="3" max="3" width="11.77734375" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="16">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="16">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="16">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="16">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -7122,7 +7122,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="16">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="16">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="16">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="16">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="16">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="16">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="16">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="16">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="16">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="16">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="16">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="16">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="16">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="16">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="16">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="16">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="16">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="16">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="16">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="16">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="16">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="16">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="16">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="16">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="16">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="16">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="16">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="16">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="16">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -7644,7 +7644,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="16">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="16">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="16">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="16">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="16">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="16">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="16">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="16">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="16">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="16">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="16">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="16">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -7860,7 +7860,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="16">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="16">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -7896,7 +7896,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="16">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="16">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="16">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="16">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="16">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="16">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="16">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="16">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -8040,7 +8040,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="16">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="16">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="16">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="16">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -8127,7 +8127,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="16">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="16">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="16">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -8181,7 +8181,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="16">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="16">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="16">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="16">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="16">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -8271,7 +8271,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="16">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="16">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="16">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="16">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="16">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="16">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="16">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -8397,7 +8397,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="16">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="16">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="16">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="16">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="16">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="16">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="16">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="16">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -8541,7 +8541,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="16">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -8559,7 +8559,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="16">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="16">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="16">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="16">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="16">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="16">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="16">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="17" thickBot="1">
+    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="17" thickBot="1">
+    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="17" thickBot="1">
+    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="17" thickBot="1">
+    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="17" thickBot="1">
+    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="17" thickBot="1">
+    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="17" thickBot="1">
+    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="17" thickBot="1">
+    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -8829,7 +8829,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="17" thickBot="1">
+    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="17" thickBot="1">
+    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="17" thickBot="1">
+    <row r="111" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="17" thickBot="1">
+    <row r="112" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="17" thickBot="1">
+    <row r="113" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -8919,7 +8919,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="17" thickBot="1">
+    <row r="114" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -8937,7 +8937,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="17" thickBot="1">
+    <row r="115" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="17" thickBot="1">
+    <row r="116" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="17" thickBot="1">
+    <row r="117" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="17" thickBot="1">
+    <row r="118" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="17" thickBot="1">
+    <row r="119" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="17" thickBot="1">
+    <row r="120" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="17" thickBot="1">
+    <row r="121" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="17" thickBot="1">
+    <row r="122" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="17" thickBot="1">
+    <row r="123" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="17" thickBot="1">
+    <row r="124" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -9117,7 +9117,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="17" thickBot="1">
+    <row r="125" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="17" thickBot="1">
+    <row r="126" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="17" thickBot="1">
+    <row r="127" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="17" thickBot="1">
+    <row r="128" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -9189,7 +9189,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="17" thickBot="1">
+    <row r="129" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -9207,7 +9207,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="17" thickBot="1">
+    <row r="130" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="17" thickBot="1">
+    <row r="131" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="17" thickBot="1">
+    <row r="132" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="17" thickBot="1">
+    <row r="133" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="17" thickBot="1">
+    <row r="134" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="17" thickBot="1">
+    <row r="135" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="17" thickBot="1">
+    <row r="136" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="17" thickBot="1">
+    <row r="137" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="17" thickBot="1">
+    <row r="138" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="17" thickBot="1">
+    <row r="139" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="17" thickBot="1">
+    <row r="140" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="17" thickBot="1">
+    <row r="141" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="17" thickBot="1">
+    <row r="142" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -9456,7 +9456,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="17" thickBot="1">
+    <row r="143" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="17" thickBot="1">
+    <row r="144" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="17" thickBot="1">
+    <row r="145" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="17" thickBot="1">
+    <row r="146" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="17" thickBot="1">
+    <row r="147" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="17" thickBot="1">
+    <row r="148" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="17" thickBot="1">
+    <row r="149" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -9582,7 +9582,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="17" thickBot="1">
+    <row r="150" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="17" thickBot="1">
+    <row r="151" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="17" thickBot="1">
+    <row r="152" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="17" thickBot="1">
+    <row r="153" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="17" thickBot="1">
+    <row r="154" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="17" thickBot="1">
+    <row r="155" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="17" thickBot="1">
+    <row r="156" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -9708,7 +9708,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="17" thickBot="1">
+    <row r="157" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -9726,7 +9726,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="17" thickBot="1">
+    <row r="158" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="17" thickBot="1">
+    <row r="159" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -9762,7 +9762,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="17" thickBot="1">
+    <row r="160" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="17" thickBot="1">
+    <row r="161" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="17" thickBot="1">
+    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="17" thickBot="1">
+    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="17" thickBot="1">
+    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="17" thickBot="1">
+    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="17" thickBot="1">
+    <row r="166" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="17" thickBot="1">
+    <row r="167" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="17" thickBot="1">
+    <row r="168" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="17" thickBot="1">
+    <row r="169" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="17" thickBot="1">
+    <row r="170" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -9960,7 +9960,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="17" thickBot="1">
+    <row r="171" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -9978,7 +9978,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="17" thickBot="1">
+    <row r="172" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -9996,7 +9996,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="17" thickBot="1">
+    <row r="173" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="17" thickBot="1">
+    <row r="174" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -10032,7 +10032,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="17" thickBot="1">
+    <row r="175" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="17" thickBot="1">
+    <row r="176" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="17" thickBot="1">
+    <row r="177" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="17" thickBot="1">
+    <row r="178" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="17" thickBot="1">
+    <row r="179" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="17" thickBot="1">
+    <row r="180" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -10140,7 +10140,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="17" thickBot="1">
+    <row r="181" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="17" thickBot="1">
+    <row r="182" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -10176,7 +10176,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="17" thickBot="1">
+    <row r="183" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="17" thickBot="1">
+    <row r="184" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -10212,7 +10212,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="17" thickBot="1">
+    <row r="185" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="17" thickBot="1">
+    <row r="186" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -10248,7 +10248,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="17" thickBot="1">
+    <row r="187" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="17" thickBot="1">
+    <row r="188" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="17" thickBot="1">
+    <row r="189" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="17" thickBot="1">
+    <row r="190" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -10320,7 +10320,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="17" thickBot="1">
+    <row r="191" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -10338,7 +10338,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="17" thickBot="1">
+    <row r="192" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -10356,7 +10356,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="17" thickBot="1">
+    <row r="193" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="17" thickBot="1">
+    <row r="194" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="17" thickBot="1">
+    <row r="195" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="17" thickBot="1">
+    <row r="196" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -10443,7 +10443,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="17" thickBot="1">
+    <row r="197" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -10461,7 +10461,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="17" thickBot="1">
+    <row r="198" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="17" thickBot="1">
+    <row r="199" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -10497,7 +10497,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="17" thickBot="1">
+    <row r="200" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -10515,7 +10515,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="17" thickBot="1">
+    <row r="201" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="17" thickBot="1">
+    <row r="202" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="17" thickBot="1">
+    <row r="203" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -10569,7 +10569,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="17" thickBot="1">
+    <row r="204" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -10587,7 +10587,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="17" thickBot="1">
+    <row r="205" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="17" thickBot="1">
+    <row r="206" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="17" thickBot="1">
+    <row r="207" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -10641,7 +10641,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="17" thickBot="1">
+    <row r="208" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -10659,7 +10659,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="17" thickBot="1">
+    <row r="209" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -10677,7 +10677,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="17" thickBot="1">
+    <row r="210" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="17" thickBot="1">
+    <row r="211" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="17" thickBot="1">
+    <row r="212" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -10731,7 +10731,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="17" thickBot="1">
+    <row r="213" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="17" thickBot="1">
+    <row r="214" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -10767,7 +10767,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="17" thickBot="1">
+    <row r="215" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="17" thickBot="1">
+    <row r="216" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="17" thickBot="1">
+    <row r="217" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="17" thickBot="1">
+    <row r="218" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -10839,7 +10839,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="17" thickBot="1">
+    <row r="219" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="17" thickBot="1">
+    <row r="220" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="17" thickBot="1">
+    <row r="221" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="17" thickBot="1">
+    <row r="222" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="17" thickBot="1">
+    <row r="223" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -10929,7 +10929,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="17" thickBot="1">
+    <row r="224" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="17" thickBot="1">
+    <row r="225" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="17" thickBot="1">
+    <row r="226" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -10983,7 +10983,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="17" thickBot="1">
+    <row r="227" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -11001,7 +11001,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="17" thickBot="1">
+    <row r="228" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="17" thickBot="1">
+    <row r="229" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="17" thickBot="1">
+    <row r="230" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -11055,7 +11055,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="17" thickBot="1">
+    <row r="231" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="17" thickBot="1">
+    <row r="232" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -11091,7 +11091,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="17" thickBot="1">
+    <row r="233" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -11109,7 +11109,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="17" thickBot="1">
+    <row r="234" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="17" thickBot="1">
+    <row r="235" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="17" thickBot="1">
+    <row r="236" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -11163,7 +11163,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="17" thickBot="1">
+    <row r="237" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -11181,7 +11181,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="17" thickBot="1">
+    <row r="238" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -11199,7 +11199,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="17" thickBot="1">
+    <row r="239" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="17" thickBot="1">
+    <row r="240" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -11235,7 +11235,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="17" thickBot="1">
+    <row r="241" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="17" thickBot="1">
+    <row r="242" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -11271,7 +11271,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="17" thickBot="1">
+    <row r="243" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="17" thickBot="1">
+    <row r="244" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -11307,7 +11307,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="17" thickBot="1">
+    <row r="245" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="17" thickBot="1">
+    <row r="246" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -11343,7 +11343,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="17" thickBot="1">
+    <row r="247" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -11361,7 +11361,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="17" thickBot="1">
+    <row r="248" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -11379,7 +11379,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="17" thickBot="1">
+    <row r="249" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -11397,7 +11397,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="17" thickBot="1">
+    <row r="250" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -11415,7 +11415,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="17" thickBot="1">
+    <row r="251" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="17" thickBot="1">
+    <row r="252" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -11451,7 +11451,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="17" thickBot="1">
+    <row r="253" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -11469,7 +11469,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="17" thickBot="1">
+    <row r="254" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="17" thickBot="1">
+    <row r="255" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -11505,7 +11505,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="17" thickBot="1">
+    <row r="256" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -11523,7 +11523,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="17" thickBot="1">
+    <row r="257" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="17" thickBot="1">
+    <row r="258" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -11574,7 +11574,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="17" thickBot="1">
+    <row r="259" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="17" thickBot="1">
+    <row r="260" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -11610,7 +11610,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="17" thickBot="1">
+    <row r="261" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="17" thickBot="1">
+    <row r="262" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -11646,7 +11646,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="17" thickBot="1">
+    <row r="263" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="17" thickBot="1">
+    <row r="264" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="17" thickBot="1">
+    <row r="265" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -11700,7 +11700,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="17" thickBot="1">
+    <row r="266" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="17" thickBot="1">
+    <row r="267" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -11736,7 +11736,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="17" thickBot="1">
+    <row r="268" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="17" thickBot="1">
+    <row r="269" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -11772,7 +11772,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="17" thickBot="1">
+    <row r="270" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -11790,7 +11790,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="17" thickBot="1">
+    <row r="271" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -11808,7 +11808,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="17" thickBot="1">
+    <row r="272" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -11826,7 +11826,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="17" thickBot="1">
+    <row r="273" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -11844,7 +11844,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="17" thickBot="1">
+    <row r="274" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="17" thickBot="1">
+    <row r="275" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="17" thickBot="1">
+    <row r="276" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="17" thickBot="1">
+    <row r="277" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="17" thickBot="1">
+    <row r="278" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -11934,7 +11934,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="17" thickBot="1">
+    <row r="279" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="17" thickBot="1">
+    <row r="280" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -11970,7 +11970,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="17" thickBot="1">
+    <row r="281" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="17" thickBot="1">
+    <row r="282" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="17" thickBot="1">
+    <row r="283" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="17" thickBot="1">
+    <row r="284" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="17" thickBot="1">
+    <row r="285" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -12060,7 +12060,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="17" thickBot="1">
+    <row r="286" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -12078,7 +12078,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="17" thickBot="1">
+    <row r="287" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="17" thickBot="1">
+    <row r="288" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -12114,7 +12114,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="17" thickBot="1">
+    <row r="289" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="17" thickBot="1">
+    <row r="290" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -12150,7 +12150,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="17" thickBot="1">
+    <row r="291" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="17" thickBot="1">
+    <row r="292" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -12186,7 +12186,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="17" thickBot="1">
+    <row r="293" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="17" thickBot="1">
+    <row r="294" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="17" thickBot="1">
+    <row r="295" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -12240,7 +12240,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="17" thickBot="1">
+    <row r="296" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="17" thickBot="1">
+    <row r="297" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -12276,7 +12276,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="17" thickBot="1">
+    <row r="298" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="17" thickBot="1">
+    <row r="299" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="17" thickBot="1">
+    <row r="300" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -12330,7 +12330,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="17" thickBot="1">
+    <row r="301" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -12348,7 +12348,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="17" thickBot="1">
+    <row r="302" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="17" thickBot="1">
+    <row r="303" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -12384,7 +12384,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="17" thickBot="1">
+    <row r="304" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="17" thickBot="1">
+    <row r="305" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -12420,7 +12420,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="17" thickBot="1">
+    <row r="306" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="17" thickBot="1">
+    <row r="307" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="17" thickBot="1">
+    <row r="308" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -12474,7 +12474,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="17" thickBot="1">
+    <row r="309" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="17" thickBot="1">
+    <row r="310" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="17" thickBot="1">
+    <row r="311" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -12528,7 +12528,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="17" thickBot="1">
+    <row r="312" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -12546,7 +12546,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="17" thickBot="1">
+    <row r="313" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="17" thickBot="1">
+    <row r="314" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -12582,7 +12582,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="17" thickBot="1">
+    <row r="315" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -12600,7 +12600,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="17" thickBot="1">
+    <row r="316" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -12618,7 +12618,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="17" thickBot="1">
+    <row r="317" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="17" thickBot="1">
+    <row r="318" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="17" thickBot="1">
+    <row r="319" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -12672,7 +12672,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="17" thickBot="1">
+    <row r="320" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -12690,7 +12690,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="17" thickBot="1">
+    <row r="321" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="17" thickBot="1">
+    <row r="322" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="17" thickBot="1">
+    <row r="323" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -12759,7 +12759,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="17" thickBot="1">
+    <row r="324" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -12777,7 +12777,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="17" thickBot="1">
+    <row r="325" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="17" thickBot="1">
+    <row r="326" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="17" thickBot="1">
+    <row r="327" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="17" thickBot="1">
+    <row r="328" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -12849,7 +12849,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="17" thickBot="1">
+    <row r="329" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -12867,7 +12867,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="17" thickBot="1">
+    <row r="330" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="17" thickBot="1">
+    <row r="331" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -12903,7 +12903,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="17" thickBot="1">
+    <row r="332" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -12921,7 +12921,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="17" thickBot="1">
+    <row r="333" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="17" thickBot="1">
+    <row r="334" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -12957,7 +12957,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="17" thickBot="1">
+    <row r="335" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -12975,7 +12975,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="17" thickBot="1">
+    <row r="336" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -12993,7 +12993,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="17" thickBot="1">
+    <row r="337" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -13011,7 +13011,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="17" thickBot="1">
+    <row r="338" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -13029,7 +13029,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="17" thickBot="1">
+    <row r="339" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -13047,7 +13047,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="17" thickBot="1">
+    <row r="340" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -13065,7 +13065,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="17" thickBot="1">
+    <row r="341" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -13083,7 +13083,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="17" thickBot="1">
+    <row r="342" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -13101,7 +13101,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="17" thickBot="1">
+    <row r="343" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="17" thickBot="1">
+    <row r="344" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -13137,7 +13137,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="17" thickBot="1">
+    <row r="345" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="17" thickBot="1">
+    <row r="346" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="17" thickBot="1">
+    <row r="347" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -13191,7 +13191,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="17" thickBot="1">
+    <row r="348" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="17" thickBot="1">
+    <row r="349" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -13227,7 +13227,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="17" thickBot="1">
+    <row r="350" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="17" thickBot="1">
+    <row r="351" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -13263,7 +13263,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="17" thickBot="1">
+    <row r="352" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -13281,7 +13281,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="17" thickBot="1">
+    <row r="353" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="17" thickBot="1">
+    <row r="354" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -13317,7 +13317,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="17" thickBot="1">
+    <row r="355" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="17" thickBot="1">
+    <row r="356" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -13353,7 +13353,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="17" thickBot="1">
+    <row r="357" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -13371,7 +13371,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="17" thickBot="1">
+    <row r="358" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -13389,7 +13389,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="17" thickBot="1">
+    <row r="359" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -13407,7 +13407,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="17" thickBot="1">
+    <row r="360" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -13425,7 +13425,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="17" thickBot="1">
+    <row r="361" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -13443,7 +13443,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="17" thickBot="1">
+    <row r="362" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -13461,7 +13461,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="17" thickBot="1">
+    <row r="363" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -13479,7 +13479,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="17" thickBot="1">
+    <row r="364" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -13497,7 +13497,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="17" thickBot="1">
+    <row r="365" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -13515,7 +13515,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="17" thickBot="1">
+    <row r="366" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="17" thickBot="1">
+    <row r="367" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -13551,7 +13551,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="17" thickBot="1">
+    <row r="368" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -13569,7 +13569,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="17" thickBot="1">
+    <row r="369" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -13587,7 +13587,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="17" thickBot="1">
+    <row r="370" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -13605,7 +13605,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="17" thickBot="1">
+    <row r="371" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -13623,7 +13623,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="17" thickBot="1">
+    <row r="372" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -13641,7 +13641,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="17" thickBot="1">
+    <row r="373" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -13659,7 +13659,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="17" thickBot="1">
+    <row r="374" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -13677,7 +13677,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="17" thickBot="1">
+    <row r="375" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="17" thickBot="1">
+    <row r="376" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -13713,7 +13713,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="17" thickBot="1">
+    <row r="377" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -13731,7 +13731,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="17" thickBot="1">
+    <row r="378" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -13749,7 +13749,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="17" thickBot="1">
+    <row r="379" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -13767,7 +13767,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="17" thickBot="1">
+    <row r="380" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -13785,7 +13785,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="17" thickBot="1">
+    <row r="381" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -13803,7 +13803,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="17" thickBot="1">
+    <row r="382" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -13821,7 +13821,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="17" thickBot="1">
+    <row r="383" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -13839,7 +13839,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="17" thickBot="1">
+    <row r="384" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -13857,7 +13857,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="17" thickBot="1">
+    <row r="385" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -13875,7 +13875,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="17" thickBot="1">
+    <row r="386" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="17" thickBot="1">
+    <row r="387" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -13926,7 +13926,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="17" thickBot="1">
+    <row r="388" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -13944,7 +13944,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="17" thickBot="1">
+    <row r="389" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="17" thickBot="1">
+    <row r="390" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -13980,7 +13980,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="17" thickBot="1">
+    <row r="391" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -13998,7 +13998,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="17" thickBot="1">
+    <row r="392" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="17" thickBot="1">
+    <row r="393" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -14034,7 +14034,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="17" thickBot="1">
+    <row r="394" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -14052,7 +14052,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="17" thickBot="1">
+    <row r="395" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -14070,7 +14070,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="17" thickBot="1">
+    <row r="396" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -14088,7 +14088,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="17" thickBot="1">
+    <row r="397" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -14106,7 +14106,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="17" thickBot="1">
+    <row r="398" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -14124,7 +14124,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="17" thickBot="1">
+    <row r="399" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="17" thickBot="1">
+    <row r="400" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -14160,7 +14160,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="17" thickBot="1">
+    <row r="401" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -14178,7 +14178,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="17" thickBot="1">
+    <row r="402" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -14196,7 +14196,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="17" thickBot="1">
+    <row r="403" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -14214,7 +14214,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="17" thickBot="1">
+    <row r="404" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -14232,7 +14232,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="17" thickBot="1">
+    <row r="405" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -14250,7 +14250,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="17" thickBot="1">
+    <row r="406" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -14268,7 +14268,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="17" thickBot="1">
+    <row r="407" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -14286,7 +14286,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="17" thickBot="1">
+    <row r="408" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -14304,7 +14304,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="17" thickBot="1">
+    <row r="409" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="17" thickBot="1">
+    <row r="410" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="17" thickBot="1">
+    <row r="411" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -14358,7 +14358,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="17" thickBot="1">
+    <row r="412" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -14376,7 +14376,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="17" thickBot="1">
+    <row r="413" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -14394,7 +14394,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="17" thickBot="1">
+    <row r="414" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -14412,7 +14412,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="17" thickBot="1">
+    <row r="415" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -14430,7 +14430,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="17" thickBot="1">
+    <row r="416" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -14448,7 +14448,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="17" thickBot="1">
+    <row r="417" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="17" thickBot="1">
+    <row r="418" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="17" thickBot="1">
+    <row r="419" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -14502,7 +14502,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="17" thickBot="1">
+    <row r="420" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -14520,7 +14520,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="17" thickBot="1">
+    <row r="421" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="17" thickBot="1">
+    <row r="422" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -14556,7 +14556,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="17" thickBot="1">
+    <row r="423" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -14574,7 +14574,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="17" thickBot="1">
+    <row r="424" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="17" thickBot="1">
+    <row r="425" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -14610,7 +14610,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="17" thickBot="1">
+    <row r="426" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -14628,7 +14628,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="17" thickBot="1">
+    <row r="427" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -14646,7 +14646,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="17" thickBot="1">
+    <row r="428" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="17" thickBot="1">
+    <row r="429" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="17" thickBot="1">
+    <row r="430" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -14700,7 +14700,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="17" thickBot="1">
+    <row r="431" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="17" thickBot="1">
+    <row r="432" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -14736,7 +14736,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="17" thickBot="1">
+    <row r="433" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -14754,7 +14754,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="17" thickBot="1">
+    <row r="434" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -14772,7 +14772,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="17" thickBot="1">
+    <row r="435" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -14790,7 +14790,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="17" thickBot="1">
+    <row r="436" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -14808,7 +14808,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="17" thickBot="1">
+    <row r="437" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -14826,7 +14826,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="17" thickBot="1">
+    <row r="438" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -14844,7 +14844,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="17" thickBot="1">
+    <row r="439" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -14862,7 +14862,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="17" thickBot="1">
+    <row r="440" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -14880,7 +14880,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="17" thickBot="1">
+    <row r="441" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="17" thickBot="1">
+    <row r="442" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -14916,7 +14916,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="17" thickBot="1">
+    <row r="443" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -14934,7 +14934,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="17" thickBot="1">
+    <row r="444" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -14952,7 +14952,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="17" thickBot="1">
+    <row r="445" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -14970,7 +14970,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="17" thickBot="1">
+    <row r="446" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -14988,7 +14988,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="17" thickBot="1">
+    <row r="447" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -15006,7 +15006,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="17" thickBot="1">
+    <row r="448" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -15024,7 +15024,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="17" thickBot="1">
+    <row r="449" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -15042,7 +15042,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="17" thickBot="1">
+    <row r="450" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -15075,7 +15075,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="17" thickBot="1">
+    <row r="451" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -15093,7 +15093,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="17" thickBot="1">
+    <row r="452" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -15111,7 +15111,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="17" thickBot="1">
+    <row r="453" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -15129,7 +15129,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="17" thickBot="1">
+    <row r="454" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -15147,7 +15147,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="17" thickBot="1">
+    <row r="455" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -15165,7 +15165,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="17" thickBot="1">
+    <row r="456" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -15183,7 +15183,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="17" thickBot="1">
+    <row r="457" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -15201,7 +15201,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="17" thickBot="1">
+    <row r="458" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -15219,7 +15219,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="17" thickBot="1">
+    <row r="459" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -15237,7 +15237,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="17" thickBot="1">
+    <row r="460" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -15255,7 +15255,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="17" thickBot="1">
+    <row r="461" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -15273,7 +15273,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="17" thickBot="1">
+    <row r="462" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -15291,7 +15291,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="17" thickBot="1">
+    <row r="463" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -15309,7 +15309,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="17" thickBot="1">
+    <row r="464" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="17" thickBot="1">
+    <row r="465" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -15345,7 +15345,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="17" thickBot="1">
+    <row r="466" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -15363,7 +15363,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="17" thickBot="1">
+    <row r="467" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -15381,7 +15381,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="17" thickBot="1">
+    <row r="468" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -15399,7 +15399,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="17" thickBot="1">
+    <row r="469" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -15417,7 +15417,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="17" thickBot="1">
+    <row r="470" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -15435,7 +15435,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="17" thickBot="1">
+    <row r="471" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -15453,7 +15453,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="17" thickBot="1">
+    <row r="472" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -15471,7 +15471,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="17" thickBot="1">
+    <row r="473" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -15489,7 +15489,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="17" thickBot="1">
+    <row r="474" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -15507,7 +15507,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="17" thickBot="1">
+    <row r="475" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -15525,7 +15525,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="17" thickBot="1">
+    <row r="476" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -15543,7 +15543,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="17" thickBot="1">
+    <row r="477" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -15561,7 +15561,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="17" thickBot="1">
+    <row r="478" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -15579,7 +15579,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="17" thickBot="1">
+    <row r="479" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -15597,7 +15597,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="17" thickBot="1">
+    <row r="480" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -15615,7 +15615,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="17" thickBot="1">
+    <row r="481" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -15633,7 +15633,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="17" thickBot="1">
+    <row r="482" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -15651,7 +15651,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="17" thickBot="1">
+    <row r="483" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -15669,7 +15669,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="17" thickBot="1">
+    <row r="484" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -15687,7 +15687,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="17" thickBot="1">
+    <row r="485" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -15705,7 +15705,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="17" thickBot="1">
+    <row r="486" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -15723,7 +15723,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="17" thickBot="1">
+    <row r="487" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -15741,7 +15741,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="17" thickBot="1">
+    <row r="488" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -15759,7 +15759,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="17" thickBot="1">
+    <row r="489" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -15777,7 +15777,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="17" thickBot="1">
+    <row r="490" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -15795,7 +15795,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="17" thickBot="1">
+    <row r="491" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="17" thickBot="1">
+    <row r="492" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -15831,7 +15831,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="17" thickBot="1">
+    <row r="493" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -15849,7 +15849,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="17" thickBot="1">
+    <row r="494" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -15867,7 +15867,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="17" thickBot="1">
+    <row r="495" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -15885,7 +15885,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="17" thickBot="1">
+    <row r="496" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="17" thickBot="1">
+    <row r="497" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -15921,7 +15921,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="17" thickBot="1">
+    <row r="498" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -15939,7 +15939,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="17" thickBot="1">
+    <row r="499" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -15957,7 +15957,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="17" thickBot="1">
+    <row r="500" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -15975,7 +15975,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="17" thickBot="1">
+    <row r="501" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="17" thickBot="1">
+    <row r="502" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -16011,7 +16011,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="17" thickBot="1">
+    <row r="503" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -16029,7 +16029,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="17" thickBot="1">
+    <row r="504" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -16047,7 +16047,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="17" thickBot="1">
+    <row r="505" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -16065,7 +16065,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="17" thickBot="1">
+    <row r="506" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -16083,7 +16083,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="17" thickBot="1">
+    <row r="507" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -16101,7 +16101,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="17" thickBot="1">
+    <row r="508" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -16119,7 +16119,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="17" thickBot="1">
+    <row r="509" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -16137,7 +16137,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="17" thickBot="1">
+    <row r="510" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -16155,7 +16155,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="17" thickBot="1">
+    <row r="511" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -16173,7 +16173,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="17" thickBot="1">
+    <row r="512" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="17" thickBot="1">
+    <row r="513" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -16209,7 +16209,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="17" thickBot="1">
+    <row r="514" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -16242,7 +16242,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="17" thickBot="1">
+    <row r="515" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -16260,7 +16260,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="17" thickBot="1">
+    <row r="516" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -16278,7 +16278,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="17" thickBot="1">
+    <row r="517" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="17" thickBot="1">
+    <row r="518" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -16314,7 +16314,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="17" thickBot="1">
+    <row r="519" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -16332,7 +16332,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="17" thickBot="1">
+    <row r="520" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -16350,7 +16350,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="17" thickBot="1">
+    <row r="521" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -16368,7 +16368,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="17" thickBot="1">
+    <row r="522" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -16386,7 +16386,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="17" thickBot="1">
+    <row r="523" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -16404,7 +16404,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="17" thickBot="1">
+    <row r="524" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="17" thickBot="1">
+    <row r="525" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -16440,7 +16440,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="17" thickBot="1">
+    <row r="526" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="17" thickBot="1">
+    <row r="527" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -16476,7 +16476,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="17" thickBot="1">
+    <row r="528" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -16494,7 +16494,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="17" thickBot="1">
+    <row r="529" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -16512,7 +16512,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="17" thickBot="1">
+    <row r="530" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -16530,7 +16530,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="17" thickBot="1">
+    <row r="531" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -16548,7 +16548,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="17" thickBot="1">
+    <row r="532" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="17" thickBot="1">
+    <row r="533" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -16584,7 +16584,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="17" thickBot="1">
+    <row r="534" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -16602,7 +16602,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="17" thickBot="1">
+    <row r="535" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -16620,7 +16620,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="17" thickBot="1">
+    <row r="536" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -16638,7 +16638,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="17" thickBot="1">
+    <row r="537" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -16656,7 +16656,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="17" thickBot="1">
+    <row r="538" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -16674,7 +16674,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="17" thickBot="1">
+    <row r="539" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -16692,7 +16692,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="17" thickBot="1">
+    <row r="540" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="17" thickBot="1">
+    <row r="541" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -16728,7 +16728,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="17" thickBot="1">
+    <row r="542" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -16746,7 +16746,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="17" thickBot="1">
+    <row r="543" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -16764,7 +16764,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="17" thickBot="1">
+    <row r="544" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -16782,7 +16782,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="17" thickBot="1">
+    <row r="545" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -16800,7 +16800,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="17" thickBot="1">
+    <row r="546" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -16818,7 +16818,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="17" thickBot="1">
+    <row r="547" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -16836,7 +16836,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="17" thickBot="1">
+    <row r="548" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -16854,7 +16854,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="17" thickBot="1">
+    <row r="549" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -16872,7 +16872,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="17" thickBot="1">
+    <row r="550" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -16890,7 +16890,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="17" thickBot="1">
+    <row r="551" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -16908,7 +16908,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="17" thickBot="1">
+    <row r="552" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -16926,7 +16926,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="17" thickBot="1">
+    <row r="553" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -16944,7 +16944,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="17" thickBot="1">
+    <row r="554" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -16962,7 +16962,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="17" thickBot="1">
+    <row r="555" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -16980,7 +16980,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="17" thickBot="1">
+    <row r="556" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -16998,7 +16998,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="17" thickBot="1">
+    <row r="557" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -17016,7 +17016,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="17" thickBot="1">
+    <row r="558" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -17034,7 +17034,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="17" thickBot="1">
+    <row r="559" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -17052,7 +17052,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="17" thickBot="1">
+    <row r="560" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -17070,7 +17070,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="17" thickBot="1">
+    <row r="561" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -17088,7 +17088,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="17" thickBot="1">
+    <row r="562" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -17106,7 +17106,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="17" thickBot="1">
+    <row r="563" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -17124,7 +17124,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="17" thickBot="1">
+    <row r="564" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -17142,7 +17142,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="17" thickBot="1">
+    <row r="565" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -17160,7 +17160,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="17" thickBot="1">
+    <row r="566" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -17178,7 +17178,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="17" thickBot="1">
+    <row r="567" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -17196,7 +17196,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="17" thickBot="1">
+    <row r="568" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -17214,7 +17214,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="17" thickBot="1">
+    <row r="569" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -17232,7 +17232,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="17" thickBot="1">
+    <row r="570" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -17250,7 +17250,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="17" thickBot="1">
+    <row r="571" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -17268,7 +17268,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="17" thickBot="1">
+    <row r="572" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -17286,7 +17286,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="17" thickBot="1">
+    <row r="573" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -17304,7 +17304,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="17" thickBot="1">
+    <row r="574" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -17322,7 +17322,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="17" thickBot="1">
+    <row r="575" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -17340,7 +17340,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="17" thickBot="1">
+    <row r="576" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -17358,7 +17358,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="17" thickBot="1">
+    <row r="577" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -17376,7 +17376,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="17" thickBot="1">
+    <row r="578" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -17409,7 +17409,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="17" thickBot="1">
+    <row r="579" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -17427,7 +17427,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="17" thickBot="1">
+    <row r="580" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -17445,7 +17445,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="17" thickBot="1">
+    <row r="581" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -17463,7 +17463,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="17" thickBot="1">
+    <row r="582" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -17481,7 +17481,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="17" thickBot="1">
+    <row r="583" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -17499,7 +17499,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="17" thickBot="1">
+    <row r="584" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -17517,7 +17517,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="17" thickBot="1">
+    <row r="585" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -17535,7 +17535,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="17" thickBot="1">
+    <row r="586" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -17553,7 +17553,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="17" thickBot="1">
+    <row r="587" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -17571,7 +17571,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="17" thickBot="1">
+    <row r="588" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -17589,7 +17589,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="17" thickBot="1">
+    <row r="589" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -17607,7 +17607,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="17" thickBot="1">
+    <row r="590" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -17625,7 +17625,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="17" thickBot="1">
+    <row r="591" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="17" thickBot="1">
+    <row r="592" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -17661,7 +17661,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="17" thickBot="1">
+    <row r="593" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -17679,7 +17679,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="17" thickBot="1">
+    <row r="594" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -17697,7 +17697,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="17" thickBot="1">
+    <row r="595" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -17715,7 +17715,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="17" thickBot="1">
+    <row r="596" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -17733,7 +17733,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="17" thickBot="1">
+    <row r="597" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -17751,7 +17751,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="17" thickBot="1">
+    <row r="598" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -17769,7 +17769,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="17" thickBot="1">
+    <row r="599" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="17" thickBot="1">
+    <row r="600" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -17805,7 +17805,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="17" thickBot="1">
+    <row r="601" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -17823,7 +17823,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="17" thickBot="1">
+    <row r="602" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -17841,7 +17841,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="17" thickBot="1">
+    <row r="603" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -17859,7 +17859,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="17" thickBot="1">
+    <row r="604" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -17877,7 +17877,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="17" thickBot="1">
+    <row r="605" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -17895,7 +17895,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="17" thickBot="1">
+    <row r="606" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -17913,7 +17913,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="17" thickBot="1">
+    <row r="607" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="17" thickBot="1">
+    <row r="608" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -17949,7 +17949,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="17" thickBot="1">
+    <row r="609" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -17967,7 +17967,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="17" thickBot="1">
+    <row r="610" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -17985,7 +17985,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="17" thickBot="1">
+    <row r="611" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -18003,7 +18003,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="17" thickBot="1">
+    <row r="612" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -18021,7 +18021,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="17" thickBot="1">
+    <row r="613" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -18039,7 +18039,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="17" thickBot="1">
+    <row r="614" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -18057,7 +18057,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="17" thickBot="1">
+    <row r="615" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -18075,7 +18075,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="17" thickBot="1">
+    <row r="616" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -18093,7 +18093,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="17" thickBot="1">
+    <row r="617" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -18111,7 +18111,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="17" thickBot="1">
+    <row r="618" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -18129,7 +18129,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="17" thickBot="1">
+    <row r="619" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -18147,7 +18147,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="17" thickBot="1">
+    <row r="620" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -18165,7 +18165,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="17" thickBot="1">
+    <row r="621" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="17" thickBot="1">
+    <row r="622" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -18201,7 +18201,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="17" thickBot="1">
+    <row r="623" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -18219,7 +18219,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="17" thickBot="1">
+    <row r="624" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -18237,7 +18237,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="17" thickBot="1">
+    <row r="625" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -18255,7 +18255,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="17" thickBot="1">
+    <row r="626" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="17" thickBot="1">
+    <row r="627" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -18291,7 +18291,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="17" thickBot="1">
+    <row r="628" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -18309,7 +18309,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="17" thickBot="1">
+    <row r="629" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -18327,7 +18327,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="17" thickBot="1">
+    <row r="630" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -18345,7 +18345,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="17" thickBot="1">
+    <row r="631" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -18363,7 +18363,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="17" thickBot="1">
+    <row r="632" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -18381,7 +18381,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="17" thickBot="1">
+    <row r="633" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -18399,7 +18399,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="17" thickBot="1">
+    <row r="634" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="17" thickBot="1">
+    <row r="635" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -18435,7 +18435,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="17" thickBot="1">
+    <row r="636" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -18453,7 +18453,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="17" thickBot="1">
+    <row r="637" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -18471,7 +18471,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="17" thickBot="1">
+    <row r="638" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -18489,7 +18489,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="17" thickBot="1">
+    <row r="639" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -18507,7 +18507,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="17" thickBot="1">
+    <row r="640" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="17" thickBot="1">
+    <row r="641" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -18543,7 +18543,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="17" thickBot="1">
+    <row r="642" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -18576,7 +18576,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="17" thickBot="1">
+    <row r="643" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -18594,7 +18594,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="17" thickBot="1">
+    <row r="644" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -18612,7 +18612,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="17" thickBot="1">
+    <row r="645" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -18630,7 +18630,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="17" thickBot="1">
+    <row r="646" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="17" thickBot="1">
+    <row r="647" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -18666,7 +18666,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="17" thickBot="1">
+    <row r="648" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -18684,7 +18684,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="17" thickBot="1">
+    <row r="649" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -18702,7 +18702,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="17" thickBot="1">
+    <row r="650" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -18720,7 +18720,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="17" thickBot="1">
+    <row r="651" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -18738,7 +18738,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="17" thickBot="1">
+    <row r="652" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -18756,7 +18756,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="17" thickBot="1">
+    <row r="653" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -18774,7 +18774,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="17" thickBot="1">
+    <row r="654" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="17" thickBot="1">
+    <row r="655" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -18810,7 +18810,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="17" thickBot="1">
+    <row r="656" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -18828,7 +18828,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="17" thickBot="1">
+    <row r="657" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -18846,7 +18846,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="17" thickBot="1">
+    <row r="658" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -18864,7 +18864,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="17" thickBot="1">
+    <row r="659" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -18882,7 +18882,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="17" thickBot="1">
+    <row r="660" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -18900,7 +18900,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="17" thickBot="1">
+    <row r="661" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -18918,7 +18918,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="17" thickBot="1">
+    <row r="662" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -18936,7 +18936,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="17" thickBot="1">
+    <row r="663" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -18954,7 +18954,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="17" thickBot="1">
+    <row r="664" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -18972,7 +18972,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="17" thickBot="1">
+    <row r="665" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -18990,7 +18990,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="17" thickBot="1">
+    <row r="666" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -19008,7 +19008,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="17" thickBot="1">
+    <row r="667" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -19026,7 +19026,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="17" thickBot="1">
+    <row r="668" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -19044,7 +19044,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="17" thickBot="1">
+    <row r="669" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -19062,7 +19062,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="17" thickBot="1">
+    <row r="670" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -19080,7 +19080,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="17" thickBot="1">
+    <row r="671" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -19098,7 +19098,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="17" thickBot="1">
+    <row r="672" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -19116,7 +19116,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="17" thickBot="1">
+    <row r="673" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -19134,7 +19134,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="17" thickBot="1">
+    <row r="674" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -19152,7 +19152,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="17" thickBot="1">
+    <row r="675" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -19170,7 +19170,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="17" thickBot="1">
+    <row r="676" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -19188,7 +19188,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="17" thickBot="1">
+    <row r="677" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -19206,7 +19206,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="17" thickBot="1">
+    <row r="678" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -19224,7 +19224,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="17" thickBot="1">
+    <row r="679" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -19242,7 +19242,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="17" thickBot="1">
+    <row r="680" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -19260,7 +19260,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="17" thickBot="1">
+    <row r="681" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -19278,7 +19278,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="17" thickBot="1">
+    <row r="682" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -19296,7 +19296,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="17" thickBot="1">
+    <row r="683" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -19314,7 +19314,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="17" thickBot="1">
+    <row r="684" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -19332,7 +19332,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="17" thickBot="1">
+    <row r="685" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="17" thickBot="1">
+    <row r="686" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -19368,7 +19368,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="17" thickBot="1">
+    <row r="687" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -19386,7 +19386,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="17" thickBot="1">
+    <row r="688" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -19404,7 +19404,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="17" thickBot="1">
+    <row r="689" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -19422,7 +19422,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="17" thickBot="1">
+    <row r="690" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -19440,7 +19440,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="17" thickBot="1">
+    <row r="691" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -19458,7 +19458,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="17" thickBot="1">
+    <row r="692" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -19476,7 +19476,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="17" thickBot="1">
+    <row r="693" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -19494,7 +19494,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="17" thickBot="1">
+    <row r="694" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="17" thickBot="1">
+    <row r="695" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -19530,7 +19530,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="17" thickBot="1">
+    <row r="696" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -19548,7 +19548,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="17" thickBot="1">
+    <row r="697" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -19566,7 +19566,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="17" thickBot="1">
+    <row r="698" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -19584,7 +19584,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="17" thickBot="1">
+    <row r="699" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -19602,7 +19602,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="17" thickBot="1">
+    <row r="700" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -19620,7 +19620,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="17" thickBot="1">
+    <row r="701" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -19638,7 +19638,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="17" thickBot="1">
+    <row r="702" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -19656,7 +19656,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="17" thickBot="1">
+    <row r="703" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="17" thickBot="1">
+    <row r="704" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="17" thickBot="1">
+    <row r="705" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -19710,7 +19710,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="17" thickBot="1">
+    <row r="706" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -19743,7 +19743,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="17" thickBot="1">
+    <row r="707" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -19761,7 +19761,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="17" thickBot="1">
+    <row r="708" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -19779,7 +19779,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="17" thickBot="1">
+    <row r="709" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -19797,7 +19797,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="17" thickBot="1">
+    <row r="710" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -19815,7 +19815,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="17" thickBot="1">
+    <row r="711" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -19833,7 +19833,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="17" thickBot="1">
+    <row r="712" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -19851,7 +19851,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="17" thickBot="1">
+    <row r="713" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -19869,7 +19869,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="17" thickBot="1">
+    <row r="714" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -19887,7 +19887,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="17" thickBot="1">
+    <row r="715" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -19905,7 +19905,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="17" thickBot="1">
+    <row r="716" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -19923,7 +19923,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="17" thickBot="1">
+    <row r="717" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -19941,7 +19941,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="17" thickBot="1">
+    <row r="718" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -19959,7 +19959,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="17" thickBot="1">
+    <row r="719" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -19977,7 +19977,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="17" thickBot="1">
+    <row r="720" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -19995,7 +19995,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="17" thickBot="1">
+    <row r="721" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -20013,7 +20013,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="17" thickBot="1">
+    <row r="722" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -20031,7 +20031,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="17" thickBot="1">
+    <row r="723" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -20049,7 +20049,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="17" thickBot="1">
+    <row r="724" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -20067,7 +20067,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="17" thickBot="1">
+    <row r="725" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -20085,7 +20085,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="17" thickBot="1">
+    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -20103,7 +20103,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="17" thickBot="1">
+    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="17" thickBot="1">
+    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -20139,7 +20139,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="17" thickBot="1">
+    <row r="729" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -20157,7 +20157,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="17" thickBot="1">
+    <row r="730" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -20175,7 +20175,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="17" thickBot="1">
+    <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -20193,7 +20193,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="17" thickBot="1">
+    <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -20211,7 +20211,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="17" thickBot="1">
+    <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -20229,7 +20229,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="17" thickBot="1">
+    <row r="734" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -20247,7 +20247,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="17" thickBot="1">
+    <row r="735" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -20265,7 +20265,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="17" thickBot="1">
+    <row r="736" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -20283,7 +20283,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="17" thickBot="1">
+    <row r="737" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -20301,7 +20301,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="17" thickBot="1">
+    <row r="738" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -20319,7 +20319,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="17" thickBot="1">
+    <row r="739" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -20337,7 +20337,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="17" thickBot="1">
+    <row r="740" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -20355,7 +20355,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="17" thickBot="1">
+    <row r="741" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -20373,7 +20373,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="17" thickBot="1">
+    <row r="742" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -20391,7 +20391,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="17" thickBot="1">
+    <row r="743" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -20409,7 +20409,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="17" thickBot="1">
+    <row r="744" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -20427,7 +20427,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="17" thickBot="1">
+    <row r="745" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -20445,7 +20445,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="17" thickBot="1">
+    <row r="746" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -20463,7 +20463,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="17" thickBot="1">
+    <row r="747" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -20481,7 +20481,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="17" thickBot="1">
+    <row r="748" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -20499,7 +20499,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="17" thickBot="1">
+    <row r="749" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -20517,7 +20517,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="17" thickBot="1">
+    <row r="750" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -20535,7 +20535,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="17" thickBot="1">
+    <row r="751" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -20553,7 +20553,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="17" thickBot="1">
+    <row r="752" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -20571,7 +20571,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="17" thickBot="1">
+    <row r="753" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -20589,7 +20589,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="17" thickBot="1">
+    <row r="754" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -20607,7 +20607,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="17" thickBot="1">
+    <row r="755" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -20625,7 +20625,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="17" thickBot="1">
+    <row r="756" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -20643,7 +20643,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="17" thickBot="1">
+    <row r="757" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -20661,7 +20661,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="17" thickBot="1">
+    <row r="758" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -20679,7 +20679,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="17" thickBot="1">
+    <row r="759" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -20697,7 +20697,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="17" thickBot="1">
+    <row r="760" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -20715,7 +20715,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="17" thickBot="1">
+    <row r="761" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -20733,7 +20733,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="17" thickBot="1">
+    <row r="762" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -20751,7 +20751,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="17" thickBot="1">
+    <row r="763" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -20769,7 +20769,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="17" thickBot="1">
+    <row r="764" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -20787,7 +20787,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="17" thickBot="1">
+    <row r="765" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -20805,7 +20805,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="17" thickBot="1">
+    <row r="766" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -20823,7 +20823,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="17" thickBot="1">
+    <row r="767" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -20841,7 +20841,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="17" thickBot="1">
+    <row r="768" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -20859,7 +20859,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="17" thickBot="1">
+    <row r="769" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -20877,7 +20877,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="17" thickBot="1">
+    <row r="770" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -20910,7 +20910,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="17" thickBot="1">
+    <row r="771" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -20928,7 +20928,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="17" thickBot="1">
+    <row r="772" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -20946,7 +20946,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="17" thickBot="1">
+    <row r="773" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -20964,7 +20964,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="17" thickBot="1">
+    <row r="774" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -20982,7 +20982,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="17" thickBot="1">
+    <row r="775" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -21000,7 +21000,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="17" thickBot="1">
+    <row r="776" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -21018,7 +21018,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="17" thickBot="1">
+    <row r="777" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -21036,7 +21036,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="17" thickBot="1">
+    <row r="778" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -21054,7 +21054,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="17" thickBot="1">
+    <row r="779" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -21072,7 +21072,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="17" thickBot="1">
+    <row r="780" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -21090,7 +21090,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="17" thickBot="1">
+    <row r="781" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -21108,7 +21108,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="17" thickBot="1">
+    <row r="782" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -21126,7 +21126,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="17" thickBot="1">
+    <row r="783" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -21144,7 +21144,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="17" thickBot="1">
+    <row r="784" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -21162,7 +21162,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="17" thickBot="1">
+    <row r="785" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -21180,7 +21180,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="17" thickBot="1">
+    <row r="786" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -21198,7 +21198,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="17" thickBot="1">
+    <row r="787" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -21216,7 +21216,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="17" thickBot="1">
+    <row r="788" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -21234,7 +21234,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="17" thickBot="1">
+    <row r="789" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -21252,7 +21252,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="17" thickBot="1">
+    <row r="790" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -21270,7 +21270,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="17" thickBot="1">
+    <row r="791" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -21288,7 +21288,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="17" thickBot="1">
+    <row r="792" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -21306,7 +21306,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="17" thickBot="1">
+    <row r="793" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -21324,7 +21324,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="17" thickBot="1">
+    <row r="794" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -21342,7 +21342,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="17" thickBot="1">
+    <row r="795" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -21360,7 +21360,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="17" thickBot="1">
+    <row r="796" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -21378,7 +21378,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="17" thickBot="1">
+    <row r="797" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -21396,7 +21396,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="17" thickBot="1">
+    <row r="798" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -21414,7 +21414,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="17" thickBot="1">
+    <row r="799" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -21432,7 +21432,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="17" thickBot="1">
+    <row r="800" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -21450,7 +21450,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="17" thickBot="1">
+    <row r="801" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -21468,7 +21468,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="17" thickBot="1">
+    <row r="802" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -21486,7 +21486,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="17" thickBot="1">
+    <row r="803" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -21504,7 +21504,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="17" thickBot="1">
+    <row r="804" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -21522,7 +21522,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="17" thickBot="1">
+    <row r="805" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -21540,7 +21540,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="17" thickBot="1">
+    <row r="806" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -21558,7 +21558,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="17" thickBot="1">
+    <row r="807" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -21576,7 +21576,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="17" thickBot="1">
+    <row r="808" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -21594,7 +21594,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="17" thickBot="1">
+    <row r="809" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -21612,7 +21612,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="17" thickBot="1">
+    <row r="810" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -21630,7 +21630,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="17" thickBot="1">
+    <row r="811" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -21648,7 +21648,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="17" thickBot="1">
+    <row r="812" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -21666,7 +21666,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="17" thickBot="1">
+    <row r="813" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -21684,7 +21684,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="17" thickBot="1">
+    <row r="814" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -21702,7 +21702,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="17" thickBot="1">
+    <row r="815" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -21720,7 +21720,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="17" thickBot="1">
+    <row r="816" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -21738,7 +21738,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="17" thickBot="1">
+    <row r="817" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -21756,7 +21756,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="17" thickBot="1">
+    <row r="818" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -21774,7 +21774,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="17" thickBot="1">
+    <row r="819" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -21792,7 +21792,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="17" thickBot="1">
+    <row r="820" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -21810,7 +21810,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="17" thickBot="1">
+    <row r="821" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -21828,7 +21828,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="17" thickBot="1">
+    <row r="822" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -21846,7 +21846,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="17" thickBot="1">
+    <row r="823" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -21864,7 +21864,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="17" thickBot="1">
+    <row r="824" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -21882,7 +21882,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="17" thickBot="1">
+    <row r="825" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -21900,7 +21900,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="17" thickBot="1">
+    <row r="826" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -21918,7 +21918,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="17" thickBot="1">
+    <row r="827" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -21936,7 +21936,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="17" thickBot="1">
+    <row r="828" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -21954,7 +21954,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="17" thickBot="1">
+    <row r="829" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -21972,7 +21972,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="17" thickBot="1">
+    <row r="830" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -21990,7 +21990,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="17" thickBot="1">
+    <row r="831" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -22008,7 +22008,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="17" thickBot="1">
+    <row r="832" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -22026,7 +22026,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="17" thickBot="1">
+    <row r="833" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -22044,7 +22044,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="17" thickBot="1">
+    <row r="834" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -22077,7 +22077,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="17" thickBot="1">
+    <row r="835" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -22095,7 +22095,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="17" thickBot="1">
+    <row r="836" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -22113,7 +22113,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="17" thickBot="1">
+    <row r="837" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -22131,7 +22131,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="17" thickBot="1">
+    <row r="838" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -22149,7 +22149,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="17" thickBot="1">
+    <row r="839" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -22167,7 +22167,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="17" thickBot="1">
+    <row r="840" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -22185,7 +22185,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="17" thickBot="1">
+    <row r="841" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -22203,7 +22203,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="17" thickBot="1">
+    <row r="842" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -22221,7 +22221,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="17" thickBot="1">
+    <row r="843" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -22239,7 +22239,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="17" thickBot="1">
+    <row r="844" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -22257,7 +22257,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="17" thickBot="1">
+    <row r="845" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -22275,7 +22275,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="17" thickBot="1">
+    <row r="846" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -22293,7 +22293,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="17" thickBot="1">
+    <row r="847" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -22311,7 +22311,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="17" thickBot="1">
+    <row r="848" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -22329,7 +22329,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="17" thickBot="1">
+    <row r="849" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -22347,7 +22347,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="17" thickBot="1">
+    <row r="850" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -22365,7 +22365,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="17" thickBot="1">
+    <row r="851" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -22383,7 +22383,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="17" thickBot="1">
+    <row r="852" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -22401,7 +22401,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="17" thickBot="1">
+    <row r="853" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -22419,7 +22419,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="17" thickBot="1">
+    <row r="854" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -22437,7 +22437,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="17" thickBot="1">
+    <row r="855" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -22455,7 +22455,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="17" thickBot="1">
+    <row r="856" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -22473,7 +22473,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="17" thickBot="1">
+    <row r="857" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -22491,7 +22491,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="17" thickBot="1">
+    <row r="858" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -22509,7 +22509,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="17" thickBot="1">
+    <row r="859" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -22527,7 +22527,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="17" thickBot="1">
+    <row r="860" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -22545,7 +22545,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="17" thickBot="1">
+    <row r="861" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -22563,7 +22563,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="17" thickBot="1">
+    <row r="862" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -22581,7 +22581,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="17" thickBot="1">
+    <row r="863" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -22599,7 +22599,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="17" thickBot="1">
+    <row r="864" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -22617,7 +22617,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="17" thickBot="1">
+    <row r="865" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -22635,7 +22635,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="17" thickBot="1">
+    <row r="866" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -22653,7 +22653,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="17" thickBot="1">
+    <row r="867" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -22671,7 +22671,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="17" thickBot="1">
+    <row r="868" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -22689,7 +22689,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="17" thickBot="1">
+    <row r="869" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -22707,7 +22707,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="17" thickBot="1">
+    <row r="870" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -22725,7 +22725,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="17" thickBot="1">
+    <row r="871" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -22743,7 +22743,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="17" thickBot="1">
+    <row r="872" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -22761,7 +22761,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="17" thickBot="1">
+    <row r="873" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -22779,7 +22779,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="17" thickBot="1">
+    <row r="874" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -22797,7 +22797,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="17" thickBot="1">
+    <row r="875" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -22815,7 +22815,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="17" thickBot="1">
+    <row r="876" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -22833,7 +22833,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="17" thickBot="1">
+    <row r="877" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -22851,7 +22851,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="17" thickBot="1">
+    <row r="878" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -22884,7 +22884,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="17" thickBot="1">
+    <row r="879" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -22917,7 +22917,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="17" thickBot="1">
+    <row r="880" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -22950,7 +22950,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="17" thickBot="1">
+    <row r="881" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -22968,7 +22968,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="17" thickBot="1">
+    <row r="882" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -23001,7 +23001,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="17" thickBot="1">
+    <row r="883" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -23034,7 +23034,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="17" thickBot="1">
+    <row r="884" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
@@ -23052,7 +23052,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="17" thickBot="1">
+    <row r="885" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A885" s="15">
         <v>46088</v>
       </c>
@@ -23070,7 +23070,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" ht="16">
+    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A886" s="8">
         <v>46102</v>
       </c>
@@ -23088,7 +23088,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5" ht="16">
+    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A887" s="8">
         <v>46109</v>
       </c>
@@ -23106,7 +23106,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5" ht="16">
+    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A888" s="8">
         <v>46116</v>
       </c>
@@ -23124,7 +23124,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5" ht="16">
+    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A889" s="8">
         <v>46123</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>500040</v>
       </c>
     </row>
-    <row r="890" spans="1:5" ht="16">
+    <row r="890" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A890" s="8">
         <v>46130</v>
       </c>
@@ -23160,7 +23160,7 @@
         <v>508303</v>
       </c>
     </row>
-    <row r="891" spans="1:5" ht="16">
+    <row r="891" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A891" s="8">
         <v>46137</v>
       </c>
@@ -23178,7 +23178,7 @@
         <v>511616</v>
       </c>
     </row>
-    <row r="892" spans="1:5" ht="16">
+    <row r="892" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A892" s="8">
         <v>46144</v>
       </c>
@@ -23196,7 +23196,7 @@
         <v>518773</v>
       </c>
     </row>
-    <row r="893" spans="1:5" ht="16">
+    <row r="893" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A893" s="8">
         <v>46151</v>
       </c>
@@ -23229,7 +23229,7 @@
         <v>513755</v>
       </c>
     </row>
-    <row r="894" spans="1:5" ht="16">
+    <row r="894" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A894" s="8">
         <v>46158</v>
       </c>
@@ -23247,7 +23247,7 @@
         <v>511216</v>
       </c>
     </row>
-    <row r="895" spans="1:5" ht="16">
+    <row r="895" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A895" s="8">
         <v>46165</v>
       </c>
@@ -23265,7 +23265,7 @@
         <v>523574</v>
       </c>
     </row>
-    <row r="896" spans="1:5" ht="16">
+    <row r="896" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A896" s="8">
         <v>46172</v>
       </c>
@@ -23298,7 +23298,7 @@
         <v>492795</v>
       </c>
     </row>
-    <row r="897" spans="1:5" ht="16">
+    <row r="897" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A897" s="8">
         <v>46179</v>
       </c>
@@ -23316,7 +23316,7 @@
         <v>521804</v>
       </c>
     </row>
-    <row r="898" spans="1:5" ht="16">
+    <row r="898" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A898" s="8">
         <v>46186</v>
       </c>
@@ -23334,7 +23334,7 @@
         <v>520406</v>
       </c>
     </row>
-    <row r="899" spans="1:5" ht="16">
+    <row r="899" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A899" s="8">
         <v>46193</v>
       </c>
@@ -23367,7 +23367,7 @@
         <v>521998</v>
       </c>
     </row>
-    <row r="900" spans="1:5" ht="16">
+    <row r="900" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A900" s="8">
         <v>46200</v>
       </c>
@@ -23385,7 +23385,7 @@
         <v>525474</v>
       </c>
     </row>
-    <row r="901" spans="1:5" ht="16">
+    <row r="901" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A901" s="8">
         <v>46207</v>
       </c>
@@ -23418,7 +23418,7 @@
         <v>482121</v>
       </c>
     </row>
-    <row r="902" spans="1:5" ht="16">
+    <row r="902" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A902" s="8">
         <v>46214</v>
       </c>
@@ -23436,7 +23436,7 @@
         <v>503525</v>
       </c>
     </row>
-    <row r="903" spans="1:5" ht="16">
+    <row r="903" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A903" s="8">
         <v>46221</v>
       </c>
@@ -23454,7 +23454,7 @@
         <v>523900</v>
       </c>
     </row>
-    <row r="904" spans="1:5" ht="16">
+    <row r="904" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A904" s="8">
         <v>46228</v>
       </c>
@@ -23487,7 +23487,7 @@
         <v>527162</v>
       </c>
     </row>
-    <row r="905" spans="1:5" ht="16">
+    <row r="905" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A905" s="8">
         <v>46235</v>
       </c>
@@ -23505,7 +23505,7 @@
         <v>526410</v>
       </c>
     </row>
-    <row r="906" spans="1:5" ht="16">
+    <row r="906" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A906" s="8">
         <v>46242</v>
       </c>
@@ -23516,7 +23516,7 @@
         <v>0.50069444444444444</v>
       </c>
       <c r="D906" s="7" t="str">
-        <f t="shared" ref="D906" si="21">IF(
+        <f t="shared" ref="D906:D907" si="21">IF(
  AND(
   A906 &gt;= IF(
          YEAR(A906)&gt;=2007,
@@ -23538,6 +23538,24 @@
         <v>526624</v>
       </c>
     </row>
+    <row r="907" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A907" s="8">
+        <v>46249</v>
+      </c>
+      <c r="B907" s="8">
+        <v>46253</v>
+      </c>
+      <c r="C907" s="21">
+        <v>0.50972222222222219</v>
+      </c>
+      <c r="D907" s="7" t="str">
+        <f t="shared" si="21"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E907" s="20">
+        <v>525099</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">
     <sortCondition ref="B2:B876"/>
@@ -23551,7 +23569,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23562,12 +23580,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23575,7 +23593,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23583,7 +23601,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155FC8E2-A783-4C8A-80CB-4E2470ADE9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4352567C-D31F-4D4C-A967-6D285C862FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="17980" yWindow="780" windowWidth="18020" windowHeight="20760" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -86,12 +86,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -189,7 +189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -206,68 +206,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -285,7 +285,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6534,9 +6534,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6574,7 +6574,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6680,7 +6680,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6822,7 +6822,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6830,18 +6830,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E907"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E908"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="6"/>
+    <col min="3" max="3" width="11.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="16">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="16">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="16">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="16">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="16">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="16">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="16">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="16">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="16">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="16">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="16">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="16">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -7122,7 +7122,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="16">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="16">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="16">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="16">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="16">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="16">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="16">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="16">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="16">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="16">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="16">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="16">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="16">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="16">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="16">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="16">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="16">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="16">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="16">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="16">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="16">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="16">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="16">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="16">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="16">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="16">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="16">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="16">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="16">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -7644,7 +7644,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="16">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="16">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="16">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" ht="16">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" ht="16">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" ht="16">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" ht="16">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" ht="16">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" ht="16">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" ht="16">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" ht="16">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" ht="16">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -7860,7 +7860,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" ht="16">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" ht="16">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -7896,7 +7896,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" ht="16">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" ht="16">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" ht="16">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" ht="16">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" ht="16">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" ht="16">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" ht="16">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" ht="16">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -8040,7 +8040,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" ht="16">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" ht="16">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" ht="16">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" ht="16">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -8127,7 +8127,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" ht="16">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" ht="16">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" ht="16">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -8181,7 +8181,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" ht="16">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" ht="16">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" ht="16">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" ht="16">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" ht="16">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -8271,7 +8271,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" ht="16">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" ht="16">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" ht="16">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" ht="16">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" ht="16">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" ht="16">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" ht="16">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -8397,7 +8397,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" ht="16">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" ht="16">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" ht="16">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" ht="16">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" ht="16">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" ht="16">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" ht="16">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" ht="16">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -8541,7 +8541,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" ht="16">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -8559,7 +8559,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" ht="16">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" ht="16">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" ht="16">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" ht="16">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" ht="16">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" ht="16">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" ht="16">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" ht="17" thickBot="1">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" ht="17" thickBot="1">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" ht="17" thickBot="1">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" ht="17" thickBot="1">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" ht="17" thickBot="1">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" ht="17" thickBot="1">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" ht="17" thickBot="1">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" ht="17" thickBot="1">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -8829,7 +8829,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" ht="17" thickBot="1">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" ht="17" thickBot="1">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" ht="17" thickBot="1">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" ht="17" thickBot="1">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:5" ht="17" thickBot="1">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -8919,7 +8919,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:5" ht="17" thickBot="1">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -8937,7 +8937,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:5" ht="17" thickBot="1">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:5" ht="17" thickBot="1">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:5" ht="17" thickBot="1">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:5" ht="17" thickBot="1">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:5" ht="17" thickBot="1">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:5" ht="17" thickBot="1">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:5" ht="17" thickBot="1">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:5" ht="17" thickBot="1">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:5" ht="17" thickBot="1">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:5" ht="17" thickBot="1">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -9117,7 +9117,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:5" ht="17" thickBot="1">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:5" ht="17" thickBot="1">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:5" ht="17" thickBot="1">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:5" ht="17" thickBot="1">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -9189,7 +9189,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:5" ht="17" thickBot="1">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -9207,7 +9207,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:5" ht="17" thickBot="1">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:5" ht="17" thickBot="1">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:5" ht="17" thickBot="1">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:5" ht="17" thickBot="1">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:5" ht="17" thickBot="1">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:5" ht="17" thickBot="1">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:5" ht="17" thickBot="1">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:5" ht="17" thickBot="1">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:5" ht="17" thickBot="1">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:5" ht="17" thickBot="1">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:5" ht="17" thickBot="1">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:5" ht="17" thickBot="1">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:5" ht="17" thickBot="1">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -9456,7 +9456,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:5" ht="17" thickBot="1">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:5" ht="17" thickBot="1">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:5" ht="17" thickBot="1">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:5" ht="17" thickBot="1">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:5" ht="17" thickBot="1">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:5" ht="17" thickBot="1">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:5" ht="17" thickBot="1">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -9582,7 +9582,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:5" ht="17" thickBot="1">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:5" ht="17" thickBot="1">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:5" ht="17" thickBot="1">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:5" ht="17" thickBot="1">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:5" ht="17" thickBot="1">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:5" ht="17" thickBot="1">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:5" ht="17" thickBot="1">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -9708,7 +9708,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:5" ht="17" thickBot="1">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -9726,7 +9726,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:5" ht="17" thickBot="1">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:5" ht="17" thickBot="1">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -9762,7 +9762,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:5" ht="17" thickBot="1">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:5" ht="17" thickBot="1">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:5" ht="17" thickBot="1">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:5" ht="17" thickBot="1">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:5" ht="17" thickBot="1">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:5" ht="17" thickBot="1">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:5" ht="17" thickBot="1">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:5" ht="17" thickBot="1">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:5" ht="17" thickBot="1">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:5" ht="17" thickBot="1">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:5" ht="17" thickBot="1">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -9960,7 +9960,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:5" ht="17" thickBot="1">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -9978,7 +9978,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:5" ht="17" thickBot="1">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -9996,7 +9996,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:5" ht="17" thickBot="1">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:5" ht="17" thickBot="1">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -10032,7 +10032,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:5" ht="17" thickBot="1">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:5" ht="17" thickBot="1">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:5" ht="17" thickBot="1">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:5" ht="17" thickBot="1">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:5" ht="17" thickBot="1">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:5" ht="17" thickBot="1">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -10140,7 +10140,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:5" ht="17" thickBot="1">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:5" ht="17" thickBot="1">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -10176,7 +10176,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:5" ht="17" thickBot="1">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:5" ht="17" thickBot="1">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -10212,7 +10212,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:5" ht="17" thickBot="1">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:5" ht="17" thickBot="1">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -10248,7 +10248,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:5" ht="17" thickBot="1">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:5" ht="17" thickBot="1">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:5" ht="17" thickBot="1">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:5" ht="17" thickBot="1">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -10320,7 +10320,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:5" ht="17" thickBot="1">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -10338,7 +10338,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:5" ht="17" thickBot="1">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -10356,7 +10356,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:5" ht="17" thickBot="1">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:5" ht="17" thickBot="1">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:5" ht="17" thickBot="1">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:5" ht="17" thickBot="1">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -10443,7 +10443,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:5" ht="17" thickBot="1">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -10461,7 +10461,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:5" ht="17" thickBot="1">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:5" ht="17" thickBot="1">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -10497,7 +10497,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:5" ht="17" thickBot="1">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -10515,7 +10515,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:5" ht="17" thickBot="1">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:5" ht="17" thickBot="1">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:5" ht="17" thickBot="1">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -10569,7 +10569,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:5" ht="17" thickBot="1">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -10587,7 +10587,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:5" ht="17" thickBot="1">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:5" ht="17" thickBot="1">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:5" ht="17" thickBot="1">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -10641,7 +10641,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:5" ht="17" thickBot="1">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -10659,7 +10659,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:5" ht="17" thickBot="1">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -10677,7 +10677,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:5" ht="17" thickBot="1">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:5" ht="17" thickBot="1">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:5" ht="17" thickBot="1">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -10731,7 +10731,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:5" ht="17" thickBot="1">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:5" ht="17" thickBot="1">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -10767,7 +10767,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:5" ht="17" thickBot="1">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:5" ht="17" thickBot="1">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:5" ht="17" thickBot="1">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:5" ht="17" thickBot="1">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -10839,7 +10839,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:5" ht="17" thickBot="1">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:5" ht="17" thickBot="1">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:5" ht="17" thickBot="1">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:5" ht="17" thickBot="1">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:5" ht="17" thickBot="1">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -10929,7 +10929,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:5" ht="17" thickBot="1">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:5" ht="17" thickBot="1">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:5" ht="17" thickBot="1">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -10983,7 +10983,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:5" ht="17" thickBot="1">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -11001,7 +11001,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:5" ht="17" thickBot="1">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:5" ht="17" thickBot="1">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:5" ht="17" thickBot="1">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -11055,7 +11055,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:5" ht="17" thickBot="1">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:5" ht="17" thickBot="1">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -11091,7 +11091,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:5" ht="17" thickBot="1">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -11109,7 +11109,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:5" ht="17" thickBot="1">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:5" ht="17" thickBot="1">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:5" ht="17" thickBot="1">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -11163,7 +11163,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:5" ht="17" thickBot="1">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -11181,7 +11181,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:5" ht="17" thickBot="1">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -11199,7 +11199,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:5" ht="17" thickBot="1">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:5" ht="17" thickBot="1">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -11235,7 +11235,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:5" ht="17" thickBot="1">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:5" ht="17" thickBot="1">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -11271,7 +11271,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:5" ht="17" thickBot="1">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:5" ht="17" thickBot="1">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -11307,7 +11307,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:5" ht="17" thickBot="1">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:5" ht="17" thickBot="1">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -11343,7 +11343,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:5" ht="17" thickBot="1">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -11361,7 +11361,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:5" ht="17" thickBot="1">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -11379,7 +11379,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:5" ht="17" thickBot="1">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -11397,7 +11397,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:5" ht="17" thickBot="1">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -11415,7 +11415,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:5" ht="17" thickBot="1">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:5" ht="17" thickBot="1">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -11451,7 +11451,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:5" ht="17" thickBot="1">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -11469,7 +11469,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:5" ht="17" thickBot="1">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:5" ht="17" thickBot="1">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -11505,7 +11505,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:5" ht="17" thickBot="1">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -11523,7 +11523,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:5" ht="17" thickBot="1">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:5" ht="17" thickBot="1">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -11574,7 +11574,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:5" ht="17" thickBot="1">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:5" ht="17" thickBot="1">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -11610,7 +11610,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:5" ht="17" thickBot="1">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:5" ht="17" thickBot="1">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -11646,7 +11646,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:5" ht="17" thickBot="1">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:5" ht="17" thickBot="1">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:5" ht="17" thickBot="1">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -11700,7 +11700,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:5" ht="17" thickBot="1">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:5" ht="17" thickBot="1">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -11736,7 +11736,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:5" ht="17" thickBot="1">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:5" ht="17" thickBot="1">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -11772,7 +11772,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:5" ht="17" thickBot="1">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -11790,7 +11790,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:5" ht="17" thickBot="1">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -11808,7 +11808,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:5" ht="17" thickBot="1">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -11826,7 +11826,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:5" ht="17" thickBot="1">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -11844,7 +11844,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:5" ht="17" thickBot="1">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:5" ht="17" thickBot="1">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:5" ht="17" thickBot="1">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:5" ht="17" thickBot="1">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:5" ht="17" thickBot="1">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -11934,7 +11934,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:5" ht="17" thickBot="1">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:5" ht="17" thickBot="1">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -11970,7 +11970,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:5" ht="17" thickBot="1">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:5" ht="17" thickBot="1">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:5" ht="17" thickBot="1">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:5" ht="17" thickBot="1">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:5" ht="17" thickBot="1">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -12060,7 +12060,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:5" ht="17" thickBot="1">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -12078,7 +12078,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:5" ht="17" thickBot="1">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:5" ht="17" thickBot="1">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -12114,7 +12114,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:5" ht="17" thickBot="1">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:5" ht="17" thickBot="1">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -12150,7 +12150,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:5" ht="17" thickBot="1">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:5" ht="17" thickBot="1">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -12186,7 +12186,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:5" ht="17" thickBot="1">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:5" ht="17" thickBot="1">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:5" ht="17" thickBot="1">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -12240,7 +12240,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:5" ht="17" thickBot="1">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:5" ht="17" thickBot="1">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -12276,7 +12276,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:5" ht="17" thickBot="1">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:5" ht="17" thickBot="1">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:5" ht="17" thickBot="1">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -12330,7 +12330,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:5" ht="17" thickBot="1">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -12348,7 +12348,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:5" ht="17" thickBot="1">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:5" ht="17" thickBot="1">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -12384,7 +12384,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:5" ht="17" thickBot="1">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:5" ht="17" thickBot="1">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -12420,7 +12420,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:5" ht="17" thickBot="1">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:5" ht="17" thickBot="1">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:5" ht="17" thickBot="1">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -12474,7 +12474,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:5" ht="17" thickBot="1">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:5" ht="17" thickBot="1">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:5" ht="17" thickBot="1">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -12528,7 +12528,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:5" ht="17" thickBot="1">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -12546,7 +12546,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:5" ht="17" thickBot="1">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:5" ht="17" thickBot="1">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -12582,7 +12582,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:5" ht="17" thickBot="1">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -12600,7 +12600,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:5" ht="17" thickBot="1">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -12618,7 +12618,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:5" ht="17" thickBot="1">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:5" ht="17" thickBot="1">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:5" ht="17" thickBot="1">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -12672,7 +12672,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:5" ht="17" thickBot="1">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -12690,7 +12690,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:5" ht="17" thickBot="1">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:5" ht="17" thickBot="1">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:5" ht="17" thickBot="1">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -12759,7 +12759,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:5" ht="17" thickBot="1">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -12777,7 +12777,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:5" ht="17" thickBot="1">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:5" ht="17" thickBot="1">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:5" ht="17" thickBot="1">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:5" ht="17" thickBot="1">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -12849,7 +12849,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:5" ht="17" thickBot="1">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -12867,7 +12867,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:5" ht="17" thickBot="1">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:5" ht="17" thickBot="1">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -12903,7 +12903,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:5" ht="17" thickBot="1">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -12921,7 +12921,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:5" ht="17" thickBot="1">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:5" ht="17" thickBot="1">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -12957,7 +12957,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:5" ht="17" thickBot="1">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -12975,7 +12975,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:5" ht="17" thickBot="1">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -12993,7 +12993,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:5" ht="17" thickBot="1">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -13011,7 +13011,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:5" ht="17" thickBot="1">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -13029,7 +13029,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:5" ht="17" thickBot="1">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -13047,7 +13047,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:5" ht="17" thickBot="1">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -13065,7 +13065,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:5" ht="17" thickBot="1">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -13083,7 +13083,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:5" ht="17" thickBot="1">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -13101,7 +13101,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:5" ht="17" thickBot="1">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:5" ht="17" thickBot="1">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -13137,7 +13137,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:5" ht="17" thickBot="1">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:5" ht="17" thickBot="1">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:5" ht="17" thickBot="1">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -13191,7 +13191,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:5" ht="17" thickBot="1">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:5" ht="17" thickBot="1">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -13227,7 +13227,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:5" ht="17" thickBot="1">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:5" ht="17" thickBot="1">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -13263,7 +13263,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:5" ht="17" thickBot="1">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -13281,7 +13281,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:5" ht="17" thickBot="1">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:5" ht="17" thickBot="1">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -13317,7 +13317,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:5" ht="17" thickBot="1">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:5" ht="17" thickBot="1">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -13353,7 +13353,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:5" ht="17" thickBot="1">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -13371,7 +13371,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:5" ht="17" thickBot="1">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -13389,7 +13389,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:5" ht="17" thickBot="1">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -13407,7 +13407,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:5" ht="17" thickBot="1">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -13425,7 +13425,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:5" ht="17" thickBot="1">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -13443,7 +13443,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:5" ht="17" thickBot="1">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -13461,7 +13461,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:5" ht="17" thickBot="1">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -13479,7 +13479,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:5" ht="17" thickBot="1">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -13497,7 +13497,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:5" ht="17" thickBot="1">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -13515,7 +13515,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:5" ht="17" thickBot="1">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:5" ht="17" thickBot="1">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -13551,7 +13551,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:5" ht="17" thickBot="1">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -13569,7 +13569,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:5" ht="17" thickBot="1">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -13587,7 +13587,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:5" ht="17" thickBot="1">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -13605,7 +13605,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:5" ht="17" thickBot="1">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -13623,7 +13623,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:5" ht="17" thickBot="1">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -13641,7 +13641,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:5" ht="17" thickBot="1">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -13659,7 +13659,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:5" ht="17" thickBot="1">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -13677,7 +13677,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:5" ht="17" thickBot="1">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:5" ht="17" thickBot="1">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -13713,7 +13713,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:5" ht="17" thickBot="1">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -13731,7 +13731,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:5" ht="17" thickBot="1">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -13749,7 +13749,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:5" ht="17" thickBot="1">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -13767,7 +13767,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:5" ht="17" thickBot="1">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -13785,7 +13785,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:5" ht="17" thickBot="1">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -13803,7 +13803,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:5" ht="17" thickBot="1">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -13821,7 +13821,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:5" ht="17" thickBot="1">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -13839,7 +13839,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:5" ht="17" thickBot="1">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -13857,7 +13857,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:5" ht="17" thickBot="1">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -13875,7 +13875,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:5" ht="17" thickBot="1">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:5" ht="17" thickBot="1">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -13926,7 +13926,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:5" ht="17" thickBot="1">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -13944,7 +13944,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:5" ht="17" thickBot="1">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:5" ht="17" thickBot="1">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -13980,7 +13980,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:5" ht="17" thickBot="1">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -13998,7 +13998,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:5" ht="17" thickBot="1">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:5" ht="17" thickBot="1">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -14034,7 +14034,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:5" ht="17" thickBot="1">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -14052,7 +14052,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:5" ht="17" thickBot="1">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -14070,7 +14070,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:5" ht="17" thickBot="1">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -14088,7 +14088,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:5" ht="17" thickBot="1">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -14106,7 +14106,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:5" ht="17" thickBot="1">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -14124,7 +14124,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:5" ht="17" thickBot="1">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:5" ht="17" thickBot="1">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -14160,7 +14160,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:5" ht="17" thickBot="1">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -14178,7 +14178,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:5" ht="17" thickBot="1">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -14196,7 +14196,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:5" ht="17" thickBot="1">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -14214,7 +14214,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:5" ht="17" thickBot="1">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -14232,7 +14232,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:5" ht="17" thickBot="1">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -14250,7 +14250,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:5" ht="17" thickBot="1">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -14268,7 +14268,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:5" ht="17" thickBot="1">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -14286,7 +14286,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:5" ht="17" thickBot="1">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -14304,7 +14304,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:5" ht="17" thickBot="1">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:5" ht="17" thickBot="1">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:5" ht="17" thickBot="1">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -14358,7 +14358,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:5" ht="17" thickBot="1">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -14376,7 +14376,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:5" ht="17" thickBot="1">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -14394,7 +14394,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:5" ht="17" thickBot="1">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -14412,7 +14412,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:5" ht="17" thickBot="1">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -14430,7 +14430,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:5" ht="17" thickBot="1">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -14448,7 +14448,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:5" ht="17" thickBot="1">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:5" ht="17" thickBot="1">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:5" ht="17" thickBot="1">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -14502,7 +14502,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:5" ht="17" thickBot="1">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -14520,7 +14520,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:5" ht="17" thickBot="1">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:5" ht="17" thickBot="1">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -14556,7 +14556,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:5" ht="17" thickBot="1">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -14574,7 +14574,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:5" ht="17" thickBot="1">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:5" ht="17" thickBot="1">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -14610,7 +14610,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:5" ht="17" thickBot="1">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -14628,7 +14628,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:5" ht="17" thickBot="1">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -14646,7 +14646,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:5" ht="17" thickBot="1">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:5" ht="17" thickBot="1">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:5" ht="17" thickBot="1">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -14700,7 +14700,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:5" ht="17" thickBot="1">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:5" ht="17" thickBot="1">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -14736,7 +14736,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:5" ht="17" thickBot="1">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -14754,7 +14754,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:5" ht="17" thickBot="1">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -14772,7 +14772,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:5" ht="17" thickBot="1">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -14790,7 +14790,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:5" ht="17" thickBot="1">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -14808,7 +14808,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:5" ht="17" thickBot="1">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -14826,7 +14826,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:5" ht="17" thickBot="1">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -14844,7 +14844,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:5" ht="17" thickBot="1">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -14862,7 +14862,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:5" ht="17" thickBot="1">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -14880,7 +14880,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:5" ht="17" thickBot="1">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:5" ht="17" thickBot="1">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -14916,7 +14916,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:5" ht="17" thickBot="1">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -14934,7 +14934,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:5" ht="17" thickBot="1">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -14952,7 +14952,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:5" ht="17" thickBot="1">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -14970,7 +14970,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:5" ht="17" thickBot="1">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -14988,7 +14988,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:5" ht="17" thickBot="1">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -15006,7 +15006,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:5" ht="17" thickBot="1">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -15024,7 +15024,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:5" ht="17" thickBot="1">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -15042,7 +15042,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:5" ht="17" thickBot="1">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -15075,7 +15075,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:5" ht="17" thickBot="1">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -15093,7 +15093,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:5" ht="17" thickBot="1">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -15111,7 +15111,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:5" ht="17" thickBot="1">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -15129,7 +15129,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:5" ht="17" thickBot="1">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -15147,7 +15147,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:5" ht="17" thickBot="1">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -15165,7 +15165,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:5" ht="17" thickBot="1">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -15183,7 +15183,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:5" ht="17" thickBot="1">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -15201,7 +15201,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:5" ht="17" thickBot="1">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -15219,7 +15219,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:5" ht="17" thickBot="1">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -15237,7 +15237,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:5" ht="17" thickBot="1">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -15255,7 +15255,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:5" ht="17" thickBot="1">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -15273,7 +15273,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:5" ht="17" thickBot="1">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -15291,7 +15291,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:5" ht="17" thickBot="1">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -15309,7 +15309,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:5" ht="17" thickBot="1">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:5" ht="17" thickBot="1">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -15345,7 +15345,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:5" ht="17" thickBot="1">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -15363,7 +15363,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:5" ht="17" thickBot="1">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -15381,7 +15381,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:5" ht="17" thickBot="1">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -15399,7 +15399,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:5" ht="17" thickBot="1">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -15417,7 +15417,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:5" ht="17" thickBot="1">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -15435,7 +15435,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:5" ht="17" thickBot="1">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -15453,7 +15453,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:5" ht="17" thickBot="1">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -15471,7 +15471,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:5" ht="17" thickBot="1">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -15489,7 +15489,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:5" ht="17" thickBot="1">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -15507,7 +15507,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:5" ht="17" thickBot="1">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -15525,7 +15525,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:5" ht="17" thickBot="1">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -15543,7 +15543,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:5" ht="17" thickBot="1">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -15561,7 +15561,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:5" ht="17" thickBot="1">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -15579,7 +15579,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:5" ht="17" thickBot="1">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -15597,7 +15597,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:5" ht="17" thickBot="1">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -15615,7 +15615,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:5" ht="17" thickBot="1">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -15633,7 +15633,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:5" ht="17" thickBot="1">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -15651,7 +15651,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:5" ht="17" thickBot="1">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -15669,7 +15669,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:5" ht="17" thickBot="1">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -15687,7 +15687,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:5" ht="17" thickBot="1">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -15705,7 +15705,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:5" ht="17" thickBot="1">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -15723,7 +15723,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:5" ht="17" thickBot="1">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -15741,7 +15741,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:5" ht="17" thickBot="1">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -15759,7 +15759,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:5" ht="17" thickBot="1">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -15777,7 +15777,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:5" ht="17" thickBot="1">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -15795,7 +15795,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:5" ht="17" thickBot="1">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:5" ht="17" thickBot="1">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -15831,7 +15831,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:5" ht="17" thickBot="1">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -15849,7 +15849,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:5" ht="17" thickBot="1">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -15867,7 +15867,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:5" ht="17" thickBot="1">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -15885,7 +15885,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:5" ht="17" thickBot="1">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:5" ht="17" thickBot="1">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -15921,7 +15921,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:5" ht="17" thickBot="1">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -15939,7 +15939,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:5" ht="17" thickBot="1">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -15957,7 +15957,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:5" ht="17" thickBot="1">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -15975,7 +15975,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:5" ht="17" thickBot="1">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:5" ht="17" thickBot="1">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -16011,7 +16011,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:5" ht="17" thickBot="1">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -16029,7 +16029,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:5" ht="17" thickBot="1">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -16047,7 +16047,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:5" ht="17" thickBot="1">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -16065,7 +16065,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:5" ht="17" thickBot="1">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -16083,7 +16083,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:5" ht="17" thickBot="1">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -16101,7 +16101,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:5" ht="17" thickBot="1">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -16119,7 +16119,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:5" ht="17" thickBot="1">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -16137,7 +16137,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:5" ht="17" thickBot="1">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -16155,7 +16155,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:5" ht="17" thickBot="1">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -16173,7 +16173,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:5" ht="17" thickBot="1">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:5" ht="17" thickBot="1">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -16209,7 +16209,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:5" ht="17" thickBot="1">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -16242,7 +16242,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:5" ht="17" thickBot="1">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -16260,7 +16260,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:5" ht="17" thickBot="1">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -16278,7 +16278,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:5" ht="17" thickBot="1">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:5" ht="17" thickBot="1">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -16314,7 +16314,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:5" ht="17" thickBot="1">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -16332,7 +16332,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:5" ht="17" thickBot="1">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -16350,7 +16350,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:5" ht="17" thickBot="1">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -16368,7 +16368,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:5" ht="17" thickBot="1">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -16386,7 +16386,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:5" ht="17" thickBot="1">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -16404,7 +16404,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:5" ht="17" thickBot="1">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:5" ht="17" thickBot="1">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -16440,7 +16440,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:5" ht="17" thickBot="1">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:5" ht="17" thickBot="1">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -16476,7 +16476,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:5" ht="17" thickBot="1">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -16494,7 +16494,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:5" ht="17" thickBot="1">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -16512,7 +16512,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:5" ht="17" thickBot="1">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -16530,7 +16530,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:5" ht="17" thickBot="1">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -16548,7 +16548,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:5" ht="17" thickBot="1">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:5" ht="17" thickBot="1">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -16584,7 +16584,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:5" ht="17" thickBot="1">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -16602,7 +16602,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:5" ht="17" thickBot="1">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -16620,7 +16620,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:5" ht="17" thickBot="1">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -16638,7 +16638,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:5" ht="17" thickBot="1">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -16656,7 +16656,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:5" ht="17" thickBot="1">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -16674,7 +16674,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:5" ht="17" thickBot="1">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -16692,7 +16692,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:5" ht="17" thickBot="1">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:5" ht="17" thickBot="1">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -16728,7 +16728,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:5" ht="17" thickBot="1">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -16746,7 +16746,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:5" ht="17" thickBot="1">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -16764,7 +16764,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:5" ht="17" thickBot="1">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -16782,7 +16782,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:5" ht="17" thickBot="1">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -16800,7 +16800,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:5" ht="17" thickBot="1">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -16818,7 +16818,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:5" ht="17" thickBot="1">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -16836,7 +16836,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:5" ht="17" thickBot="1">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -16854,7 +16854,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:5" ht="17" thickBot="1">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -16872,7 +16872,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:5" ht="17" thickBot="1">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -16890,7 +16890,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:5" ht="17" thickBot="1">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -16908,7 +16908,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:5" ht="17" thickBot="1">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -16926,7 +16926,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:5" ht="17" thickBot="1">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -16944,7 +16944,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:5" ht="17" thickBot="1">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -16962,7 +16962,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:5" ht="17" thickBot="1">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -16980,7 +16980,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:5" ht="17" thickBot="1">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -16998,7 +16998,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:5" ht="17" thickBot="1">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -17016,7 +17016,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:5" ht="17" thickBot="1">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -17034,7 +17034,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:5" ht="17" thickBot="1">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -17052,7 +17052,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:5" ht="17" thickBot="1">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -17070,7 +17070,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:5" ht="17" thickBot="1">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -17088,7 +17088,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:5" ht="17" thickBot="1">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -17106,7 +17106,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:5" ht="17" thickBot="1">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -17124,7 +17124,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:5" ht="17" thickBot="1">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -17142,7 +17142,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:5" ht="17" thickBot="1">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -17160,7 +17160,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:5" ht="17" thickBot="1">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -17178,7 +17178,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:5" ht="17" thickBot="1">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -17196,7 +17196,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:5" ht="17" thickBot="1">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -17214,7 +17214,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:5" ht="17" thickBot="1">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -17232,7 +17232,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:5" ht="17" thickBot="1">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -17250,7 +17250,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:5" ht="17" thickBot="1">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -17268,7 +17268,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:5" ht="17" thickBot="1">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -17286,7 +17286,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:5" ht="17" thickBot="1">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -17304,7 +17304,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:5" ht="17" thickBot="1">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -17322,7 +17322,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:5" ht="17" thickBot="1">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -17340,7 +17340,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:5" ht="17" thickBot="1">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -17358,7 +17358,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:5" ht="17" thickBot="1">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -17376,7 +17376,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:5" ht="17" thickBot="1">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -17409,7 +17409,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:5" ht="17" thickBot="1">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -17427,7 +17427,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:5" ht="17" thickBot="1">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -17445,7 +17445,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:5" ht="17" thickBot="1">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -17463,7 +17463,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:5" ht="17" thickBot="1">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -17481,7 +17481,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:5" ht="17" thickBot="1">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -17499,7 +17499,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:5" ht="17" thickBot="1">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -17517,7 +17517,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:5" ht="17" thickBot="1">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -17535,7 +17535,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:5" ht="17" thickBot="1">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -17553,7 +17553,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:5" ht="17" thickBot="1">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -17571,7 +17571,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:5" ht="17" thickBot="1">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -17589,7 +17589,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:5" ht="17" thickBot="1">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -17607,7 +17607,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:5" ht="17" thickBot="1">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -17625,7 +17625,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:5" ht="17" thickBot="1">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:5" ht="17" thickBot="1">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -17661,7 +17661,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:5" ht="17" thickBot="1">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -17679,7 +17679,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:5" ht="17" thickBot="1">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -17697,7 +17697,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:5" ht="17" thickBot="1">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -17715,7 +17715,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:5" ht="17" thickBot="1">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -17733,7 +17733,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:5" ht="17" thickBot="1">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -17751,7 +17751,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:5" ht="17" thickBot="1">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -17769,7 +17769,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:5" ht="17" thickBot="1">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:5" ht="17" thickBot="1">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -17805,7 +17805,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:5" ht="17" thickBot="1">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -17823,7 +17823,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:5" ht="17" thickBot="1">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -17841,7 +17841,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:5" ht="17" thickBot="1">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -17859,7 +17859,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:5" ht="17" thickBot="1">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -17877,7 +17877,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:5" ht="17" thickBot="1">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -17895,7 +17895,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:5" ht="17" thickBot="1">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -17913,7 +17913,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:5" ht="17" thickBot="1">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:5" ht="17" thickBot="1">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -17949,7 +17949,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:5" ht="17" thickBot="1">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -17967,7 +17967,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:5" ht="17" thickBot="1">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -17985,7 +17985,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:5" ht="17" thickBot="1">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -18003,7 +18003,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:5" ht="17" thickBot="1">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -18021,7 +18021,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:5" ht="17" thickBot="1">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -18039,7 +18039,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:5" ht="17" thickBot="1">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -18057,7 +18057,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:5" ht="17" thickBot="1">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -18075,7 +18075,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:5" ht="17" thickBot="1">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -18093,7 +18093,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:5" ht="17" thickBot="1">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -18111,7 +18111,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:5" ht="17" thickBot="1">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -18129,7 +18129,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:5" ht="17" thickBot="1">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -18147,7 +18147,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:5" ht="17" thickBot="1">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -18165,7 +18165,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:5" ht="17" thickBot="1">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:5" ht="17" thickBot="1">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -18201,7 +18201,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:5" ht="17" thickBot="1">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -18219,7 +18219,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:5" ht="17" thickBot="1">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -18237,7 +18237,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:5" ht="17" thickBot="1">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -18255,7 +18255,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:5" ht="17" thickBot="1">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:5" ht="17" thickBot="1">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -18291,7 +18291,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:5" ht="17" thickBot="1">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -18309,7 +18309,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:5" ht="17" thickBot="1">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -18327,7 +18327,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:5" ht="17" thickBot="1">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -18345,7 +18345,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:5" ht="17" thickBot="1">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -18363,7 +18363,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:5" ht="17" thickBot="1">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -18381,7 +18381,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:5" ht="17" thickBot="1">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -18399,7 +18399,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:5" ht="17" thickBot="1">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:5" ht="17" thickBot="1">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -18435,7 +18435,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:5" ht="17" thickBot="1">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -18453,7 +18453,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:5" ht="17" thickBot="1">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -18471,7 +18471,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:5" ht="17" thickBot="1">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -18489,7 +18489,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:5" ht="17" thickBot="1">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -18507,7 +18507,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:5" ht="17" thickBot="1">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:5" ht="17" thickBot="1">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -18543,7 +18543,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:5" ht="17" thickBot="1">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -18576,7 +18576,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:5" ht="17" thickBot="1">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -18594,7 +18594,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:5" ht="17" thickBot="1">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -18612,7 +18612,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:5" ht="17" thickBot="1">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -18630,7 +18630,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:5" ht="17" thickBot="1">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:5" ht="17" thickBot="1">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -18666,7 +18666,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:5" ht="17" thickBot="1">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -18684,7 +18684,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:5" ht="17" thickBot="1">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -18702,7 +18702,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:5" ht="17" thickBot="1">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -18720,7 +18720,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:5" ht="17" thickBot="1">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -18738,7 +18738,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:5" ht="17" thickBot="1">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -18756,7 +18756,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:5" ht="17" thickBot="1">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -18774,7 +18774,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:5" ht="17" thickBot="1">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:5" ht="17" thickBot="1">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -18810,7 +18810,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:5" ht="17" thickBot="1">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -18828,7 +18828,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:5" ht="17" thickBot="1">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -18846,7 +18846,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:5" ht="17" thickBot="1">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -18864,7 +18864,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:5" ht="17" thickBot="1">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -18882,7 +18882,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:5" ht="17" thickBot="1">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -18900,7 +18900,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:5" ht="17" thickBot="1">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -18918,7 +18918,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:5" ht="17" thickBot="1">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -18936,7 +18936,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:5" ht="17" thickBot="1">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -18954,7 +18954,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:5" ht="17" thickBot="1">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -18972,7 +18972,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:5" ht="17" thickBot="1">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -18990,7 +18990,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:5" ht="17" thickBot="1">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -19008,7 +19008,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:5" ht="17" thickBot="1">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -19026,7 +19026,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:5" ht="17" thickBot="1">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -19044,7 +19044,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:5" ht="17" thickBot="1">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -19062,7 +19062,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:5" ht="17" thickBot="1">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -19080,7 +19080,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:5" ht="17" thickBot="1">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -19098,7 +19098,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:5" ht="17" thickBot="1">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -19116,7 +19116,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:5" ht="17" thickBot="1">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -19134,7 +19134,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:5" ht="17" thickBot="1">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -19152,7 +19152,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:5" ht="17" thickBot="1">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -19170,7 +19170,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:5" ht="17" thickBot="1">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -19188,7 +19188,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:5" ht="17" thickBot="1">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -19206,7 +19206,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:5" ht="17" thickBot="1">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -19224,7 +19224,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:5" ht="17" thickBot="1">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -19242,7 +19242,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:5" ht="17" thickBot="1">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -19260,7 +19260,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:5" ht="17" thickBot="1">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -19278,7 +19278,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:5" ht="17" thickBot="1">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -19296,7 +19296,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:5" ht="17" thickBot="1">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -19314,7 +19314,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:5" ht="17" thickBot="1">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -19332,7 +19332,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:5" ht="17" thickBot="1">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:5" ht="17" thickBot="1">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -19368,7 +19368,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:5" ht="17" thickBot="1">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -19386,7 +19386,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:5" ht="17" thickBot="1">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -19404,7 +19404,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:5" ht="17" thickBot="1">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -19422,7 +19422,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:5" ht="17" thickBot="1">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -19440,7 +19440,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:5" ht="17" thickBot="1">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -19458,7 +19458,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:5" ht="17" thickBot="1">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -19476,7 +19476,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:5" ht="17" thickBot="1">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -19494,7 +19494,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:5" ht="17" thickBot="1">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:5" ht="17" thickBot="1">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -19530,7 +19530,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:5" ht="17" thickBot="1">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -19548,7 +19548,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:5" ht="17" thickBot="1">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -19566,7 +19566,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:5" ht="17" thickBot="1">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -19584,7 +19584,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:5" ht="17" thickBot="1">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -19602,7 +19602,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:5" ht="17" thickBot="1">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -19620,7 +19620,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:5" ht="17" thickBot="1">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -19638,7 +19638,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:5" ht="17" thickBot="1">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -19656,7 +19656,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:5" ht="17" thickBot="1">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:5" ht="17" thickBot="1">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:5" ht="17" thickBot="1">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -19710,7 +19710,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:5" ht="17" thickBot="1">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -19743,7 +19743,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:5" ht="17" thickBot="1">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -19761,7 +19761,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:5" ht="17" thickBot="1">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -19779,7 +19779,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:5" ht="17" thickBot="1">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -19797,7 +19797,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:5" ht="17" thickBot="1">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -19815,7 +19815,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:5" ht="17" thickBot="1">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -19833,7 +19833,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:5" ht="17" thickBot="1">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -19851,7 +19851,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:5" ht="17" thickBot="1">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -19869,7 +19869,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:5" ht="17" thickBot="1">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -19887,7 +19887,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:5" ht="17" thickBot="1">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -19905,7 +19905,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:5" ht="17" thickBot="1">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -19923,7 +19923,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:5" ht="17" thickBot="1">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -19941,7 +19941,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:5" ht="17" thickBot="1">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -19959,7 +19959,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:5" ht="17" thickBot="1">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -19977,7 +19977,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:5" ht="17" thickBot="1">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -19995,7 +19995,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:5" ht="17" thickBot="1">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -20013,7 +20013,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:5" ht="17" thickBot="1">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -20031,7 +20031,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:5" ht="17" thickBot="1">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -20049,7 +20049,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:5" ht="17" thickBot="1">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -20067,7 +20067,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:5" ht="17" thickBot="1">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -20085,7 +20085,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:5" ht="17" thickBot="1">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -20103,7 +20103,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:5" ht="17" thickBot="1">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:5" ht="17" thickBot="1">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -20139,7 +20139,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:5" ht="17" thickBot="1">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -20157,7 +20157,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:5" ht="17" thickBot="1">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -20175,7 +20175,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:5" ht="17" thickBot="1">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -20193,7 +20193,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:5" ht="17" thickBot="1">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -20211,7 +20211,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:5" ht="17" thickBot="1">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -20229,7 +20229,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:5" ht="17" thickBot="1">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -20247,7 +20247,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:5" ht="17" thickBot="1">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -20265,7 +20265,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:5" ht="17" thickBot="1">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -20283,7 +20283,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:5" ht="17" thickBot="1">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -20301,7 +20301,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:5" ht="17" thickBot="1">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -20319,7 +20319,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:5" ht="17" thickBot="1">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -20337,7 +20337,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:5" ht="17" thickBot="1">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -20355,7 +20355,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:5" ht="17" thickBot="1">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -20373,7 +20373,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:5" ht="17" thickBot="1">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -20391,7 +20391,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:5" ht="17" thickBot="1">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -20409,7 +20409,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:5" ht="17" thickBot="1">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -20427,7 +20427,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:5" ht="17" thickBot="1">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -20445,7 +20445,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:5" ht="17" thickBot="1">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -20463,7 +20463,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:5" ht="17" thickBot="1">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -20481,7 +20481,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:5" ht="17" thickBot="1">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -20499,7 +20499,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:5" ht="17" thickBot="1">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -20517,7 +20517,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:5" ht="17" thickBot="1">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -20535,7 +20535,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:5" ht="17" thickBot="1">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -20553,7 +20553,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:5" ht="17" thickBot="1">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -20571,7 +20571,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:5" ht="17" thickBot="1">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -20589,7 +20589,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:5" ht="17" thickBot="1">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -20607,7 +20607,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:5" ht="17" thickBot="1">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -20625,7 +20625,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:5" ht="17" thickBot="1">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -20643,7 +20643,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:5" ht="17" thickBot="1">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -20661,7 +20661,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:5" ht="17" thickBot="1">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -20679,7 +20679,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:5" ht="17" thickBot="1">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -20697,7 +20697,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:5" ht="17" thickBot="1">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -20715,7 +20715,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:5" ht="17" thickBot="1">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -20733,7 +20733,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:5" ht="17" thickBot="1">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -20751,7 +20751,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:5" ht="17" thickBot="1">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -20769,7 +20769,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:5" ht="17" thickBot="1">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -20787,7 +20787,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:5" ht="17" thickBot="1">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -20805,7 +20805,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:5" ht="17" thickBot="1">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -20823,7 +20823,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:5" ht="17" thickBot="1">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -20841,7 +20841,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:5" ht="17" thickBot="1">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -20859,7 +20859,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:5" ht="17" thickBot="1">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -20877,7 +20877,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:5" ht="17" thickBot="1">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -20910,7 +20910,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:5" ht="17" thickBot="1">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -20928,7 +20928,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:5" ht="17" thickBot="1">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -20946,7 +20946,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:5" ht="17" thickBot="1">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -20964,7 +20964,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:5" ht="17" thickBot="1">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -20982,7 +20982,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:5" ht="17" thickBot="1">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -21000,7 +21000,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:5" ht="17" thickBot="1">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -21018,7 +21018,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:5" ht="17" thickBot="1">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -21036,7 +21036,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:5" ht="17" thickBot="1">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -21054,7 +21054,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:5" ht="17" thickBot="1">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -21072,7 +21072,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:5" ht="17" thickBot="1">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -21090,7 +21090,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:5" ht="17" thickBot="1">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -21108,7 +21108,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="782" spans="1:5" ht="17" thickBot="1">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -21126,7 +21126,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="783" spans="1:5" ht="17" thickBot="1">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -21144,7 +21144,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="784" spans="1:5" ht="17" thickBot="1">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -21162,7 +21162,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="785" spans="1:5" ht="17" thickBot="1">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -21180,7 +21180,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="786" spans="1:5" ht="17" thickBot="1">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -21198,7 +21198,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="787" spans="1:5" ht="17" thickBot="1">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -21216,7 +21216,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="788" spans="1:5" ht="17" thickBot="1">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -21234,7 +21234,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="789" spans="1:5" ht="17" thickBot="1">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -21252,7 +21252,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="790" spans="1:5" ht="17" thickBot="1">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -21270,7 +21270,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="791" spans="1:5" ht="17" thickBot="1">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -21288,7 +21288,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="792" spans="1:5" ht="17" thickBot="1">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -21306,7 +21306,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="793" spans="1:5" ht="17" thickBot="1">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -21324,7 +21324,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="794" spans="1:5" ht="17" thickBot="1">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -21342,7 +21342,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="795" spans="1:5" ht="17" thickBot="1">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -21360,7 +21360,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="796" spans="1:5" ht="17" thickBot="1">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -21378,7 +21378,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="797" spans="1:5" ht="17" thickBot="1">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -21396,7 +21396,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="798" spans="1:5" ht="17" thickBot="1">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -21414,7 +21414,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="799" spans="1:5" ht="17" thickBot="1">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -21432,7 +21432,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="800" spans="1:5" ht="17" thickBot="1">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -21450,7 +21450,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="801" spans="1:5" ht="17" thickBot="1">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -21468,7 +21468,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="802" spans="1:5" ht="17" thickBot="1">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -21486,7 +21486,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="803" spans="1:5" ht="17" thickBot="1">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -21504,7 +21504,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="804" spans="1:5" ht="17" thickBot="1">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -21522,7 +21522,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="805" spans="1:5" ht="17" thickBot="1">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -21540,7 +21540,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="806" spans="1:5" ht="17" thickBot="1">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -21558,7 +21558,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="807" spans="1:5" ht="17" thickBot="1">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -21576,7 +21576,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="808" spans="1:5" ht="17" thickBot="1">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -21594,7 +21594,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="809" spans="1:5" ht="17" thickBot="1">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -21612,7 +21612,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="810" spans="1:5" ht="17" thickBot="1">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -21630,7 +21630,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="811" spans="1:5" ht="17" thickBot="1">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -21648,7 +21648,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="812" spans="1:5" ht="17" thickBot="1">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -21666,7 +21666,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="813" spans="1:5" ht="17" thickBot="1">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -21684,7 +21684,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="814" spans="1:5" ht="17" thickBot="1">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -21702,7 +21702,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="815" spans="1:5" ht="17" thickBot="1">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -21720,7 +21720,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="816" spans="1:5" ht="17" thickBot="1">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -21738,7 +21738,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="817" spans="1:5" ht="17" thickBot="1">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -21756,7 +21756,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="818" spans="1:5" ht="17" thickBot="1">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -21774,7 +21774,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="819" spans="1:5" ht="17" thickBot="1">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -21792,7 +21792,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="820" spans="1:5" ht="17" thickBot="1">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -21810,7 +21810,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="821" spans="1:5" ht="17" thickBot="1">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -21828,7 +21828,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="822" spans="1:5" ht="17" thickBot="1">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -21846,7 +21846,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="823" spans="1:5" ht="17" thickBot="1">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -21864,7 +21864,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="824" spans="1:5" ht="17" thickBot="1">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -21882,7 +21882,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="825" spans="1:5" ht="17" thickBot="1">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -21900,7 +21900,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="826" spans="1:5" ht="17" thickBot="1">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -21918,7 +21918,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="827" spans="1:5" ht="17" thickBot="1">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -21936,7 +21936,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="828" spans="1:5" ht="17" thickBot="1">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -21954,7 +21954,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="829" spans="1:5" ht="17" thickBot="1">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -21972,7 +21972,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="830" spans="1:5" ht="17" thickBot="1">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -21990,7 +21990,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="831" spans="1:5" ht="17" thickBot="1">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -22008,7 +22008,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="832" spans="1:5" ht="17" thickBot="1">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -22026,7 +22026,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="833" spans="1:5" ht="17" thickBot="1">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -22044,7 +22044,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="834" spans="1:5" ht="17" thickBot="1">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -22077,7 +22077,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="835" spans="1:5" ht="17" thickBot="1">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -22095,7 +22095,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="836" spans="1:5" ht="17" thickBot="1">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -22113,7 +22113,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="837" spans="1:5" ht="17" thickBot="1">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -22131,7 +22131,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="838" spans="1:5" ht="17" thickBot="1">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -22149,7 +22149,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="839" spans="1:5" ht="17" thickBot="1">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -22167,7 +22167,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="840" spans="1:5" ht="17" thickBot="1">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -22185,7 +22185,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="841" spans="1:5" ht="17" thickBot="1">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -22203,7 +22203,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="842" spans="1:5" ht="17" thickBot="1">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -22221,7 +22221,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="843" spans="1:5" ht="17" thickBot="1">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -22239,7 +22239,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="844" spans="1:5" ht="17" thickBot="1">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -22257,7 +22257,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="845" spans="1:5" ht="17" thickBot="1">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -22275,7 +22275,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="846" spans="1:5" ht="17" thickBot="1">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -22293,7 +22293,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="847" spans="1:5" ht="17" thickBot="1">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -22311,7 +22311,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="848" spans="1:5" ht="17" thickBot="1">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -22329,7 +22329,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="849" spans="1:5" ht="17" thickBot="1">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -22347,7 +22347,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="850" spans="1:5" ht="17" thickBot="1">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -22365,7 +22365,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="851" spans="1:5" ht="17" thickBot="1">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -22383,7 +22383,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="852" spans="1:5" ht="17" thickBot="1">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -22401,7 +22401,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="853" spans="1:5" ht="17" thickBot="1">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -22419,7 +22419,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="854" spans="1:5" ht="17" thickBot="1">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -22437,7 +22437,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="855" spans="1:5" ht="17" thickBot="1">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -22455,7 +22455,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="856" spans="1:5" ht="17" thickBot="1">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -22473,7 +22473,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="857" spans="1:5" ht="17" thickBot="1">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -22491,7 +22491,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="858" spans="1:5" ht="17" thickBot="1">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -22509,7 +22509,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="859" spans="1:5" ht="17" thickBot="1">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -22527,7 +22527,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="860" spans="1:5" ht="17" thickBot="1">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -22545,7 +22545,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="861" spans="1:5" ht="17" thickBot="1">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -22563,7 +22563,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="862" spans="1:5" ht="17" thickBot="1">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -22581,7 +22581,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="863" spans="1:5" ht="17" thickBot="1">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -22599,7 +22599,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="864" spans="1:5" ht="17" thickBot="1">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -22617,7 +22617,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="865" spans="1:5" ht="17" thickBot="1">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -22635,7 +22635,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="866" spans="1:5" ht="17" thickBot="1">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -22653,7 +22653,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="867" spans="1:5" ht="17" thickBot="1">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -22671,7 +22671,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="868" spans="1:5" ht="17" thickBot="1">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -22689,7 +22689,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="869" spans="1:5" ht="17" thickBot="1">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -22707,7 +22707,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="870" spans="1:5" ht="17" thickBot="1">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -22725,7 +22725,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="871" spans="1:5" ht="17" thickBot="1">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -22743,7 +22743,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="872" spans="1:5" ht="17" thickBot="1">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -22761,7 +22761,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="873" spans="1:5" ht="17" thickBot="1">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -22779,7 +22779,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="874" spans="1:5" ht="17" thickBot="1">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -22797,7 +22797,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="875" spans="1:5" ht="17" thickBot="1">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -22815,7 +22815,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="876" spans="1:5" ht="17" thickBot="1">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -22833,7 +22833,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="877" spans="1:5" ht="17" thickBot="1">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -22851,7 +22851,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="878" spans="1:5" ht="17" thickBot="1">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -22884,7 +22884,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="879" spans="1:5" ht="17" thickBot="1">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -22917,7 +22917,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="880" spans="1:5" ht="17" thickBot="1">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -22950,7 +22950,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="881" spans="1:5" ht="17" thickBot="1">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -22968,7 +22968,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="882" spans="1:5" ht="17" thickBot="1">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -23001,7 +23001,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="883" spans="1:5" ht="17" thickBot="1">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -23034,7 +23034,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="884" spans="1:5" ht="17" thickBot="1">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
@@ -23052,7 +23052,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="885" spans="1:5" ht="17" thickBot="1">
       <c r="A885" s="15">
         <v>46088</v>
       </c>
@@ -23070,7 +23070,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:5" ht="16">
       <c r="A886" s="8">
         <v>46102</v>
       </c>
@@ -23088,7 +23088,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:5" ht="16">
       <c r="A887" s="8">
         <v>46109</v>
       </c>
@@ -23106,7 +23106,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:5" ht="16">
       <c r="A888" s="8">
         <v>46116</v>
       </c>
@@ -23124,7 +23124,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:5" ht="16">
       <c r="A889" s="8">
         <v>46123</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>500040</v>
       </c>
     </row>
-    <row r="890" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:5" ht="16">
       <c r="A890" s="8">
         <v>46130</v>
       </c>
@@ -23160,7 +23160,7 @@
         <v>508303</v>
       </c>
     </row>
-    <row r="891" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:5" ht="16">
       <c r="A891" s="8">
         <v>46137</v>
       </c>
@@ -23178,7 +23178,7 @@
         <v>511616</v>
       </c>
     </row>
-    <row r="892" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:5" ht="16">
       <c r="A892" s="8">
         <v>46144</v>
       </c>
@@ -23196,7 +23196,7 @@
         <v>518773</v>
       </c>
     </row>
-    <row r="893" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:5" ht="16">
       <c r="A893" s="8">
         <v>46151</v>
       </c>
@@ -23229,7 +23229,7 @@
         <v>513755</v>
       </c>
     </row>
-    <row r="894" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:5" ht="16">
       <c r="A894" s="8">
         <v>46158</v>
       </c>
@@ -23247,7 +23247,7 @@
         <v>511216</v>
       </c>
     </row>
-    <row r="895" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:5" ht="16">
       <c r="A895" s="8">
         <v>46165</v>
       </c>
@@ -23265,7 +23265,7 @@
         <v>523574</v>
       </c>
     </row>
-    <row r="896" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:5" ht="16">
       <c r="A896" s="8">
         <v>46172</v>
       </c>
@@ -23298,7 +23298,7 @@
         <v>492795</v>
       </c>
     </row>
-    <row r="897" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:5" ht="16">
       <c r="A897" s="8">
         <v>46179</v>
       </c>
@@ -23316,7 +23316,7 @@
         <v>521804</v>
       </c>
     </row>
-    <row r="898" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:5" ht="16">
       <c r="A898" s="8">
         <v>46186</v>
       </c>
@@ -23334,7 +23334,7 @@
         <v>520406</v>
       </c>
     </row>
-    <row r="899" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:5" ht="16">
       <c r="A899" s="8">
         <v>46193</v>
       </c>
@@ -23367,7 +23367,7 @@
         <v>521998</v>
       </c>
     </row>
-    <row r="900" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:5" ht="16">
       <c r="A900" s="8">
         <v>46200</v>
       </c>
@@ -23385,7 +23385,7 @@
         <v>525474</v>
       </c>
     </row>
-    <row r="901" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:5" ht="16">
       <c r="A901" s="8">
         <v>46207</v>
       </c>
@@ -23418,7 +23418,7 @@
         <v>482121</v>
       </c>
     </row>
-    <row r="902" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:5" ht="16">
       <c r="A902" s="8">
         <v>46214</v>
       </c>
@@ -23436,7 +23436,7 @@
         <v>503525</v>
       </c>
     </row>
-    <row r="903" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:5" ht="16">
       <c r="A903" s="8">
         <v>46221</v>
       </c>
@@ -23454,7 +23454,7 @@
         <v>523900</v>
       </c>
     </row>
-    <row r="904" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:5" ht="16">
       <c r="A904" s="8">
         <v>46228</v>
       </c>
@@ -23487,7 +23487,7 @@
         <v>527162</v>
       </c>
     </row>
-    <row r="905" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:5" ht="16">
       <c r="A905" s="8">
         <v>46235</v>
       </c>
@@ -23505,7 +23505,7 @@
         <v>526410</v>
       </c>
     </row>
-    <row r="906" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:5" ht="16">
       <c r="A906" s="8">
         <v>46242</v>
       </c>
@@ -23516,7 +23516,7 @@
         <v>0.50069444444444444</v>
       </c>
       <c r="D906" s="7" t="str">
-        <f t="shared" ref="D906:D907" si="21">IF(
+        <f t="shared" ref="D906:D908" si="21">IF(
  AND(
   A906 &gt;= IF(
          YEAR(A906)&gt;=2007,
@@ -23538,7 +23538,7 @@
         <v>526624</v>
       </c>
     </row>
-    <row r="907" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:5" ht="16">
       <c r="A907" s="8">
         <v>46249</v>
       </c>
@@ -23554,6 +23554,24 @@
       </c>
       <c r="E907" s="20">
         <v>525099</v>
+      </c>
+    </row>
+    <row r="908" spans="1:5" ht="16">
+      <c r="A908" s="8">
+        <v>46256</v>
+      </c>
+      <c r="B908" s="8">
+        <v>46260</v>
+      </c>
+      <c r="C908" s="21">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="D908" s="7" t="str">
+        <f t="shared" si="21"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E908" s="20">
+        <v>532462</v>
       </c>
     </row>
   </sheetData>
@@ -23569,7 +23587,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23580,12 +23598,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23593,7 +23611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23601,7 +23619,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4352567C-D31F-4D4C-A967-6D285C862FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD90C406-87E4-DA45-A71C-AC601F3A8992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17980" yWindow="780" windowWidth="18020" windowHeight="20760" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -6830,7 +6830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E908"/>
+  <dimension ref="A1:E909"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -23572,6 +23572,39 @@
       </c>
       <c r="E908" s="20">
         <v>532462</v>
+      </c>
+    </row>
+    <row r="909" spans="1:5" ht="16">
+      <c r="A909" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B909" s="8">
+        <v>46267</v>
+      </c>
+      <c r="C909" s="21">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="D909" s="7" t="str">
+        <f t="shared" ref="D909" si="22">IF(
+ AND(
+  A909 &gt;= IF(
+         YEAR(A909)&gt;=2007,
+         DATE(YEAR(A909),3,14)-WEEKDAY(DATE(YEAR(A909),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A909),4,7)-WEEKDAY(DATE(YEAR(A909),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A909 &lt;  IF(
+         YEAR(A909)&gt;=2007,
+         DATE(YEAR(A909),11,7)-WEEKDAY(DATE(YEAR(A909),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A909),10,31)-WEEKDAY(DATE(YEAR(A909),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E909" s="20">
+        <v>543212</v>
       </c>
     </row>
   </sheetData>
